--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W144"/>
+  <dimension ref="A1:W143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7815,700 +7815,704 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PowerCabling [0.65 m]</t>
+          <t>PowerCabling [1 km]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.39785486915998</v>
+        <v>2.010781985154887</v>
       </c>
       <c r="C102" t="n">
-        <v>1.177547892477173</v>
+        <v>2.501748562758023</v>
       </c>
       <c r="D102" t="n">
-        <v>0.7079518073210659</v>
+        <v>1.0762827351967</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8064463076048899</v>
+        <v>1.340395859588833</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8567240852678373</v>
+        <v>2.690233385028318</v>
       </c>
       <c r="G102" t="n">
-        <v>1.098612288668121</v>
+        <v>2.69207351105048</v>
       </c>
       <c r="H102" t="n">
-        <v>0.816763606488635</v>
+        <v>0.8831062648796865</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8871977641674974</v>
+        <v>0.8877342334965648</v>
       </c>
       <c r="J102" t="n">
-        <v>0.6903397119573619</v>
+        <v>0.5360395876713213</v>
       </c>
       <c r="K102" t="n">
-        <v>0.778485755451308</v>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+        <v>0.4102693147587508</v>
+      </c>
+      <c r="L102" t="n">
+        <v>15.48374245255928</v>
+      </c>
+      <c r="M102" t="n">
+        <v>31.87182960641649</v>
+      </c>
       <c r="N102" t="n">
-        <v>0.7178641773253449</v>
+        <v>1.094649658656712</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>1.01477540141736</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>1.02391197499309</v>
       </c>
       <c r="R102" t="n">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="S102" t="n">
-        <v>3.482677556076688</v>
+        <v>3.448040243151771</v>
       </c>
       <c r="T102" t="n">
-        <v>1.723275581494747</v>
+        <v>5.163013430090539</v>
       </c>
       <c r="U102" t="n">
-        <v>0.3227037865590063</v>
+        <v>0.2569234179085018</v>
       </c>
       <c r="V102" t="n">
-        <v>0.2098032219716392</v>
+        <v>0.136355733685096</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>0.1274900398406374</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PowerCabling [1 km]</t>
+          <t>PowerCabling [1 m]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.010781985154887</v>
+        <v>8.960628703994312</v>
       </c>
       <c r="C103" t="n">
-        <v>2.501748562758023</v>
+        <v>8.512605080109912</v>
       </c>
       <c r="D103" t="n">
-        <v>1.0762827351967</v>
+        <v>2.563826009997479</v>
       </c>
       <c r="E103" t="n">
-        <v>1.340395859588833</v>
+        <v>2.657354358659842</v>
       </c>
       <c r="F103" t="n">
-        <v>2.690233385028318</v>
+        <v>0.09569829597351423</v>
       </c>
       <c r="G103" t="n">
-        <v>2.69207351105048</v>
+        <v>0.1926644596544404</v>
       </c>
       <c r="H103" t="n">
-        <v>0.8831062648796865</v>
+        <v>0.9304145161156586</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8877342334965648</v>
+        <v>0.9409416144394661</v>
       </c>
       <c r="J103" t="n">
-        <v>0.5360395876713213</v>
+        <v>0.07617349154285293</v>
       </c>
       <c r="K103" t="n">
-        <v>0.4102693147587508</v>
+        <v>0.08994329490793485</v>
       </c>
       <c r="L103" t="n">
-        <v>15.48374245255928</v>
+        <v>154.4205952845249</v>
       </c>
       <c r="M103" t="n">
-        <v>31.87182960641649</v>
+        <v>117.2489847683706</v>
       </c>
       <c r="N103" t="n">
-        <v>1.094649658656712</v>
+        <v>0.8092134325026138</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
       <c r="P103" t="n">
-        <v>1.01477540141736</v>
+        <v>1.012109905071207</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.02391197499309</v>
+        <v>1.013709029470608</v>
       </c>
       <c r="R103" t="n">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="S103" t="n">
-        <v>3.448040243151771</v>
+        <v>11.97095412098275</v>
       </c>
       <c r="T103" t="n">
-        <v>5.163013430090539</v>
+        <v>10.5816499252207</v>
       </c>
       <c r="U103" t="n">
-        <v>0.2569234179085018</v>
+        <v>0.2007217651287972</v>
       </c>
       <c r="V103" t="n">
-        <v>0.136355733685096</v>
+        <v>0.01288688487317927</v>
       </c>
       <c r="W103" t="n">
-        <v>0.1274900398406374</v>
+        <v>0.02027027027027027</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PowerCabling [1 m]</t>
+          <t>PrecastConcrete</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11.20334621985414</v>
+        <v>0.3786825381440391</v>
       </c>
       <c r="C104" t="n">
-        <v>8.464978196559391</v>
+        <v>0.4139935392052079</v>
       </c>
       <c r="D104" t="n">
-        <v>2.635624454095594</v>
+        <v>0.5213861998549613</v>
       </c>
       <c r="E104" t="n">
-        <v>2.64134983197638</v>
+        <v>0.606841084710584</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1036665331854352</v>
+        <v>4.10855010168048</v>
       </c>
       <c r="G104" t="n">
-        <v>0.194829642911157</v>
+        <v>4.182741758969894</v>
       </c>
       <c r="H104" t="n">
-        <v>0.9506221817290958</v>
+        <v>0.9470780582933653</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9397831710268998</v>
+        <v>0.9302077316110111</v>
       </c>
       <c r="J104" t="n">
-        <v>0.05192588075204101</v>
+        <v>0.8140167374036025</v>
       </c>
       <c r="K104" t="n">
-        <v>0.09081500265574627</v>
+        <v>0.7336729667981577</v>
       </c>
       <c r="L104" t="n">
-        <v>201.3553956838669</v>
+        <v>9.302569536348297</v>
       </c>
       <c r="M104" t="n">
-        <v>115.6525766093446</v>
+        <v>12.10141041085339</v>
       </c>
       <c r="N104" t="n">
-        <v>0.5983132679485376</v>
+        <v>0.9751404761879316</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
       <c r="P104" t="n">
-        <v>1.006312070646944</v>
+        <v>1.010954665172787</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.013899356429624</v>
+        <v>1.015071317116978</v>
       </c>
       <c r="R104" t="n">
-        <v>146</v>
+        <v>499</v>
       </c>
       <c r="S104" t="n">
-        <v>14.02844419713255</v>
+        <v>2.303176105176199</v>
       </c>
       <c r="T104" t="n">
-        <v>10.50946777434202</v>
+        <v>2.906557984936481</v>
       </c>
       <c r="U104" t="n">
-        <v>0.4029033360905952</v>
+        <v>0.02502537181778215</v>
       </c>
       <c r="V104" t="n">
-        <v>0.01629430506519627</v>
+        <v>0.04873973715259736</v>
       </c>
       <c r="W104" t="n">
-        <v>0.02054794520547945</v>
+        <v>0.0501002004008016</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PrecastConcrete</t>
+          <t>ProcessedNonInsulatingGlassPanes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.3786825381440391</v>
+        <v>1.33446238571039</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4139935392052079</v>
+        <v>1.448612953955083</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5213861998549613</v>
+        <v>0.6881025032050327</v>
       </c>
       <c r="E105" t="n">
-        <v>0.606841084710584</v>
+        <v>0.6113143746920594</v>
       </c>
       <c r="F105" t="n">
-        <v>4.10855010168048</v>
+        <v>3.546016452620567</v>
       </c>
       <c r="G105" t="n">
-        <v>4.182741758969894</v>
+        <v>3.703351838411336</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9470780582933653</v>
+        <v>0.9474301938836615</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9302077316110111</v>
+        <v>0.9607776179559141</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8140167374036025</v>
+        <v>0.7127931567166175</v>
       </c>
       <c r="K105" t="n">
-        <v>0.7336729667981577</v>
+        <v>0.6561514067583674</v>
       </c>
       <c r="L105" t="n">
-        <v>9.302569536348297</v>
+        <v>6.993810882712427</v>
       </c>
       <c r="M105" t="n">
-        <v>12.10141041085339</v>
+        <v>9.588530078040709</v>
       </c>
       <c r="N105" t="n">
-        <v>0.9751404761879316</v>
+        <v>1.164250442794594</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>1.010954665172787</v>
+        <v>1.009893725976472</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.015071317116978</v>
+        <v>1.020541475120251</v>
       </c>
       <c r="R105" t="n">
-        <v>499</v>
+        <v>130</v>
       </c>
       <c r="S105" t="n">
-        <v>2.303176105176199</v>
+        <v>2.417049395166277</v>
       </c>
       <c r="T105" t="n">
-        <v>2.906557984936481</v>
+        <v>2.869891820976882</v>
       </c>
       <c r="U105" t="n">
-        <v>0.02502537181778215</v>
+        <v>0.1726170480952466</v>
       </c>
       <c r="V105" t="n">
-        <v>0.04873973715259736</v>
+        <v>0.06381066808003505</v>
       </c>
       <c r="W105" t="n">
-        <v>0.0501002004008016</v>
+        <v>0.06923076923076923</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ProcessedNonInsulatingGlassPanes</t>
+          <t>ReadyMix</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.33446238571039</v>
+        <v>0.290951979596255</v>
       </c>
       <c r="C106" t="n">
-        <v>1.448612953955083</v>
+        <v>0.2909845604249281</v>
       </c>
       <c r="D106" t="n">
-        <v>0.6881025032050327</v>
+        <v>0.6846305795100622</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6113143746920594</v>
+        <v>0.5153703803405862</v>
       </c>
       <c r="F106" t="n">
-        <v>3.546016452620567</v>
+        <v>4.434617601504179</v>
       </c>
       <c r="G106" t="n">
-        <v>3.703351838411336</v>
+        <v>4.433677739630799</v>
       </c>
       <c r="H106" t="n">
-        <v>0.9474301938836615</v>
+        <v>0.9870453238000487</v>
       </c>
       <c r="I106" t="n">
-        <v>0.9607776179559141</v>
+        <v>0.987965882497951</v>
       </c>
       <c r="J106" t="n">
-        <v>0.7127931567166175</v>
+        <v>0.9806788719522553</v>
       </c>
       <c r="K106" t="n">
-        <v>0.6561514067583674</v>
+        <v>0.9796251503495242</v>
       </c>
       <c r="L106" t="n">
-        <v>6.993810882712427</v>
+        <v>1.305638161006107</v>
       </c>
       <c r="M106" t="n">
-        <v>9.588530078040709</v>
+        <v>1.398262415869179</v>
       </c>
       <c r="N106" t="n">
-        <v>1.164250442794594</v>
+        <v>1.000637790752057</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>1.009893725976472</v>
+        <v>1.001537524163858</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.020541475120251</v>
+        <v>1.001822199521841</v>
       </c>
       <c r="R106" t="n">
-        <v>130</v>
+        <v>86770</v>
       </c>
       <c r="S106" t="n">
-        <v>2.417049395166277</v>
+        <v>0.6220325513957662</v>
       </c>
       <c r="T106" t="n">
-        <v>2.869891820976882</v>
+        <v>0.6429799944743362</v>
       </c>
       <c r="U106" t="n">
-        <v>0.1726170480952466</v>
+        <v>0.00110744742533687</v>
       </c>
       <c r="V106" t="n">
-        <v>0.06381066808003505</v>
+        <v>0.01130539686853737</v>
       </c>
       <c r="W106" t="n">
-        <v>0.06923076923076923</v>
+        <v>0.01195113518497177</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ReadyMix</t>
+          <t>RebarSteel</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.290951979596255</v>
+        <v>0.9342361934783976</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2909845604249281</v>
+        <v>0.9381636366760756</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6846305795100622</v>
+        <v>1.661363338618052</v>
       </c>
       <c r="E107" t="n">
-        <v>0.5153703803405862</v>
+        <v>1.651861243795067</v>
       </c>
       <c r="F107" t="n">
-        <v>4.434617601504179</v>
+        <v>3.664424224778775</v>
       </c>
       <c r="G107" t="n">
-        <v>4.433677739630799</v>
+        <v>3.751123252407115</v>
       </c>
       <c r="H107" t="n">
-        <v>0.9870453238000487</v>
+        <v>0.9680636738527292</v>
       </c>
       <c r="I107" t="n">
-        <v>0.987965882497951</v>
+        <v>0.9746013036068354</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9806788719522553</v>
+        <v>0.6875658452951185</v>
       </c>
       <c r="K107" t="n">
-        <v>0.9796251503495242</v>
+        <v>0.7006694797153243</v>
       </c>
       <c r="L107" t="n">
-        <v>1.305638161006107</v>
+        <v>20.99519948678543</v>
       </c>
       <c r="M107" t="n">
-        <v>1.398262415869179</v>
+        <v>20.6025159996925</v>
       </c>
       <c r="N107" t="n">
-        <v>1.000637790752057</v>
+        <v>0.9974560885017318</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="P107" t="n">
-        <v>1.001537524163858</v>
+        <v>1.007455236554274</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.001822199521841</v>
+        <v>1.025271466101481</v>
       </c>
       <c r="R107" t="n">
-        <v>86770</v>
+        <v>204</v>
       </c>
       <c r="S107" t="n">
-        <v>0.6220325513957662</v>
+        <v>3.414816783051021</v>
       </c>
       <c r="T107" t="n">
-        <v>0.6429799944743362</v>
+        <v>3.36976542456875</v>
       </c>
       <c r="U107" t="n">
-        <v>0.00110744742533687</v>
+        <v>0.03106269780107337</v>
       </c>
       <c r="V107" t="n">
-        <v>0.01130539686853737</v>
+        <v>0.1207410319314589</v>
       </c>
       <c r="W107" t="n">
-        <v>0.01195113518497177</v>
+        <v>0.08823529411764705</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RebarSteel</t>
+          <t>ResilientFlooring</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.9342361934783976</v>
+        <v>1.084354343907561</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9381636366760756</v>
+        <v>1.089526301974485</v>
       </c>
       <c r="D108" t="n">
-        <v>1.661363338618052</v>
+        <v>1.048598896860703</v>
       </c>
       <c r="E108" t="n">
-        <v>1.651861243795067</v>
+        <v>1.068473315614834</v>
       </c>
       <c r="F108" t="n">
-        <v>3.664424224778775</v>
+        <v>3.915868751342284</v>
       </c>
       <c r="G108" t="n">
-        <v>3.751123252407115</v>
+        <v>3.995149172082091</v>
       </c>
       <c r="H108" t="n">
-        <v>0.9680636738527292</v>
+        <v>0.9384346422416922</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9746013036068354</v>
+        <v>0.9360211490591377</v>
       </c>
       <c r="J108" t="n">
-        <v>0.6875658452951185</v>
+        <v>0.5506846500526584</v>
       </c>
       <c r="K108" t="n">
-        <v>0.7006694797153243</v>
+        <v>0.5447395756348599</v>
       </c>
       <c r="L108" t="n">
-        <v>20.99519948678543</v>
+        <v>12.72678860894951</v>
       </c>
       <c r="M108" t="n">
-        <v>20.6025159996925</v>
+        <v>12.74343554804122</v>
       </c>
       <c r="N108" t="n">
-        <v>0.9974560885017318</v>
+        <v>1.011640502955706</v>
       </c>
       <c r="O108" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>1.007455236554274</v>
+        <v>1.038976544759671</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.025271466101481</v>
+        <v>1.037810624895072</v>
       </c>
       <c r="R108" t="n">
-        <v>204</v>
+        <v>468</v>
       </c>
       <c r="S108" t="n">
-        <v>3.414816783051021</v>
+        <v>3.488955810413167</v>
       </c>
       <c r="T108" t="n">
-        <v>3.36976542456875</v>
+        <v>3.512280715203127</v>
       </c>
       <c r="U108" t="n">
-        <v>0.03106269780107337</v>
+        <v>0.02520482083034865</v>
       </c>
       <c r="V108" t="n">
-        <v>0.1207410319314589</v>
+        <v>0.08316791825924923</v>
       </c>
       <c r="W108" t="n">
-        <v>0.08823529411764705</v>
+        <v>0.09401709401709404</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ResilientFlooring</t>
+          <t>RoofCoverBoards</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.084354343907561</v>
+        <v>0.2052640089593039</v>
       </c>
       <c r="C109" t="n">
-        <v>1.089526301974485</v>
+        <v>0.2001241086768103</v>
       </c>
       <c r="D109" t="n">
-        <v>1.048598896860703</v>
+        <v>0.6846773439688794</v>
       </c>
       <c r="E109" t="n">
-        <v>1.068473315614834</v>
+        <v>0.4718036292600613</v>
       </c>
       <c r="F109" t="n">
-        <v>3.915868751342284</v>
+        <v>2.543783342502795</v>
       </c>
       <c r="G109" t="n">
-        <v>3.995149172082091</v>
+        <v>2.926417555497999</v>
       </c>
       <c r="H109" t="n">
-        <v>0.9384346422416922</v>
+        <v>0.7591825066523465</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9360211490591377</v>
+        <v>0.8980326989054888</v>
       </c>
       <c r="J109" t="n">
-        <v>0.5506846500526584</v>
+        <v>0.8004099537943093</v>
       </c>
       <c r="K109" t="n">
-        <v>0.5447395756348599</v>
+        <v>0.9393258346928226</v>
       </c>
       <c r="L109" t="n">
-        <v>12.72678860894951</v>
+        <v>0.04147614781625295</v>
       </c>
       <c r="M109" t="n">
-        <v>12.74343554804122</v>
+        <v>0.7934112410859429</v>
       </c>
       <c r="N109" t="n">
-        <v>1.011640502955706</v>
+        <v>0.9768535432132915</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P109" t="n">
-        <v>1.038976544759671</v>
+        <v>1.007015456525137</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.037810624895072</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>468</v>
+        <v>20</v>
       </c>
       <c r="S109" t="n">
-        <v>3.488955810413167</v>
+        <v>-1.058163125479492</v>
       </c>
       <c r="T109" t="n">
-        <v>3.512280715203127</v>
+        <v>-0.3681207526856916</v>
       </c>
       <c r="U109" t="n">
-        <v>0.02520482083034865</v>
+        <v>0.0436559872099314</v>
       </c>
       <c r="V109" t="n">
-        <v>0.08316791825924923</v>
+        <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0.09401709401709404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RoofCoverBoards</t>
+          <t>RoofPanels</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.2052640089593039</v>
+        <v>0.745973544696887</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2001241086768103</v>
+        <v>0.8136678978089753</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6846773439688794</v>
+        <v>0.3853193452093117</v>
       </c>
       <c r="E110" t="n">
-        <v>0.4718036292600613</v>
+        <v>0.4201810589694409</v>
       </c>
       <c r="F110" t="n">
-        <v>2.543783342502795</v>
+        <v>3.449693254850341</v>
       </c>
       <c r="G110" t="n">
-        <v>2.926417555497999</v>
+        <v>3.715951695602787</v>
       </c>
       <c r="H110" t="n">
-        <v>0.7591825066523465</v>
+        <v>0.9396276723664576</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8980326989054888</v>
+        <v>0.9652075554857067</v>
       </c>
       <c r="J110" t="n">
-        <v>0.8004099537943093</v>
+        <v>0.923417045201437</v>
       </c>
       <c r="K110" t="n">
-        <v>0.9393258346928226</v>
+        <v>0.8885601779274186</v>
       </c>
       <c r="L110" t="n">
-        <v>0.04147614781625295</v>
+        <v>-0.4677286136268061</v>
       </c>
       <c r="M110" t="n">
-        <v>0.7934112410859429</v>
+        <v>1.488071442124216</v>
       </c>
       <c r="N110" t="n">
-        <v>0.9768535432132915</v>
+        <v>1.091270222023103</v>
       </c>
       <c r="O110" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
-        <v>1.007015456525137</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="S110" t="n">
-        <v>-1.058163125479492</v>
+        <v>0.6888254212557682</v>
       </c>
       <c r="T110" t="n">
-        <v>-0.3681207526856916</v>
+        <v>1.22494588083562</v>
       </c>
       <c r="U110" t="n">
-        <v>0.0436559872099314</v>
+        <v>0.1270133769611202</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>0.002674418540895177</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>0.01639344262295082</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RoofPanels</t>
+          <t>SheathingPanels</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.745973544696887</v>
+        <v>0.8791106428021422</v>
       </c>
       <c r="C111" t="n">
-        <v>0.8136678978089753</v>
+        <v>0.9276204385819743</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3853193452093117</v>
+        <v>0.4381401936628306</v>
       </c>
       <c r="E111" t="n">
-        <v>0.4201810589694409</v>
+        <v>0.4736889633141357</v>
       </c>
       <c r="F111" t="n">
-        <v>3.449693254850341</v>
+        <v>3.422862831835396</v>
       </c>
       <c r="G111" t="n">
-        <v>3.715951695602787</v>
+        <v>3.725544018390972</v>
       </c>
       <c r="H111" t="n">
-        <v>0.9396276723664576</v>
+        <v>0.8992945415794971</v>
       </c>
       <c r="I111" t="n">
-        <v>0.9652075554857067</v>
+        <v>0.8999491904844276</v>
       </c>
       <c r="J111" t="n">
-        <v>0.923417045201437</v>
+        <v>0.7577563043655118</v>
       </c>
       <c r="K111" t="n">
-        <v>0.8885601779274186</v>
+        <v>0.769626178997154</v>
       </c>
       <c r="L111" t="n">
-        <v>-0.4677286136268061</v>
+        <v>1.214287604857461</v>
       </c>
       <c r="M111" t="n">
-        <v>1.488071442124216</v>
+        <v>1.406364396437214</v>
       </c>
       <c r="N111" t="n">
-        <v>1.091270222023103</v>
+        <v>0.9778903919942947</v>
       </c>
       <c r="O111" t="n">
         <v>1</v>
@@ -8517,2429 +8521,2356 @@
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>1.00123504297487</v>
       </c>
       <c r="R111" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S111" t="n">
-        <v>0.6888254212557682</v>
+        <v>1.490840749307944</v>
       </c>
       <c r="T111" t="n">
-        <v>1.22494588083562</v>
+        <v>1.50472930102468</v>
       </c>
       <c r="U111" t="n">
-        <v>0.1270133769611202</v>
+        <v>0.06592609035373777</v>
       </c>
       <c r="V111" t="n">
-        <v>0.002674418540895177</v>
+        <v>0.130167125795917</v>
       </c>
       <c r="W111" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.08450704225352113</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SheathingPanels</t>
+          <t>Shotcrete</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8791106428021422</v>
+        <v>0.2061240257110084</v>
       </c>
       <c r="C112" t="n">
-        <v>0.9276204385819743</v>
+        <v>0.2088770449700179</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4381401936628306</v>
+        <v>0.2059043117074972</v>
       </c>
       <c r="E112" t="n">
-        <v>0.4736889633141357</v>
+        <v>0.2953234364491428</v>
       </c>
       <c r="F112" t="n">
-        <v>3.422862831835396</v>
+        <v>4.852066389845827</v>
       </c>
       <c r="G112" t="n">
-        <v>3.725544018390972</v>
+        <v>4.928685215250402</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8992945415794971</v>
+        <v>0.9946071392706413</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8999491904844276</v>
+        <v>0.9961483874264266</v>
       </c>
       <c r="J112" t="n">
-        <v>0.7577563043655118</v>
+        <v>0.9855533066567019</v>
       </c>
       <c r="K112" t="n">
-        <v>0.769626178997154</v>
+        <v>0.9830732894153505</v>
       </c>
       <c r="L112" t="n">
-        <v>1.214287604857461</v>
+        <v>0.341197960431295</v>
       </c>
       <c r="M112" t="n">
-        <v>1.406364396437214</v>
+        <v>0.5220493719608227</v>
       </c>
       <c r="N112" t="n">
-        <v>0.9778903919942947</v>
+        <v>1.001251398196377</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.00123504297487</v>
+        <v>1.00316410435467</v>
       </c>
       <c r="R112" t="n">
-        <v>71</v>
+        <v>1669</v>
       </c>
       <c r="S112" t="n">
-        <v>1.490840749307944</v>
+        <v>0.4656725122853836</v>
       </c>
       <c r="T112" t="n">
-        <v>1.50472930102468</v>
+        <v>0.5310968586525006</v>
       </c>
       <c r="U112" t="n">
-        <v>0.06592609035373777</v>
+        <v>0.004261886147028044</v>
       </c>
       <c r="V112" t="n">
-        <v>0.130167125795917</v>
+        <v>0.01219312958341807</v>
       </c>
       <c r="W112" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.01318154583582984</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Shotcrete</t>
+          <t>SinglePlyEPDM</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.2061240257110084</v>
+        <v>0.4358591106778351</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2088770449700179</v>
+        <v>0.3429269161616528</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2059043117074972</v>
+        <v>1.012411780363077</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2953234364491428</v>
+        <v>0.691677623209071</v>
       </c>
       <c r="F113" t="n">
-        <v>4.852066389845827</v>
+        <v>2.442855553318303</v>
       </c>
       <c r="G113" t="n">
-        <v>4.928685215250402</v>
+        <v>2.823416998397396</v>
       </c>
       <c r="H113" t="n">
-        <v>0.9946071392706413</v>
+        <v>0.9226673453469799</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9961483874264266</v>
+        <v>0.9430512033296627</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9855533066567019</v>
+        <v>0.8318027219855723</v>
       </c>
       <c r="K113" t="n">
-        <v>0.9830732894153505</v>
+        <v>0.8438402111619846</v>
       </c>
       <c r="L113" t="n">
-        <v>0.341197960431295</v>
+        <v>-0.2080023265869152</v>
       </c>
       <c r="M113" t="n">
-        <v>0.5220493719608227</v>
+        <v>3.621526818691267</v>
       </c>
       <c r="N113" t="n">
-        <v>1.001251398196377</v>
+        <v>1.199151078807034</v>
       </c>
       <c r="O113" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>1.007777424459459</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.00316410435467</v>
+        <v>1.022020897969908</v>
       </c>
       <c r="R113" t="n">
-        <v>1669</v>
+        <v>29</v>
       </c>
       <c r="S113" t="n">
-        <v>0.4656725122853836</v>
+        <v>1.02550517992069</v>
       </c>
       <c r="T113" t="n">
-        <v>0.5310968586525006</v>
+        <v>1.685904792682899</v>
       </c>
       <c r="U113" t="n">
-        <v>0.004261886147028044</v>
+        <v>0.2035956850033169</v>
       </c>
       <c r="V113" t="n">
-        <v>0.01219312958341807</v>
+        <v>0.1800080011824223</v>
       </c>
       <c r="W113" t="n">
-        <v>0.01318154583582984</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SinglePlyEPDM</t>
+          <t>SinglePlyKEE</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4358591106778351</v>
+        <v>0.2375175161157313</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3429269161616528</v>
+        <v>0.2268333749369714</v>
       </c>
       <c r="D114" t="n">
-        <v>1.012411780363077</v>
+        <v>0.4736158114785398</v>
       </c>
       <c r="E114" t="n">
-        <v>0.691677623209071</v>
+        <v>0.5456010963617324</v>
       </c>
       <c r="F114" t="n">
-        <v>2.442855553318303</v>
+        <v>1.961510770444917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.823416998397396</v>
+        <v>2.271868512696562</v>
       </c>
       <c r="H114" t="n">
-        <v>0.9226673453469799</v>
+        <v>0.9617146086840636</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9430512033296627</v>
+        <v>0.9442930210267295</v>
       </c>
       <c r="J114" t="n">
-        <v>0.8318027219855723</v>
+        <v>0.9455208862675365</v>
       </c>
       <c r="K114" t="n">
-        <v>0.8438402111619846</v>
+        <v>0.9477417689983973</v>
       </c>
       <c r="L114" t="n">
-        <v>-0.2080023265869152</v>
+        <v>-1.224529637038703</v>
       </c>
       <c r="M114" t="n">
-        <v>3.621526818691267</v>
+        <v>-1.092193674990339</v>
       </c>
       <c r="N114" t="n">
-        <v>1.199151078807034</v>
+        <v>1.014313252054271</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>1.007777424459459</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.022020897969908</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="S114" t="n">
-        <v>1.02550517992069</v>
+        <v>0.3461965781098211</v>
       </c>
       <c r="T114" t="n">
-        <v>1.685904792682899</v>
+        <v>0.1932887635188584</v>
       </c>
       <c r="U114" t="n">
-        <v>0.2035956850033169</v>
+        <v>0.0316613160507849</v>
       </c>
       <c r="V114" t="n">
-        <v>0.1800080011824223</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.03448275862068965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SinglePlyKEE</t>
+          <t>SinglePlyPVC</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.2375175161157313</v>
+        <v>0.5139083244130161</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2268333749369714</v>
+        <v>0.5697844926120312</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4736158114785398</v>
+        <v>1.577867706814175</v>
       </c>
       <c r="E115" t="n">
-        <v>0.5456010963617324</v>
+        <v>1.628114609785603</v>
       </c>
       <c r="F115" t="n">
-        <v>1.961510770444917</v>
+        <v>3.360328861672627</v>
       </c>
       <c r="G115" t="n">
-        <v>2.271868512696562</v>
+        <v>3.580155174195158</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9617146086840636</v>
+        <v>0.9307528474348624</v>
       </c>
       <c r="I115" t="n">
-        <v>0.9442930210267295</v>
+        <v>0.94268343126057</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9455208862675365</v>
+        <v>0.646043008293982</v>
       </c>
       <c r="K115" t="n">
-        <v>0.9477417689983973</v>
+        <v>0.6277805150881279</v>
       </c>
       <c r="L115" t="n">
-        <v>-1.224529637038703</v>
+        <v>35.68071805113103</v>
       </c>
       <c r="M115" t="n">
-        <v>-1.092193674990339</v>
+        <v>29.3671832390443</v>
       </c>
       <c r="N115" t="n">
-        <v>1.014313252054271</v>
+        <v>0.9599927591045546</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>1</v>
+        <v>1.013150226475954</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>1.021223614675844</v>
       </c>
       <c r="R115" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="S115" t="n">
-        <v>0.3461965781098211</v>
+        <v>4.700346506375285</v>
       </c>
       <c r="T115" t="n">
-        <v>0.1932887635188584</v>
+        <v>4.52945457277894</v>
       </c>
       <c r="U115" t="n">
-        <v>0.0316613160507849</v>
+        <v>0.04456402920810431</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>0.05896447331394603</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>0.04054054054054054</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SinglePlyPVC</t>
+          <t>SinglePlyPolyurethane</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5139083244130161</v>
+        <v>1.052655847663158</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5697844926120312</v>
+        <v>1.47993235799541</v>
       </c>
       <c r="D116" t="n">
-        <v>1.577867706814175</v>
+        <v>0.8178729393394245</v>
       </c>
       <c r="E116" t="n">
-        <v>1.628114609785603</v>
+        <v>0.945407429712929</v>
       </c>
       <c r="F116" t="n">
-        <v>3.360328861672627</v>
+        <v>2.014987073692391</v>
       </c>
       <c r="G116" t="n">
-        <v>3.580155174195158</v>
+        <v>2.4125524321158</v>
       </c>
       <c r="H116" t="n">
-        <v>0.9307528474348624</v>
+        <v>0.8871166200130614</v>
       </c>
       <c r="I116" t="n">
-        <v>0.94268343126057</v>
+        <v>0.912454605945104</v>
       </c>
       <c r="J116" t="n">
-        <v>0.646043008293982</v>
+        <v>0.7765846155466269</v>
       </c>
       <c r="K116" t="n">
-        <v>0.6277805150881279</v>
+        <v>0.6706855173315315</v>
       </c>
       <c r="L116" t="n">
-        <v>35.68071805113103</v>
+        <v>7.807711274457489</v>
       </c>
       <c r="M116" t="n">
-        <v>29.3671832390443</v>
+        <v>8.41012405520817</v>
       </c>
       <c r="N116" t="n">
-        <v>0.9599927591045546</v>
+        <v>0.8813126756598268</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>1.013150226475954</v>
+        <v>1.010963873907253</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.021223614675844</v>
+        <v>1.045290362191896</v>
       </c>
       <c r="R116" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="S116" t="n">
-        <v>4.700346506375285</v>
+        <v>1.739460911994443</v>
       </c>
       <c r="T116" t="n">
-        <v>4.52945457277894</v>
+        <v>2.586558181307767</v>
       </c>
       <c r="U116" t="n">
-        <v>0.04456402920810431</v>
+        <v>0.3059427237263445</v>
       </c>
       <c r="V116" t="n">
-        <v>0.05896447331394603</v>
+        <v>0.004575005067148818</v>
       </c>
       <c r="W116" t="n">
-        <v>0.04054054054054054</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SinglePlyPolyurethane</t>
+          <t>SinglePlyTPO</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1.052655847663158</v>
+        <v>0.2993369040417522</v>
       </c>
       <c r="C117" t="n">
-        <v>1.47993235799541</v>
+        <v>0.2894896863961585</v>
       </c>
       <c r="D117" t="n">
-        <v>0.8178729393394245</v>
+        <v>0.5243308716300528</v>
       </c>
       <c r="E117" t="n">
-        <v>0.945407429712929</v>
+        <v>0.3482466623663282</v>
       </c>
       <c r="F117" t="n">
-        <v>2.014987073692391</v>
+        <v>3.319222202643261</v>
       </c>
       <c r="G117" t="n">
-        <v>2.4125524321158</v>
+        <v>3.569549989986674</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8871166200130614</v>
+        <v>0.9496686631194888</v>
       </c>
       <c r="I117" t="n">
-        <v>0.912454605945104</v>
+        <v>0.9628177563247164</v>
       </c>
       <c r="J117" t="n">
-        <v>0.7765846155466269</v>
+        <v>0.9567995493782506</v>
       </c>
       <c r="K117" t="n">
-        <v>0.6706855173315315</v>
+        <v>0.970432080527098</v>
       </c>
       <c r="L117" t="n">
-        <v>7.807711274457489</v>
+        <v>-0.1785070810978135</v>
       </c>
       <c r="M117" t="n">
-        <v>8.41012405520817</v>
+        <v>-0.248085148375232</v>
       </c>
       <c r="N117" t="n">
-        <v>0.8813126756598268</v>
+        <v>1.028131826936511</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>1.010963873907253</v>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.045290362191896</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="S117" t="n">
-        <v>1.739460911994443</v>
+        <v>0.3600575355469509</v>
       </c>
       <c r="T117" t="n">
-        <v>2.586558181307767</v>
+        <v>0.3458057653557264</v>
       </c>
       <c r="U117" t="n">
-        <v>0.3059427237263445</v>
+        <v>0.03305879380724572</v>
       </c>
       <c r="V117" t="n">
-        <v>0.004575005067148818</v>
+        <v>0.07694031895308452</v>
       </c>
       <c r="W117" t="n">
-        <v>0.03703703703703703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SinglePlyTPO</t>
+          <t>SprayedInsulation</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2993369040417522</v>
+        <v>1.006886985595747</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2894896863961585</v>
+        <v>0.9697947138020934</v>
       </c>
       <c r="D118" t="n">
-        <v>0.5243308716300528</v>
+        <v>0.9482368714663055</v>
       </c>
       <c r="E118" t="n">
-        <v>0.3482466623663282</v>
+        <v>0.9664301163130178</v>
       </c>
       <c r="F118" t="n">
-        <v>3.319222202643261</v>
+        <v>1.832062777947439</v>
       </c>
       <c r="G118" t="n">
-        <v>3.569549989986674</v>
+        <v>2.397895272798384</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9496686631194888</v>
+        <v>0.8914574667257523</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9628177563247164</v>
+        <v>0.9069414764011795</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9567995493782506</v>
+        <v>0.6053408251649799</v>
       </c>
       <c r="K118" t="n">
-        <v>0.970432080527098</v>
+        <v>0.6129075333222098</v>
       </c>
       <c r="L118" t="n">
-        <v>-0.1785070810978135</v>
+        <v>11.98313305105714</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.248085148375232</v>
+        <v>8.799933580686853</v>
       </c>
       <c r="N118" t="n">
-        <v>1.028131826936511</v>
+        <v>0.8902717323966147</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
       </c>
       <c r="P118" t="n">
-        <v>1</v>
+        <v>1.043999769996914</v>
       </c>
       <c r="Q118" t="n">
-        <v>1</v>
+        <v>1.077946271588657</v>
       </c>
       <c r="R118" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="S118" t="n">
-        <v>0.3600575355469509</v>
+        <v>3.180278128527188</v>
       </c>
       <c r="T118" t="n">
-        <v>0.3458057653557264</v>
+        <v>2.846399436709792</v>
       </c>
       <c r="U118" t="n">
-        <v>0.03305879380724572</v>
+        <v>0.1224618968751506</v>
       </c>
       <c r="V118" t="n">
-        <v>0.07694031895308452</v>
+        <v>0.07152232190490906</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SprayedInsulation</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.006886985595747</v>
+        <v>1.381241648888869</v>
       </c>
       <c r="C119" t="n">
-        <v>0.9697947138020934</v>
+        <v>1.566929812464727</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9482368714663055</v>
+        <v>2.150199572809753</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9664301163130178</v>
+        <v>2.364227317204637</v>
       </c>
       <c r="F119" t="n">
-        <v>1.832062777947439</v>
+        <v>3.036874975264181</v>
       </c>
       <c r="G119" t="n">
-        <v>2.397895272798384</v>
+        <v>3.096306281467452</v>
       </c>
       <c r="H119" t="n">
-        <v>0.8914574667257523</v>
+        <v>0.9462607410924028</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9069414764011795</v>
+        <v>0.9355756648166935</v>
       </c>
       <c r="J119" t="n">
-        <v>0.6053408251649799</v>
+        <v>0.359820302942662</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6129075333222098</v>
+        <v>0.318347646258578</v>
       </c>
       <c r="L119" t="n">
-        <v>11.98313305105714</v>
+        <v>118.6372006035264</v>
       </c>
       <c r="M119" t="n">
-        <v>8.799933580686853</v>
+        <v>113.9173313309566</v>
       </c>
       <c r="N119" t="n">
-        <v>0.8902717323966147</v>
+        <v>0.9263682952918006</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P119" t="n">
-        <v>1.043999769996914</v>
+        <v>1.009362783182016</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.077946271588657</v>
+        <v>1.010966942575138</v>
       </c>
       <c r="R119" t="n">
-        <v>11</v>
+        <v>554</v>
       </c>
       <c r="S119" t="n">
-        <v>3.180278128527188</v>
+        <v>9.821989752526187</v>
       </c>
       <c r="T119" t="n">
-        <v>2.846399436709792</v>
+        <v>9.804880883772157</v>
       </c>
       <c r="U119" t="n">
-        <v>0.1224618968751506</v>
+        <v>0.08134939839932363</v>
       </c>
       <c r="V119" t="n">
-        <v>0.07152232190490906</v>
+        <v>0.02083499762848658</v>
       </c>
       <c r="W119" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.03249097472924188</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>SteelSuspensionAssembly</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.381241648888869</v>
+        <v>0.1607612154791172</v>
       </c>
       <c r="C120" t="n">
-        <v>1.566929812464727</v>
+        <v>0.1775169045851855</v>
       </c>
       <c r="D120" t="n">
-        <v>2.150199572809753</v>
+        <v>1.083885536277512</v>
       </c>
       <c r="E120" t="n">
-        <v>2.364227317204637</v>
+        <v>1.056416719107693</v>
       </c>
       <c r="F120" t="n">
-        <v>3.036874975264181</v>
+        <v>3.538738371017739</v>
       </c>
       <c r="G120" t="n">
-        <v>3.096306281467452</v>
+        <v>3.799116738187332</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9462607410924028</v>
+        <v>0.898945551679846</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9355756648166935</v>
+        <v>0.8890456976663696</v>
       </c>
       <c r="J120" t="n">
-        <v>0.359820302942662</v>
+        <v>0.7898639318757688</v>
       </c>
       <c r="K120" t="n">
-        <v>0.318347646258578</v>
+        <v>0.7802496254202818</v>
       </c>
       <c r="L120" t="n">
-        <v>118.6372006035264</v>
+        <v>12.38627472421985</v>
       </c>
       <c r="M120" t="n">
-        <v>113.9173313309566</v>
+        <v>10.27564432985529</v>
       </c>
       <c r="N120" t="n">
-        <v>0.9263682952918006</v>
+        <v>0.9885989775417648</v>
       </c>
       <c r="O120" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>1.009362783182016</v>
+        <v>1.025782251517174</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.010966942575138</v>
+        <v>1.034552392430763</v>
       </c>
       <c r="R120" t="n">
-        <v>554</v>
+        <v>99</v>
       </c>
       <c r="S120" t="n">
-        <v>9.821989752526187</v>
+        <v>2.66663841204372</v>
       </c>
       <c r="T120" t="n">
-        <v>9.804880883772157</v>
+        <v>2.60442718380626</v>
       </c>
       <c r="U120" t="n">
-        <v>0.08134939839932363</v>
+        <v>0.01320726398859391</v>
       </c>
       <c r="V120" t="n">
-        <v>0.02083499762848658</v>
+        <v>0.0201233152307345</v>
       </c>
       <c r="W120" t="n">
-        <v>0.03249097472924188</v>
+        <v>0.04040404040404041</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SteelSuspensionAssembly</t>
+          <t>StoneCladding</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1607612154791172</v>
+        <v>0.7778554304874405</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1775169045851855</v>
+        <v>0.9558796840416389</v>
       </c>
       <c r="D121" t="n">
-        <v>1.083885536277512</v>
+        <v>0.5742692839980315</v>
       </c>
       <c r="E121" t="n">
-        <v>1.056416719107693</v>
+        <v>0.6752562077596506</v>
       </c>
       <c r="F121" t="n">
-        <v>3.538738371017739</v>
+        <v>2.465504923424276</v>
       </c>
       <c r="G121" t="n">
-        <v>3.799116738187332</v>
+        <v>2.871476118054878</v>
       </c>
       <c r="H121" t="n">
-        <v>0.898945551679846</v>
+        <v>0.8902670687288543</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8890456976663696</v>
+        <v>0.9293250095388597</v>
       </c>
       <c r="J121" t="n">
-        <v>0.7898639318757688</v>
+        <v>0.9018427458553473</v>
       </c>
       <c r="K121" t="n">
-        <v>0.7802496254202818</v>
+        <v>0.8190954874447443</v>
       </c>
       <c r="L121" t="n">
-        <v>12.38627472421985</v>
+        <v>-1.103819071228612</v>
       </c>
       <c r="M121" t="n">
-        <v>10.27564432985529</v>
+        <v>-0.7438563083664108</v>
       </c>
       <c r="N121" t="n">
-        <v>0.9885989775417648</v>
+        <v>1.153601772760521</v>
       </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>1.025782251517174</v>
+        <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.034552392430763</v>
+        <v>1.045878182358265</v>
       </c>
       <c r="R121" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="S121" t="n">
-        <v>2.66663841204372</v>
+        <v>0.5513200988965944</v>
       </c>
       <c r="T121" t="n">
-        <v>2.60442718380626</v>
+        <v>0.9008376289479634</v>
       </c>
       <c r="U121" t="n">
-        <v>0.01320726398859391</v>
+        <v>0.1841703437718766</v>
       </c>
       <c r="V121" t="n">
-        <v>0.0201233152307345</v>
+        <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.04040404040404041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>StoneCladding</t>
+          <t>StorageFurniture</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7778554304874405</v>
+        <v>0.3482352089914686</v>
       </c>
       <c r="C122" t="n">
-        <v>0.9558796840416389</v>
+        <v>0.4654584517878537</v>
       </c>
       <c r="D122" t="n">
-        <v>0.5742692839980315</v>
+        <v>0.564548520134097</v>
       </c>
       <c r="E122" t="n">
-        <v>0.6752562077596506</v>
+        <v>0.7812530624112051</v>
       </c>
       <c r="F122" t="n">
-        <v>2.465504923424276</v>
+        <v>2.218838001837228</v>
       </c>
       <c r="G122" t="n">
-        <v>2.871476118054878</v>
+        <v>2.615630577027558</v>
       </c>
       <c r="H122" t="n">
-        <v>0.8902670687288543</v>
+        <v>0.9209915505378991</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9293250095388597</v>
+        <v>0.961507346072651</v>
       </c>
       <c r="J122" t="n">
-        <v>0.9018427458553473</v>
+        <v>0.916898270823452</v>
       </c>
       <c r="K122" t="n">
-        <v>0.8190954874447443</v>
+        <v>0.8159698579517914</v>
       </c>
       <c r="L122" t="n">
-        <v>-1.103819071228612</v>
+        <v>5.078547098091626</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.7438563083664108</v>
+        <v>5.163234974270583</v>
       </c>
       <c r="N122" t="n">
-        <v>1.153601772760521</v>
+        <v>0.9557832437667452</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>1</v>
+        <v>1.003212601165653</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.045878182358265</v>
+        <v>1.031584810111214</v>
       </c>
       <c r="R122" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="S122" t="n">
-        <v>0.5513200988965944</v>
+        <v>1.064748612743193</v>
       </c>
       <c r="T122" t="n">
-        <v>0.9008376289479634</v>
+        <v>1.983009311902034</v>
       </c>
       <c r="U122" t="n">
-        <v>0.1841703437718766</v>
+        <v>0.1010731619659722</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>0.1002792644248142</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>StorageFurniture</t>
+          <t>StructuralSteel</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.3482352089914686</v>
+        <v>1.761250226703174</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4654584517878537</v>
+        <v>1.346149012209193</v>
       </c>
       <c r="D123" t="n">
-        <v>0.564548520134097</v>
+        <v>2.629326880938862</v>
       </c>
       <c r="E123" t="n">
-        <v>0.7812530624112051</v>
+        <v>2.363041057153155</v>
       </c>
       <c r="F123" t="n">
-        <v>2.218838001837228</v>
+        <v>2.923011526212917</v>
       </c>
       <c r="G123" t="n">
-        <v>2.615630577027558</v>
+        <v>3.015652951195378</v>
       </c>
       <c r="H123" t="n">
-        <v>0.9209915505378991</v>
+        <v>0.8034890322440559</v>
       </c>
       <c r="I123" t="n">
-        <v>0.961507346072651</v>
+        <v>0.8505410303616352</v>
       </c>
       <c r="J123" t="n">
-        <v>0.916898270823452</v>
+        <v>0.2971568614357509</v>
       </c>
       <c r="K123" t="n">
-        <v>0.8159698579517914</v>
+        <v>0.2848634747074299</v>
       </c>
       <c r="L123" t="n">
-        <v>5.078547098091626</v>
+        <v>20.82504006237809</v>
       </c>
       <c r="M123" t="n">
-        <v>5.163234974270583</v>
+        <v>84.93769601858503</v>
       </c>
       <c r="N123" t="n">
-        <v>0.9557832437667452</v>
+        <v>1.445972993331096</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
       </c>
       <c r="P123" t="n">
-        <v>1.003212601165653</v>
+        <v>1.042334036528113</v>
       </c>
       <c r="Q123" t="n">
-        <v>1.031584810111214</v>
+        <v>1.012344740352193</v>
       </c>
       <c r="R123" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="S123" t="n">
-        <v>1.064748612743193</v>
+        <v>4.672572863377227</v>
       </c>
       <c r="T123" t="n">
-        <v>1.983009311902034</v>
+        <v>8.785365836662631</v>
       </c>
       <c r="U123" t="n">
-        <v>0.1010731619659722</v>
+        <v>0.4459729933310957</v>
       </c>
       <c r="V123" t="n">
-        <v>0.1002792644248142</v>
+        <v>0.03885763122781018</v>
       </c>
       <c r="W123" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.009708737864077669</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>StructuralSteel</t>
+          <t>SupplementaryCementitiousMaterials</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.761250226703174</v>
+        <v>0.5850765240017057</v>
       </c>
       <c r="C124" t="n">
-        <v>1.346149012209193</v>
+        <v>0.6785534637936887</v>
       </c>
       <c r="D124" t="n">
-        <v>2.629326880938862</v>
+        <v>0.4596360605148826</v>
       </c>
       <c r="E124" t="n">
-        <v>2.363041057153155</v>
+        <v>0.5403061702655045</v>
       </c>
       <c r="F124" t="n">
-        <v>2.923011526212917</v>
+        <v>2.894083367254022</v>
       </c>
       <c r="G124" t="n">
-        <v>3.015652951195378</v>
+        <v>3.13416245858666</v>
       </c>
       <c r="H124" t="n">
-        <v>0.8034890322440559</v>
+        <v>0.8198598691081508</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8505410303616352</v>
+        <v>0.8792057181561285</v>
       </c>
       <c r="J124" t="n">
-        <v>0.2971568614357509</v>
+        <v>0.9348060212576879</v>
       </c>
       <c r="K124" t="n">
-        <v>0.2848634747074299</v>
+        <v>0.9016795102115777</v>
       </c>
       <c r="L124" t="n">
-        <v>20.82504006237809</v>
+        <v>0.644274067629103</v>
       </c>
       <c r="M124" t="n">
-        <v>84.93769601858503</v>
+        <v>1.862545845364489</v>
       </c>
       <c r="N124" t="n">
-        <v>1.445972993331096</v>
+        <v>0.915197657366311</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
       </c>
       <c r="P124" t="n">
-        <v>1.042334036528113</v>
+        <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.012344740352193</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="S124" t="n">
-        <v>4.672572863377227</v>
+        <v>0.6952762095073944</v>
       </c>
       <c r="T124" t="n">
-        <v>8.785365836662631</v>
+        <v>1.259071096346934</v>
       </c>
       <c r="U124" t="n">
-        <v>0.4459729933310957</v>
+        <v>0.0974221713568257</v>
       </c>
       <c r="V124" t="n">
-        <v>0.03885763122781018</v>
+        <v>0.005488659894453104</v>
       </c>
       <c r="W124" t="n">
-        <v>0.009708737864077669</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SupplementaryCementitiousMaterials</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5850765240017057</v>
+        <v>1.40754481138985</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6785534637936887</v>
+        <v>1.422732913023462</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4596360605148826</v>
+        <v>1.484878107205031</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5403061702655045</v>
+        <v>1.552734347075567</v>
       </c>
       <c r="F125" t="n">
-        <v>2.894083367254022</v>
+        <v>3.084753430103623</v>
       </c>
       <c r="G125" t="n">
-        <v>3.13416245858666</v>
+        <v>3.326909091902428</v>
       </c>
       <c r="H125" t="n">
-        <v>0.8198598691081508</v>
+        <v>0.8915580580551598</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8792057181561285</v>
+        <v>0.8940085624857316</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9348060212576879</v>
+        <v>0.6832362286231244</v>
       </c>
       <c r="K125" t="n">
-        <v>0.9016795102115777</v>
+        <v>0.6767488200663816</v>
       </c>
       <c r="L125" t="n">
-        <v>0.644274067629103</v>
+        <v>23.20285075355689</v>
       </c>
       <c r="M125" t="n">
-        <v>1.862545845364489</v>
+        <v>19.41964680217087</v>
       </c>
       <c r="N125" t="n">
-        <v>0.915197657366311</v>
+        <v>0.809570709795656</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
       </c>
       <c r="P125" t="n">
-        <v>1</v>
+        <v>1.005243726951597</v>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>1.010052084659834</v>
       </c>
       <c r="R125" t="n">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="S125" t="n">
-        <v>0.6952762095073944</v>
+        <v>3.456624944671316</v>
       </c>
       <c r="T125" t="n">
-        <v>1.259071096346934</v>
+        <v>3.368519701550973</v>
       </c>
       <c r="U125" t="n">
-        <v>0.0974221713568257</v>
+        <v>0.1907074721795889</v>
       </c>
       <c r="V125" t="n">
-        <v>0.005488659894453104</v>
+        <v>0.04815173800946337</v>
       </c>
       <c r="W125" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.06211180124223602</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>ThermalMoistureProtection</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.40754481138985</v>
+        <v>0.8875404851516723</v>
       </c>
       <c r="C126" t="n">
-        <v>1.422732913023462</v>
+        <v>0.8253240274314084</v>
       </c>
       <c r="D126" t="n">
-        <v>1.484878107205031</v>
+        <v>0.9376364336787344</v>
       </c>
       <c r="E126" t="n">
-        <v>1.552734347075567</v>
+        <v>0.8294424098154558</v>
       </c>
       <c r="F126" t="n">
-        <v>3.084753430103623</v>
+        <v>1.189536047706182</v>
       </c>
       <c r="G126" t="n">
-        <v>3.326909091902428</v>
+        <v>1.386294361119899</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8915580580551598</v>
+        <v>0.8319446469147392</v>
       </c>
       <c r="I126" t="n">
-        <v>0.8940085624857316</v>
+        <v>0.8171922783769087</v>
       </c>
       <c r="J126" t="n">
-        <v>0.6832362286231244</v>
+        <v>0.8227693515122829</v>
       </c>
       <c r="K126" t="n">
-        <v>0.6767488200663816</v>
+        <v>0.8527462263722759</v>
       </c>
       <c r="L126" t="n">
-        <v>23.20285075355689</v>
+        <v>-5.166345192366014</v>
       </c>
       <c r="M126" t="n">
-        <v>19.41964680217087</v>
+        <v>-4.168587394141225</v>
       </c>
       <c r="N126" t="n">
-        <v>0.809570709795656</v>
+        <v>1.023872473009777</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
       </c>
       <c r="P126" t="n">
-        <v>1.005243726951597</v>
+        <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.010052084659834</v>
+        <v>1.007970957925331</v>
       </c>
       <c r="R126" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="S126" t="n">
-        <v>3.456624944671316</v>
+        <v>0.4314710448729124</v>
       </c>
       <c r="T126" t="n">
-        <v>3.368519701550973</v>
+        <v>0.3209332241114087</v>
       </c>
       <c r="U126" t="n">
-        <v>0.1907074721795889</v>
+        <v>0.1476411818658854</v>
       </c>
       <c r="V126" t="n">
-        <v>0.04815173800946337</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.06211180124223602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ThermalMoistureProtection</t>
+          <t>TileGrout</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.8875404851516723</v>
+        <v>1.310460382339101</v>
       </c>
       <c r="C127" t="n">
-        <v>0.8253240274314084</v>
+        <v>1.415695224759527</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9376364336787344</v>
+        <v>1.177187487658947</v>
       </c>
       <c r="E127" t="n">
-        <v>0.8294424098154558</v>
+        <v>1.272089670909019</v>
       </c>
       <c r="F127" t="n">
-        <v>1.189536047706182</v>
+        <v>2.966010294752452</v>
       </c>
       <c r="G127" t="n">
-        <v>1.386294361119899</v>
+        <v>3.200961690512133</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8319446469147392</v>
+        <v>0.9606060147057622</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8171922783769087</v>
+        <v>0.9452086398049784</v>
       </c>
       <c r="J127" t="n">
-        <v>0.8227693515122829</v>
+        <v>0.5296291252817421</v>
       </c>
       <c r="K127" t="n">
-        <v>0.8527462263722759</v>
+        <v>0.4942027505529892</v>
       </c>
       <c r="L127" t="n">
-        <v>-5.166345192366014</v>
+        <v>23.0586054696122</v>
       </c>
       <c r="M127" t="n">
-        <v>-4.168587394141225</v>
+        <v>21.00029393316604</v>
       </c>
       <c r="N127" t="n">
-        <v>1.023872473009777</v>
+        <v>0.9794089103831004</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P127" t="n">
-        <v>1</v>
+        <v>1.019779094781289</v>
       </c>
       <c r="Q127" t="n">
-        <v>1.007970957925331</v>
+        <v>1.028004806138072</v>
       </c>
       <c r="R127" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="S127" t="n">
-        <v>0.4314710448729124</v>
+        <v>4.301494336286658</v>
       </c>
       <c r="T127" t="n">
-        <v>0.3209332241114087</v>
+        <v>4.263071936016621</v>
       </c>
       <c r="U127" t="n">
-        <v>0.1476411818658854</v>
+        <v>0.07539327501076835</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>0.1089321650063793</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>0.1395348837209302</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TileGrout</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.310460382339101</v>
+        <v>0.7232811916098527</v>
       </c>
       <c r="C128" t="n">
-        <v>1.415695224759527</v>
+        <v>0.7157452272244843</v>
       </c>
       <c r="D128" t="n">
-        <v>1.177187487658947</v>
+        <v>0.6270307807416442</v>
       </c>
       <c r="E128" t="n">
-        <v>1.272089670909019</v>
+        <v>0.491830073949215</v>
       </c>
       <c r="F128" t="n">
-        <v>2.966010294752452</v>
+        <v>2.371362515213716</v>
       </c>
       <c r="G128" t="n">
-        <v>3.200961690512133</v>
+        <v>2.670119889806826</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9606060147057622</v>
+        <v>0.9682220641444185</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9452086398049784</v>
+        <v>0.9472277148076841</v>
       </c>
       <c r="J128" t="n">
-        <v>0.5296291252817421</v>
+        <v>0.8957644788216702</v>
       </c>
       <c r="K128" t="n">
-        <v>0.4942027505529892</v>
+        <v>0.8891830643148253</v>
       </c>
       <c r="L128" t="n">
-        <v>23.0586054696122</v>
+        <v>-0.5228737801711257</v>
       </c>
       <c r="M128" t="n">
-        <v>21.00029393316604</v>
+        <v>-0.6612808274714739</v>
       </c>
       <c r="N128" t="n">
-        <v>0.9794089103831004</v>
+        <v>1.02029800875323</v>
       </c>
       <c r="O128" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="P128" t="n">
-        <v>1.019779094781289</v>
+        <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.028004806138072</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="S128" t="n">
-        <v>4.301494336286658</v>
+        <v>0.8728583014274085</v>
       </c>
       <c r="T128" t="n">
-        <v>4.263071936016621</v>
+        <v>0.7762759986306239</v>
       </c>
       <c r="U128" t="n">
-        <v>0.07539327501076835</v>
+        <v>0.07785094710466912</v>
       </c>
       <c r="V128" t="n">
-        <v>0.1089321650063793</v>
+        <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>0.1395348837209302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>TranslucentWallAndRoofAssemblies</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.7232811916098527</v>
+        <v>1.245537054766756</v>
       </c>
       <c r="C129" t="n">
-        <v>0.7157452272244843</v>
+        <v>1.225950337725105</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6270307807416442</v>
+        <v>0.759664567368557</v>
       </c>
       <c r="E129" t="n">
-        <v>0.491830073949215</v>
+        <v>0.6943586052753362</v>
       </c>
       <c r="F129" t="n">
-        <v>2.371362515213716</v>
+        <v>3.266548717600072</v>
       </c>
       <c r="G129" t="n">
-        <v>2.670119889806826</v>
+        <v>3.425487595656</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9682220641444185</v>
+        <v>0.9576374152704024</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9472277148076841</v>
+        <v>0.9549088030554224</v>
       </c>
       <c r="J129" t="n">
-        <v>0.8957644788216702</v>
+        <v>0.6291891017625849</v>
       </c>
       <c r="K129" t="n">
-        <v>0.8891830643148253</v>
+        <v>0.681419677490616</v>
       </c>
       <c r="L129" t="n">
-        <v>-0.5228737801711257</v>
+        <v>6.09647201553334</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.6612808274714739</v>
+        <v>3.856817957815732</v>
       </c>
       <c r="N129" t="n">
-        <v>1.02029800875323</v>
+        <v>0.92889220482044</v>
       </c>
       <c r="O129" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="P129" t="n">
-        <v>1</v>
+        <v>1.021429504033348</v>
       </c>
       <c r="Q129" t="n">
-        <v>1</v>
+        <v>1.021736585612737</v>
       </c>
       <c r="R129" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="S129" t="n">
-        <v>0.8728583014274085</v>
+        <v>2.550063488248152</v>
       </c>
       <c r="T129" t="n">
-        <v>0.7762759986306239</v>
+        <v>2.138730143454938</v>
       </c>
       <c r="U129" t="n">
-        <v>0.07785094710466912</v>
+        <v>0.1067213274131488</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>0.1282198907768533</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TranslucentWallAndRoofAssemblies</t>
+          <t>UnitSkylights</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.245537054766756</v>
+        <v>0.6575556533639743</v>
       </c>
       <c r="C130" t="n">
-        <v>1.225950337725105</v>
+        <v>0.6372305118437162</v>
       </c>
       <c r="D130" t="n">
-        <v>0.759664567368557</v>
+        <v>0.6485524908118037</v>
       </c>
       <c r="E130" t="n">
-        <v>0.6943586052753362</v>
+        <v>0.55608713754734</v>
       </c>
       <c r="F130" t="n">
-        <v>3.266548717600072</v>
+        <v>2.515367042631386</v>
       </c>
       <c r="G130" t="n">
-        <v>3.425487595656</v>
+        <v>2.639340587232442</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9576374152704024</v>
+        <v>0.9208483665563526</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9549088030554224</v>
+        <v>0.9393172999575172</v>
       </c>
       <c r="J130" t="n">
-        <v>0.6291891017625849</v>
+        <v>0.9112207558086641</v>
       </c>
       <c r="K130" t="n">
-        <v>0.681419677490616</v>
+        <v>0.9022556790137422</v>
       </c>
       <c r="L130" t="n">
-        <v>6.09647201553334</v>
+        <v>-0.4165425314789139</v>
       </c>
       <c r="M130" t="n">
-        <v>3.856817957815732</v>
+        <v>0.5566068457998969</v>
       </c>
       <c r="N130" t="n">
-        <v>0.92889220482044</v>
+        <v>1.041897610320604</v>
       </c>
       <c r="O130" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P130" t="n">
-        <v>1.021429504033348</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>1.021736585612737</v>
+        <v>1</v>
       </c>
       <c r="R130" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="S130" t="n">
-        <v>2.550063488248152</v>
+        <v>0.6915859731887382</v>
       </c>
       <c r="T130" t="n">
-        <v>2.138730143454938</v>
+        <v>0.9785275424222478</v>
       </c>
       <c r="U130" t="n">
-        <v>0.1067213274131488</v>
+        <v>0.09613029841044696</v>
       </c>
       <c r="V130" t="n">
-        <v>0.1282198907768533</v>
+        <v>0.0298471967647992</v>
       </c>
       <c r="W130" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UnitSkylights</t>
+          <t>VinylSiding</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6575556533639743</v>
+        <v>1.272182588215972</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6372305118437162</v>
+        <v>1.384538461969029</v>
       </c>
       <c r="D131" t="n">
-        <v>0.6485524908118037</v>
+        <v>0.4857480314913799</v>
       </c>
       <c r="E131" t="n">
-        <v>0.55608713754734</v>
+        <v>0.6943472311202832</v>
       </c>
       <c r="F131" t="n">
-        <v>2.515367042631386</v>
+        <v>2.090806620967929</v>
       </c>
       <c r="G131" t="n">
-        <v>2.639340587232442</v>
+        <v>2.397895272798388</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9208483665563526</v>
+        <v>0.9720288126065325</v>
       </c>
       <c r="I131" t="n">
-        <v>0.9393172999575172</v>
+        <v>0.9799075377812185</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9112207558086641</v>
+        <v>0.6382700162309799</v>
       </c>
       <c r="K131" t="n">
-        <v>0.9022556790137422</v>
+        <v>0.6868774911084219</v>
       </c>
       <c r="L131" t="n">
-        <v>-0.4165425314789139</v>
+        <v>23.00421932769493</v>
       </c>
       <c r="M131" t="n">
-        <v>0.5566068457998969</v>
+        <v>4.389694439131625</v>
       </c>
       <c r="N131" t="n">
-        <v>1.041897610320604</v>
+        <v>0.5511671176368158</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P131" t="n">
-        <v>1</v>
+        <v>1.015155867651729</v>
       </c>
       <c r="Q131" t="n">
-        <v>1</v>
+        <v>1.003816909802737</v>
       </c>
       <c r="R131" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S131" t="n">
-        <v>0.6915859731887382</v>
+        <v>3.849436291510053</v>
       </c>
       <c r="T131" t="n">
-        <v>0.9785275424222478</v>
+        <v>2.1481102322363</v>
       </c>
       <c r="U131" t="n">
-        <v>0.09613029841044696</v>
+        <v>0.4552356302167588</v>
       </c>
       <c r="V131" t="n">
-        <v>0.0298471967647992</v>
+        <v>0.05704518364057862</v>
       </c>
       <c r="W131" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VinylSiding</t>
+          <t>WallBase</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.272182588215972</v>
+        <v>0.4595522319585266</v>
       </c>
       <c r="C132" t="n">
-        <v>1.384538461969029</v>
+        <v>0.3570025496450679</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4857480314913799</v>
+        <v>0.6136782049633925</v>
       </c>
       <c r="E132" t="n">
-        <v>0.6943472311202832</v>
+        <v>0.5065159058766877</v>
       </c>
       <c r="F132" t="n">
-        <v>2.090806620967929</v>
+        <v>2.019269425874043</v>
       </c>
       <c r="G132" t="n">
-        <v>2.397895272798388</v>
+        <v>2.441015278026709</v>
       </c>
       <c r="H132" t="n">
-        <v>0.9720288126065325</v>
+        <v>0.9681139100160299</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9799075377812185</v>
+        <v>0.9662404692278658</v>
       </c>
       <c r="J132" t="n">
-        <v>0.6382700162309799</v>
+        <v>0.9269262931830053</v>
       </c>
       <c r="K132" t="n">
-        <v>0.6868774911084219</v>
+        <v>0.9412145242170876</v>
       </c>
       <c r="L132" t="n">
-        <v>23.00421932769493</v>
+        <v>0.2478778917058951</v>
       </c>
       <c r="M132" t="n">
-        <v>4.389694439131625</v>
+        <v>-0.1152558145303462</v>
       </c>
       <c r="N132" t="n">
-        <v>0.5511671176368158</v>
+        <v>0.8516393997769891</v>
       </c>
       <c r="O132" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>1.015155867651729</v>
+        <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.003816909802737</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S132" t="n">
-        <v>3.849436291510053</v>
+        <v>0.9567116660103139</v>
       </c>
       <c r="T132" t="n">
-        <v>2.1481102322363</v>
+        <v>0.5686335102790787</v>
       </c>
       <c r="U132" t="n">
-        <v>0.4552356302167588</v>
+        <v>0.1483606002230113</v>
       </c>
       <c r="V132" t="n">
-        <v>0.05704518364057862</v>
+        <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>WallBase</t>
+          <t>WallFinishes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4595522319585266</v>
+        <v>2.199285093667711</v>
       </c>
       <c r="C133" t="n">
-        <v>0.3570025496450679</v>
+        <v>2.475181738741</v>
       </c>
       <c r="D133" t="n">
-        <v>0.6136782049633925</v>
+        <v>2.338522255073253</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5065159058766877</v>
+        <v>2.525579322254112</v>
       </c>
       <c r="F133" t="n">
-        <v>2.019269425874043</v>
+        <v>2.611287702135423</v>
       </c>
       <c r="G133" t="n">
-        <v>2.441015278026709</v>
+        <v>2.703165945311127</v>
       </c>
       <c r="H133" t="n">
-        <v>0.9681139100160299</v>
+        <v>0.9844274126410508</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9662404692278658</v>
+        <v>0.9809802278442254</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9269262931830053</v>
+        <v>0.4237422910337682</v>
       </c>
       <c r="K133" t="n">
-        <v>0.9412145242170876</v>
+        <v>0.3345254896314322</v>
       </c>
       <c r="L133" t="n">
-        <v>0.2478778917058951</v>
+        <v>58.17265674559997</v>
       </c>
       <c r="M133" t="n">
-        <v>-0.1152558145303462</v>
+        <v>87.2069190746648</v>
       </c>
       <c r="N133" t="n">
-        <v>0.8516393997769891</v>
+        <v>1.120022675176394</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>1.020413391949968</v>
       </c>
       <c r="Q133" t="n">
-        <v>1</v>
+        <v>1.010492619786958</v>
       </c>
       <c r="R133" t="n">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="S133" t="n">
-        <v>0.9567116660103139</v>
+        <v>6.223904940906609</v>
       </c>
       <c r="T133" t="n">
-        <v>0.5686335102790787</v>
+        <v>8.363448947307949</v>
       </c>
       <c r="U133" t="n">
-        <v>0.1483606002230113</v>
+        <v>0.2573313695009826</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>0.1164493340973879</v>
       </c>
       <c r="W133" t="n">
-        <v>0</v>
+        <v>0.08092485549132947</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>WallFinishes</t>
+          <t>WallPanels</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2.199285093667711</v>
+        <v>1.034221944058446</v>
       </c>
       <c r="C134" t="n">
-        <v>2.475181738741</v>
+        <v>1.010689229240488</v>
       </c>
       <c r="D134" t="n">
-        <v>2.338522255073253</v>
+        <v>1.251629894500565</v>
       </c>
       <c r="E134" t="n">
-        <v>2.525579322254112</v>
+        <v>0.9260735457240363</v>
       </c>
       <c r="F134" t="n">
-        <v>2.611287702135423</v>
+        <v>3.893230966461578</v>
       </c>
       <c r="G134" t="n">
-        <v>2.703165945311127</v>
+        <v>4.06369833187158</v>
       </c>
       <c r="H134" t="n">
-        <v>0.9844274126410508</v>
+        <v>0.9881674008309478</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9809802278442254</v>
+        <v>0.9856935628953374</v>
       </c>
       <c r="J134" t="n">
-        <v>0.4237422910337682</v>
+        <v>0.6774120471869016</v>
       </c>
       <c r="K134" t="n">
-        <v>0.3345254896314322</v>
+        <v>0.6870348852696693</v>
       </c>
       <c r="L134" t="n">
-        <v>58.17265674559997</v>
+        <v>11.51200395612495</v>
       </c>
       <c r="M134" t="n">
-        <v>87.2069190746648</v>
+        <v>13.91572769955165</v>
       </c>
       <c r="N134" t="n">
-        <v>1.120022675176394</v>
+        <v>1.123946527843807</v>
       </c>
       <c r="O134" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>1.020413391949968</v>
+        <v>1.032575533870016</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.010492619786958</v>
+        <v>1.033932292630582</v>
       </c>
       <c r="R134" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="S134" t="n">
-        <v>6.223904940906609</v>
+        <v>3.021101980483781</v>
       </c>
       <c r="T134" t="n">
-        <v>8.363448947307949</v>
+        <v>3.223048032724432</v>
       </c>
       <c r="U134" t="n">
-        <v>0.2573313695009826</v>
+        <v>0.1255466710745843</v>
       </c>
       <c r="V134" t="n">
-        <v>0.1164493340973879</v>
+        <v>0.06117989852082235</v>
       </c>
       <c r="W134" t="n">
-        <v>0.08092485549132947</v>
+        <v>0.0736196319018405</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>WallPanels</t>
+          <t>WeatherBarriers</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.034221944058446</v>
+        <v>1.568007141874413</v>
       </c>
       <c r="C135" t="n">
-        <v>1.010689229240488</v>
+        <v>1.450182609277627</v>
       </c>
       <c r="D135" t="n">
-        <v>1.251629894500565</v>
+        <v>1.361223178550987</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9260735457240363</v>
+        <v>1.203850632559995</v>
       </c>
       <c r="F135" t="n">
-        <v>3.893230966461578</v>
+        <v>3.106428276517223</v>
       </c>
       <c r="G135" t="n">
-        <v>4.06369833187158</v>
+        <v>3.301964344103027</v>
       </c>
       <c r="H135" t="n">
-        <v>0.9881674008309478</v>
+        <v>0.8808236646950579</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9856935628953374</v>
+        <v>0.9252327779453707</v>
       </c>
       <c r="J135" t="n">
-        <v>0.6774120471869016</v>
+        <v>0.4720476949310664</v>
       </c>
       <c r="K135" t="n">
-        <v>0.6870348852696693</v>
+        <v>0.4928442127330489</v>
       </c>
       <c r="L135" t="n">
-        <v>11.51200395612495</v>
+        <v>9.058462764842714</v>
       </c>
       <c r="M135" t="n">
-        <v>13.91572769955165</v>
+        <v>16.43944359051128</v>
       </c>
       <c r="N135" t="n">
-        <v>1.123946527843807</v>
+        <v>1.188063992724911</v>
       </c>
       <c r="O135" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P135" t="n">
-        <v>1.032575533870016</v>
+        <v>1.066958734048004</v>
       </c>
       <c r="Q135" t="n">
-        <v>1.033932292630582</v>
+        <v>1.037569978740648</v>
       </c>
       <c r="R135" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="S135" t="n">
-        <v>3.021101980483781</v>
+        <v>3.156829667099132</v>
       </c>
       <c r="T135" t="n">
-        <v>3.223048032724432</v>
+        <v>3.922462462830909</v>
       </c>
       <c r="U135" t="n">
-        <v>0.1255466710745843</v>
+        <v>0.1989045080603218</v>
       </c>
       <c r="V135" t="n">
-        <v>0.06117989852082235</v>
+        <v>0.09603208430333636</v>
       </c>
       <c r="W135" t="n">
-        <v>0.0736196319018405</v>
+        <v>0.0847457627118644</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>WeatherBarriers</t>
+          <t>WindTurbines</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.568007141874413</v>
+        <v>0.3989257195156556</v>
       </c>
       <c r="C136" t="n">
-        <v>1.450182609277627</v>
+        <v>0.4153789910288454</v>
       </c>
       <c r="D136" t="n">
-        <v>1.361223178550987</v>
+        <v>0.822334180669847</v>
       </c>
       <c r="E136" t="n">
-        <v>1.203850632559995</v>
+        <v>0.7190962020828512</v>
       </c>
       <c r="F136" t="n">
-        <v>3.106428276517223</v>
+        <v>1.084223711727008</v>
       </c>
       <c r="G136" t="n">
-        <v>3.301964344103027</v>
+        <v>1.098612288668114</v>
       </c>
       <c r="H136" t="n">
-        <v>0.8808236646950579</v>
+        <v>0.9996282146198306</v>
       </c>
       <c r="I136" t="n">
-        <v>0.9252327779453707</v>
+        <v>0.9981966088328774</v>
       </c>
       <c r="J136" t="n">
-        <v>0.4720476949310664</v>
+        <v>0.9771598841771193</v>
       </c>
       <c r="K136" t="n">
-        <v>0.4928442127330489</v>
-      </c>
-      <c r="L136" t="n">
-        <v>9.058462764842714</v>
-      </c>
-      <c r="M136" t="n">
-        <v>16.43944359051128</v>
-      </c>
+        <v>0.966668504417591</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
-        <v>1.188063992724911</v>
+        <v>1.069962835861313</v>
       </c>
       <c r="O136" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
-        <v>1.066958734048004</v>
+        <v>1</v>
       </c>
       <c r="Q136" t="n">
-        <v>1.037569978740648</v>
+        <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="S136" t="n">
-        <v>3.156829667099132</v>
+        <v>0.190516492494381</v>
       </c>
       <c r="T136" t="n">
-        <v>3.922462462830909</v>
+        <v>0.9064969307395134</v>
       </c>
       <c r="U136" t="n">
-        <v>0.1989045080603218</v>
+        <v>0.0699628358613127</v>
       </c>
       <c r="V136" t="n">
-        <v>0.09603208430333636</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>0.0847457627118644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>WindTurbines</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.3989257195156556</v>
+        <v>0.9837663146858279</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4153789910288454</v>
+        <v>0.9470498289022686</v>
       </c>
       <c r="D137" t="n">
-        <v>0.822334180669847</v>
+        <v>0.9185567161942861</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7190962020828512</v>
+        <v>0.7414686595908531</v>
       </c>
       <c r="F137" t="n">
-        <v>1.084223711727008</v>
+        <v>3.879639213605753</v>
       </c>
       <c r="G137" t="n">
-        <v>1.098612288668114</v>
+        <v>3.994912591847233</v>
       </c>
       <c r="H137" t="n">
-        <v>0.9996282146198306</v>
+        <v>0.8976603124129124</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9981966088328774</v>
+        <v>0.9058813516735246</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9771598841771193</v>
+        <v>0.628474710843386</v>
       </c>
       <c r="K137" t="n">
-        <v>0.966668504417591</v>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
+        <v>0.6544545514974429</v>
+      </c>
+      <c r="L137" t="n">
+        <v>19.87096425476178</v>
+      </c>
+      <c r="M137" t="n">
+        <v>19.2192015804776</v>
+      </c>
       <c r="N137" t="n">
-        <v>1.069962835861313</v>
+        <v>0.9655063077976336</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P137" t="n">
-        <v>1</v>
+        <v>1.017727904411585</v>
       </c>
       <c r="Q137" t="n">
-        <v>1</v>
+        <v>1.012312089381855</v>
       </c>
       <c r="R137" t="n">
-        <v>3</v>
+        <v>358</v>
       </c>
       <c r="S137" t="n">
-        <v>0.190516492494381</v>
+        <v>3.878523692484617</v>
       </c>
       <c r="T137" t="n">
-        <v>0.9064969307395134</v>
+        <v>3.734577612306516</v>
       </c>
       <c r="U137" t="n">
-        <v>0.0699628358613127</v>
+        <v>0.04622617007454531</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>0.05470677793314647</v>
       </c>
       <c r="W137" t="n">
-        <v>0</v>
+        <v>0.05586592178770949</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>WireMeshSteel</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.9837663146858279</v>
+        <v>0.7490184834473188</v>
       </c>
       <c r="C138" t="n">
-        <v>0.9470498289022686</v>
+        <v>0.9281123703275191</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9185567161942861</v>
+        <v>0.5735094355854033</v>
       </c>
       <c r="E138" t="n">
-        <v>0.7414686595908531</v>
+        <v>0.6384995828501319</v>
       </c>
       <c r="F138" t="n">
-        <v>3.879639213605753</v>
+        <v>3.129030984481892</v>
       </c>
       <c r="G138" t="n">
-        <v>3.994912591847233</v>
+        <v>3.474962360214349</v>
       </c>
       <c r="H138" t="n">
-        <v>0.8976603124129124</v>
+        <v>0.9643001620431965</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9058813516735246</v>
+        <v>0.9821929129457144</v>
       </c>
       <c r="J138" t="n">
-        <v>0.628474710843386</v>
+        <v>0.8243188167737956</v>
       </c>
       <c r="K138" t="n">
-        <v>0.6544545514974429</v>
+        <v>0.7204815130384645</v>
       </c>
       <c r="L138" t="n">
-        <v>19.87096425476178</v>
+        <v>5.227208621196781</v>
       </c>
       <c r="M138" t="n">
-        <v>19.2192015804776</v>
+        <v>7.628868477339268</v>
       </c>
       <c r="N138" t="n">
-        <v>0.9655063077976336</v>
+        <v>1.05962759769533</v>
       </c>
       <c r="O138" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P138" t="n">
-        <v>1.017727904411585</v>
+        <v>1.00557437476491</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.012312089381855</v>
+        <v>1.037900570163677</v>
       </c>
       <c r="R138" t="n">
-        <v>358</v>
+        <v>53</v>
       </c>
       <c r="S138" t="n">
-        <v>3.878523692484617</v>
+        <v>1.899414364315825</v>
       </c>
       <c r="T138" t="n">
-        <v>3.734577612306516</v>
+        <v>2.545524398306053</v>
       </c>
       <c r="U138" t="n">
-        <v>0.04622617007454531</v>
+        <v>0.1487209151004562</v>
       </c>
       <c r="V138" t="n">
-        <v>0.05470677793314647</v>
+        <v>0.06662691262845767</v>
       </c>
       <c r="W138" t="n">
-        <v>0.05586592178770949</v>
+        <v>0.07547169811320754</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WireMeshSteel</t>
+          <t>WoodDoors</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.7490184834473188</v>
+        <v>0.7619135220461626</v>
       </c>
       <c r="C139" t="n">
-        <v>0.9281123703275191</v>
+        <v>0.7851614306847334</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5735094355854033</v>
+        <v>0.5398249230900236</v>
       </c>
       <c r="E139" t="n">
-        <v>0.6384995828501319</v>
+        <v>0.5347831307565294</v>
       </c>
       <c r="F139" t="n">
-        <v>3.129030984481892</v>
+        <v>2.904149912297454</v>
       </c>
       <c r="G139" t="n">
-        <v>3.474962360214349</v>
+        <v>3.14613250681212</v>
       </c>
       <c r="H139" t="n">
-        <v>0.9643001620431965</v>
+        <v>0.8624887507882475</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9821929129457144</v>
+        <v>0.88727920197009</v>
       </c>
       <c r="J139" t="n">
-        <v>0.8243188167737956</v>
+        <v>0.8322231756648512</v>
       </c>
       <c r="K139" t="n">
-        <v>0.7204815130384645</v>
+        <v>0.8345202118701367</v>
       </c>
       <c r="L139" t="n">
-        <v>5.227208621196781</v>
+        <v>2.477569487998396</v>
       </c>
       <c r="M139" t="n">
-        <v>7.628868477339268</v>
+        <v>1.145034504994338</v>
       </c>
       <c r="N139" t="n">
-        <v>1.05962759769533</v>
+        <v>0.8505071509555647</v>
       </c>
       <c r="O139" t="n">
         <v>1</v>
       </c>
       <c r="P139" t="n">
-        <v>1.00557437476491</v>
+        <v>1.012782755456062</v>
       </c>
       <c r="Q139" t="n">
-        <v>1.037900570163677</v>
+        <v>1.000278931611801</v>
       </c>
       <c r="R139" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="S139" t="n">
-        <v>1.899414364315825</v>
+        <v>1.576269932998556</v>
       </c>
       <c r="T139" t="n">
-        <v>2.545524398306053</v>
+        <v>1.363434763597087</v>
       </c>
       <c r="U139" t="n">
-        <v>0.1487209151004562</v>
+        <v>0.1495797502656855</v>
       </c>
       <c r="V139" t="n">
-        <v>0.06662691262845767</v>
+        <v>0.1283725245153101</v>
       </c>
       <c r="W139" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WoodDoors</t>
+          <t>WoodFlooring</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.7619135220461626</v>
+        <v>0.7272922710971119</v>
       </c>
       <c r="C140" t="n">
-        <v>0.7851614306847334</v>
+        <v>0.7629643150502472</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5398249230900236</v>
+        <v>0.4697831747716281</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5347831307565294</v>
+        <v>0.4373213263147568</v>
       </c>
       <c r="F140" t="n">
-        <v>2.904149912297454</v>
+        <v>3.271879938406655</v>
       </c>
       <c r="G140" t="n">
-        <v>3.14613250681212</v>
+        <v>3.517271447240406</v>
       </c>
       <c r="H140" t="n">
-        <v>0.8624887507882475</v>
+        <v>0.8897426380015548</v>
       </c>
       <c r="I140" t="n">
-        <v>0.88727920197009</v>
+        <v>0.898500164593806</v>
       </c>
       <c r="J140" t="n">
-        <v>0.8322231756648512</v>
+        <v>0.898153998545116</v>
       </c>
       <c r="K140" t="n">
-        <v>0.8345202118701367</v>
+        <v>0.8865250577638243</v>
       </c>
       <c r="L140" t="n">
-        <v>2.477569487998396</v>
+        <v>-0.1945256725278302</v>
       </c>
       <c r="M140" t="n">
-        <v>1.145034504994338</v>
+        <v>0.4082871668264633</v>
       </c>
       <c r="N140" t="n">
-        <v>0.8505071509555647</v>
+        <v>1.03770068470998</v>
       </c>
       <c r="O140" t="n">
         <v>1</v>
       </c>
       <c r="P140" t="n">
-        <v>1.012782755456062</v>
+        <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.000278931611801</v>
+        <v>1.000144120413532</v>
       </c>
       <c r="R140" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="S140" t="n">
-        <v>1.576269932998556</v>
+        <v>0.8601329234915431</v>
       </c>
       <c r="T140" t="n">
-        <v>1.363434763597087</v>
+        <v>1.039274492787589</v>
       </c>
       <c r="U140" t="n">
-        <v>0.1495797502656855</v>
+        <v>0.06422663949696464</v>
       </c>
       <c r="V140" t="n">
-        <v>0.1283725245153101</v>
+        <v>0.001505695639488217</v>
       </c>
       <c r="W140" t="n">
-        <v>0.09375</v>
+        <v>0.08139534883720931</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WoodFlooring</t>
+          <t>WoodFraming</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.7272922710971119</v>
+        <v>0.4845021405176518</v>
       </c>
       <c r="C141" t="n">
-        <v>0.7629643150502472</v>
+        <v>0.5500719124716609</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4697831747716281</v>
+        <v>0.5668988138145282</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4373213263147568</v>
+        <v>0.7258724228388833</v>
       </c>
       <c r="F141" t="n">
-        <v>3.271879938406655</v>
+        <v>1.602755957940582</v>
       </c>
       <c r="G141" t="n">
-        <v>3.517271447240406</v>
+        <v>1.945910149055321</v>
       </c>
       <c r="H141" t="n">
-        <v>0.8897426380015548</v>
+        <v>0.8457985588734399</v>
       </c>
       <c r="I141" t="n">
-        <v>0.898500164593806</v>
+        <v>0.9330783948343561</v>
       </c>
       <c r="J141" t="n">
-        <v>0.898153998545116</v>
+        <v>0.8875395705508148</v>
       </c>
       <c r="K141" t="n">
-        <v>0.8865250577638243</v>
+        <v>0.8565311507370187</v>
       </c>
       <c r="L141" t="n">
-        <v>-0.1945256725278302</v>
+        <v>8.21800057730905</v>
       </c>
       <c r="M141" t="n">
-        <v>0.4082871668264633</v>
+        <v>3.279366218317636</v>
       </c>
       <c r="N141" t="n">
-        <v>1.03770068470998</v>
+        <v>0.7574387372228915</v>
       </c>
       <c r="O141" t="n">
         <v>1</v>
       </c>
       <c r="P141" t="n">
-        <v>1</v>
+        <v>1.002586608618625</v>
       </c>
       <c r="Q141" t="n">
-        <v>1.000144120413532</v>
+        <v>1.000893303299127</v>
       </c>
       <c r="R141" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="S141" t="n">
-        <v>0.8601329234915431</v>
+        <v>1.046584952875219</v>
       </c>
       <c r="T141" t="n">
-        <v>1.039274492787589</v>
+        <v>1.506255263709312</v>
       </c>
       <c r="U141" t="n">
-        <v>0.06422663949696464</v>
+        <v>0.2444793042576891</v>
       </c>
       <c r="V141" t="n">
-        <v>0.001505695639488217</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0.08139534883720931</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WoodFraming</t>
+          <t>WoodJoists</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4845021405176518</v>
+        <v>0.4204852656376782</v>
       </c>
       <c r="C142" t="n">
-        <v>0.5500719124716609</v>
+        <v>0.4718213786193156</v>
       </c>
       <c r="D142" t="n">
-        <v>0.5668988138145282</v>
+        <v>0.5724381055187128</v>
       </c>
       <c r="E142" t="n">
-        <v>0.7258724228388833</v>
+        <v>0.6312889582991137</v>
       </c>
       <c r="F142" t="n">
-        <v>1.602755957940582</v>
+        <v>1.208565652520271</v>
       </c>
       <c r="G142" t="n">
-        <v>1.945910149055321</v>
+        <v>1.332179040210127</v>
       </c>
       <c r="H142" t="n">
-        <v>0.8457985588734399</v>
+        <v>0.9396581500159067</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9330783948343561</v>
+        <v>0.7946017684845508</v>
       </c>
       <c r="J142" t="n">
-        <v>0.8875395705508148</v>
+        <v>0.9372025573840849</v>
       </c>
       <c r="K142" t="n">
-        <v>0.8565311507370187</v>
+        <v>0.7794993846516854</v>
       </c>
       <c r="L142" t="n">
-        <v>8.21800057730905</v>
+        <v>-1.17828373499126</v>
       </c>
       <c r="M142" t="n">
-        <v>3.279366218317636</v>
+        <v>0.8355693823115756</v>
       </c>
       <c r="N142" t="n">
-        <v>0.7574387372228915</v>
+        <v>1.129751680504357</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P142" t="n">
-        <v>1.002586608618625</v>
+        <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>1.000893303299127</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S142" t="n">
-        <v>1.046584952875219</v>
+        <v>0.5927797837953724</v>
       </c>
       <c r="T142" t="n">
-        <v>1.506255263709312</v>
+        <v>1.354300096597658</v>
       </c>
       <c r="U142" t="n">
-        <v>0.2444793042576891</v>
+        <v>0.1298758075264771</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>WoodJoists</t>
+          <t>WorkSurfaces</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4204852656376782</v>
+        <v>0.3367819149821296</v>
       </c>
       <c r="C143" t="n">
-        <v>0.4718213786193156</v>
+        <v>0.4741989368897199</v>
       </c>
       <c r="D143" t="n">
-        <v>0.5724381055187128</v>
+        <v>0.5859529952200963</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6312889582991137</v>
+        <v>0.7892017609315067</v>
       </c>
       <c r="F143" t="n">
-        <v>1.208565652520271</v>
+        <v>2.196061456341202</v>
       </c>
       <c r="G143" t="n">
-        <v>1.332179040210127</v>
+        <v>2.484906649788008</v>
       </c>
       <c r="H143" t="n">
-        <v>0.9396581500159067</v>
+        <v>0.8062726345199401</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7946017684845508</v>
+        <v>0.931095573596477</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9372025573840849</v>
+        <v>0.9170056577822541</v>
       </c>
       <c r="K143" t="n">
-        <v>0.7794993846516854</v>
+        <v>0.8502937991478721</v>
       </c>
       <c r="L143" t="n">
-        <v>-1.17828373499126</v>
+        <v>3.033899820285974</v>
       </c>
       <c r="M143" t="n">
-        <v>0.8355693823115756</v>
+        <v>4.478796333399863</v>
       </c>
       <c r="N143" t="n">
-        <v>1.129751680504357</v>
+        <v>0.9072432565893767</v>
       </c>
       <c r="O143" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>1</v>
+        <v>1.004835435131385</v>
       </c>
       <c r="Q143" t="n">
-        <v>1</v>
+        <v>1.04137986588416</v>
       </c>
       <c r="R143" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S143" t="n">
-        <v>0.5927797837953724</v>
+        <v>-0.256052564058103</v>
       </c>
       <c r="T143" t="n">
-        <v>1.354300096597658</v>
+        <v>1.650346730904077</v>
       </c>
       <c r="U143" t="n">
-        <v>0.1298758075264771</v>
+        <v>0.1194784357290234</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>0.004962090400331437</v>
       </c>
       <c r="W143" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>WorkSurfaces</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0.3367819149821296</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0.4741989368897199</v>
-      </c>
-      <c r="D144" t="n">
-        <v>0.5859529952200963</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.7892017609315067</v>
-      </c>
-      <c r="F144" t="n">
-        <v>2.196061456341202</v>
-      </c>
-      <c r="G144" t="n">
-        <v>2.484906649788008</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.8062726345199401</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.931095573596477</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0.9170056577822541</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0.8502937991478721</v>
-      </c>
-      <c r="L144" t="n">
-        <v>3.033899820285974</v>
-      </c>
-      <c r="M144" t="n">
-        <v>4.478796333399863</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0.9072432565893767</v>
-      </c>
-      <c r="O144" t="n">
-        <v>1</v>
-      </c>
-      <c r="P144" t="n">
-        <v>1.004835435131385</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>1.04137986588416</v>
-      </c>
-      <c r="R144" t="n">
-        <v>12</v>
-      </c>
-      <c r="S144" t="n">
-        <v>-0.256052564058103</v>
-      </c>
-      <c r="T144" t="n">
-        <v>1.650346730904077</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0.1194784357290234</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0.004962090400331437</v>
-      </c>
-      <c r="W144" t="n">
         <v>0.08333333333333333</v>
       </c>
     </row>

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -754,70 +754,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.34073636572407</v>
+        <v>7.107461973628843</v>
       </c>
       <c r="C5" t="n">
-        <v>13.60095675444667</v>
+        <v>6.424245552319687</v>
       </c>
       <c r="D5" t="n">
-        <v>4.171017698886292</v>
+        <v>3.958660834633497</v>
       </c>
       <c r="E5" t="n">
-        <v>4.366959600325371</v>
+        <v>3.7717960864095</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1970744491073821</v>
+        <v>1.173641000985568</v>
       </c>
       <c r="G5" t="n">
-        <v>0.233125731150824</v>
+        <v>1.1402171587636</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9288929792928595</v>
+        <v>0.9166235632163843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9226675547271814</v>
+        <v>0.9221747183264277</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03202752421613641</v>
+        <v>0.08282164949145206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04217035484506115</v>
+        <v>0.1134030124205291</v>
       </c>
       <c r="L5" t="n">
-        <v>835.3200854384146</v>
+        <v>296.0683305504247</v>
       </c>
       <c r="M5" t="n">
-        <v>368.3169377513279</v>
+        <v>246.7219645331271</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6261666530801666</v>
+        <v>0.8972473692360423</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="P5" t="n">
-        <v>1.003051437930402</v>
+        <v>1.003861468735493</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.004931721897228</v>
+        <v>1.008431731713051</v>
       </c>
       <c r="R5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="S5" t="n">
-        <v>28.35737689864836</v>
+        <v>16.95037173912774</v>
       </c>
       <c r="T5" t="n">
-        <v>19.02603617625802</v>
+        <v>14.9226815538486</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4421482703800806</v>
+        <v>0.2305335990446752</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06594931642866098</v>
+        <v>0.06818067608021712</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1064935064935065</v>
+        <v>0.1145833333333333</v>
       </c>
     </row>
     <row r="6">
@@ -900,70 +900,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7674662456690937</v>
+        <v>0.8514955388435604</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8424412596827917</v>
+        <v>0.8177231796232496</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8846275386839074</v>
+        <v>1.010546759055283</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9415570094719036</v>
+        <v>0.9452903412491029</v>
       </c>
       <c r="F7" t="n">
-        <v>3.046177064540284</v>
+        <v>2.930607142898502</v>
       </c>
       <c r="G7" t="n">
-        <v>3.282894907874287</v>
+        <v>3.260918854213801</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9192116540168563</v>
+        <v>0.9207403261318348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9227744837479634</v>
+        <v>0.9519748627859773</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7587763388015577</v>
+        <v>0.6899197883377912</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7307795213591978</v>
+        <v>0.7183996529751426</v>
       </c>
       <c r="L7" t="n">
-        <v>7.41889195515598</v>
+        <v>6.812647729582318</v>
       </c>
       <c r="M7" t="n">
-        <v>7.093139300939295</v>
+        <v>7.180976195643482</v>
       </c>
       <c r="N7" t="n">
-        <v>1.022658748434803</v>
+        <v>1.009485243148028</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.053687794222365</v>
+        <v>1.073893286310778</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.069858707730748</v>
+        <v>1.070504973760363</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.404032282326074</v>
+        <v>2.511320968056919</v>
       </c>
       <c r="T7" t="n">
-        <v>2.476128867831439</v>
+        <v>2.521743750247535</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06735164952341033</v>
+        <v>0.08005163988094979</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04498975752074255</v>
+        <v>0.06494546106111922</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8">
@@ -3005,70 +3005,70 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4237144246043144</v>
+        <v>0.4447191641064449</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4281210112432972</v>
+        <v>0.4243794419925587</v>
       </c>
       <c r="D36" t="n">
-        <v>0.919365392656772</v>
+        <v>1.17458250529422</v>
       </c>
       <c r="E36" t="n">
-        <v>1.034705921768088</v>
+        <v>1.040544765572041</v>
       </c>
       <c r="F36" t="n">
-        <v>4.357585304522925</v>
+        <v>4.370884049531277</v>
       </c>
       <c r="G36" t="n">
-        <v>4.420658417439149</v>
+        <v>4.425519548579544</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9327467982170162</v>
+        <v>0.9412089093464671</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9351709493486164</v>
+        <v>0.9456228633803195</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8825491626693601</v>
+        <v>0.8688056087814576</v>
       </c>
       <c r="K36" t="n">
-        <v>0.891265753733663</v>
+        <v>0.8884211610099567</v>
       </c>
       <c r="L36" t="n">
-        <v>11.93408231872264</v>
+        <v>12.21131677476156</v>
       </c>
       <c r="M36" t="n">
-        <v>10.61496942790837</v>
+        <v>10.85741903252037</v>
       </c>
       <c r="N36" t="n">
-        <v>0.9870989746592806</v>
+        <v>0.9911512014126438</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>1.012362348799518</v>
+        <v>1.012825415429883</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.007843890530722</v>
+        <v>1.007902376243321</v>
       </c>
       <c r="R36" t="n">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="S36" t="n">
-        <v>1.947114619870997</v>
+        <v>2.126514049803474</v>
       </c>
       <c r="T36" t="n">
-        <v>1.87695238603348</v>
+        <v>1.923788942613817</v>
       </c>
       <c r="U36" t="n">
-        <v>0.01840605312652853</v>
+        <v>0.01479881726374722</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01966282887297305</v>
+        <v>0.02438209250151993</v>
       </c>
       <c r="W36" t="n">
-        <v>0.02205882352941176</v>
+        <v>0.02214022140221402</v>
       </c>
     </row>
     <row r="37">
@@ -3297,70 +3297,70 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.79258164699418</v>
+        <v>2.891582446522646</v>
       </c>
       <c r="C40" t="n">
-        <v>3.903714889380274</v>
+        <v>2.926739630790556</v>
       </c>
       <c r="D40" t="n">
-        <v>1.064901590273135</v>
+        <v>2.042115936593674</v>
       </c>
       <c r="E40" t="n">
-        <v>1.352368656659608</v>
+        <v>2.132571176835218</v>
       </c>
       <c r="F40" t="n">
-        <v>1.635641024573326</v>
+        <v>1.517443912638903</v>
       </c>
       <c r="G40" t="n">
-        <v>1.745096336392684</v>
+        <v>1.840430905301075</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8548466114154959</v>
+        <v>0.8016409880900751</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8555344264368472</v>
+        <v>0.840783124284445</v>
       </c>
       <c r="J40" t="n">
-        <v>0.21935509729898</v>
+        <v>0.2786544651680828</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2468231687995682</v>
+        <v>0.3001284095028359</v>
       </c>
       <c r="L40" t="n">
-        <v>61.13413308729697</v>
+        <v>123.96825221912</v>
       </c>
       <c r="M40" t="n">
-        <v>40.2477602928396</v>
+        <v>65.60832679435495</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6126830888696119</v>
+        <v>0.7274079759806709</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P40" t="n">
-        <v>1.019697280919649</v>
+        <v>1.006982630907901</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.032331467158111</v>
+        <v>1.014479929636982</v>
       </c>
       <c r="R40" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S40" t="n">
-        <v>7.517221182708751</v>
+        <v>10.10185147527461</v>
       </c>
       <c r="T40" t="n">
-        <v>6.142664340966792</v>
+        <v>7.657854804947737</v>
       </c>
       <c r="U40" t="n">
-        <v>0.3944782524861937</v>
+        <v>0.2728558347958247</v>
       </c>
       <c r="V40" t="n">
-        <v>0.02012915670122786</v>
+        <v>0.007254999852193866</v>
       </c>
       <c r="W40" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.02325581395348837</v>
       </c>
     </row>
     <row r="41">
@@ -4749,70 +4749,70 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.888699895757342</v>
+        <v>1.935074098502654</v>
       </c>
       <c r="C60" t="n">
-        <v>3.158894520650614</v>
+        <v>1.838185965570362</v>
       </c>
       <c r="D60" t="n">
-        <v>1.000561393943554</v>
+        <v>0.8708544567943179</v>
       </c>
       <c r="E60" t="n">
-        <v>1.035375825628718</v>
+        <v>0.941653996274857</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2712319808240816</v>
+        <v>1.466267383603564</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3676494774001865</v>
+        <v>1.842189370452505</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9244871914772512</v>
+        <v>0.9583520154878493</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9256606509173072</v>
+        <v>0.9426447578313228</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2619337838145553</v>
+        <v>0.5740443939582374</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3357137078245687</v>
+        <v>0.5969111209131408</v>
       </c>
       <c r="L60" t="n">
-        <v>14.65162095165188</v>
+        <v>10.6070709542266</v>
       </c>
       <c r="M60" t="n">
-        <v>8.125955933890543</v>
+        <v>8.63762014659661</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6870122618633148</v>
+        <v>0.8343894210991238</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="P60" t="n">
-        <v>1.062676556171896</v>
+        <v>1.030812974708947</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.092776722767243</v>
+        <v>1.053539405537984</v>
       </c>
       <c r="R60" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S60" t="n">
-        <v>3.912821397011444</v>
+        <v>2.851938276063051</v>
       </c>
       <c r="T60" t="n">
-        <v>3.062997573071773</v>
+        <v>2.727836334067292</v>
       </c>
       <c r="U60" t="n">
-        <v>0.3129877790086587</v>
+        <v>0.1949146510083789</v>
       </c>
       <c r="V60" t="n">
-        <v>0.08295749366410619</v>
+        <v>0.2184653199952523</v>
       </c>
       <c r="W60" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61">
@@ -9786,70 +9786,70 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.1607612154791172</v>
+        <v>0.129182604735649</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1775169045851855</v>
+        <v>0.1547096061297618</v>
       </c>
       <c r="D129" t="n">
-        <v>1.083885536277512</v>
+        <v>0.7119973534230507</v>
       </c>
       <c r="E129" t="n">
-        <v>1.056416719107693</v>
+        <v>1.046228458314024</v>
       </c>
       <c r="F129" t="n">
-        <v>3.538738371017739</v>
+        <v>3.557818504800712</v>
       </c>
       <c r="G129" t="n">
-        <v>3.799116738187332</v>
+        <v>3.849106163925768</v>
       </c>
       <c r="H129" t="n">
-        <v>0.898945551679846</v>
+        <v>0.9498891688784538</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8890456976663696</v>
+        <v>0.9283842137379847</v>
       </c>
       <c r="J129" t="n">
-        <v>0.7898639318757688</v>
+        <v>0.9214953156959456</v>
       </c>
       <c r="K129" t="n">
-        <v>0.7802496254202818</v>
+        <v>0.8455053260876462</v>
       </c>
       <c r="L129" t="n">
-        <v>12.38627472421985</v>
+        <v>0.9743820982059499</v>
       </c>
       <c r="M129" t="n">
-        <v>10.27564432985529</v>
+        <v>9.000325552285496</v>
       </c>
       <c r="N129" t="n">
-        <v>0.9885989775417648</v>
+        <v>0.9972101934824076</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="P129" t="n">
-        <v>1.025782251517174</v>
+        <v>1.000465302497204</v>
       </c>
       <c r="Q129" t="n">
-        <v>1.034552392430763</v>
+        <v>1.020658356003813</v>
       </c>
       <c r="R129" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S129" t="n">
-        <v>2.66663841204372</v>
+        <v>1.009265704486047</v>
       </c>
       <c r="T129" t="n">
-        <v>2.60442718380626</v>
+        <v>2.176972493956989</v>
       </c>
       <c r="U129" t="n">
-        <v>0.01320726398859391</v>
+        <v>0.01612059176206102</v>
       </c>
       <c r="V129" t="n">
-        <v>0.0201233152307345</v>
+        <v>0.02046487814224904</v>
       </c>
       <c r="W129" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.03061224489795918</v>
       </c>
     </row>
     <row r="130">

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -1751,10 +1751,10 @@
         <v>0.09293681618496408</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3622193416706191</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -4736,7 +4736,7 @@
         <v>0.009230255466642488</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>0.2482240629063026</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
         <v>0.2444793042576891</v>
       </c>
       <c r="V148" t="n">
-        <v>0</v>
+        <v>0.01969552426254956</v>
       </c>
       <c r="W148" t="n">
         <v>0.1428571428571428</v>

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -7742,70 +7742,70 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>13.40409564039896</v>
+        <v>2.029460048637381</v>
       </c>
       <c r="C101" t="n">
-        <v>12.82854672118702</v>
+        <v>2.055861454624757</v>
       </c>
       <c r="D101" t="n">
-        <v>4.175688026156342</v>
+        <v>1.385904764890303</v>
       </c>
       <c r="E101" t="n">
-        <v>4.146832406273914</v>
+        <v>1.200377348323862</v>
       </c>
       <c r="F101" t="n">
-        <v>0.233075422137223</v>
+        <v>2.758357898540478</v>
       </c>
       <c r="G101" t="n">
-        <v>0.1942530625767057</v>
+        <v>2.867950817169004</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9299110110853639</v>
+        <v>0.9239818202435618</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9237387140813667</v>
+        <v>0.912141377651869</v>
       </c>
       <c r="J101" t="n">
-        <v>0.03933279113409365</v>
+        <v>0.5215875085852623</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04600312568793574</v>
+        <v>0.5105591663139327</v>
       </c>
       <c r="L101" t="n">
-        <v>347.0233764045531</v>
+        <v>28.28160030708699</v>
       </c>
       <c r="M101" t="n">
-        <v>317.9583438867255</v>
+        <v>30.45870415093044</v>
       </c>
       <c r="N101" t="n">
-        <v>0.9333797658356822</v>
+        <v>0.9947237430837617</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>1.004094196054909</v>
+        <v>1.014016365397673</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.005043833147337</v>
+        <v>1.013484922788592</v>
       </c>
       <c r="R101" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="S101" t="n">
-        <v>18.3304796368036</v>
+        <v>4.343920701537407</v>
       </c>
       <c r="T101" t="n">
-        <v>17.41288271073222</v>
+        <v>4.609640689229552</v>
       </c>
       <c r="U101" t="n">
-        <v>0.1138608317178825</v>
+        <v>0.06895988746928795</v>
       </c>
       <c r="V101" t="n">
-        <v>0.1635946369790653</v>
+        <v>0.1594215066973216</v>
       </c>
       <c r="W101" t="n">
-        <v>0.1425</v>
+        <v>0.1407035175879397</v>
       </c>
     </row>
     <row r="102">

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>fit_lognorm_SW</t>
+          <t>fit_lognorm_SF</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>fit_lognorm_SW_uw</t>
+          <t>fit_lognorm_SF_uw</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>fit_norm_SW</t>
+          <t>fit_norm_SF</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>fit_norm_SW_uw</t>
+          <t>fit_norm_SF_uw</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -556,13 +556,13 @@
         <v>0.8494116503658599</v>
       </c>
       <c r="I2" t="n">
-        <v>0.912889545161801</v>
+        <v>0.9092060209108411</v>
       </c>
       <c r="J2" t="n">
         <v>0.9408523678774999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8870817017132662</v>
+        <v>0.8835780693820586</v>
       </c>
       <c r="L2" t="n">
         <v>-0.4232017742483016</v>
@@ -629,13 +629,13 @@
         <v>0.8917379209458604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9247448315443465</v>
+        <v>0.9176917024745919</v>
       </c>
       <c r="J3" t="n">
         <v>0.9666226237052599</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9467795739712258</v>
+        <v>0.9456204318122453</v>
       </c>
       <c r="L3" t="n">
         <v>0.1662591797972714</v>
@@ -702,13 +702,13 @@
         <v>0.9533433053206312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9622585378473276</v>
+        <v>0.9620883018847108</v>
       </c>
       <c r="J4" t="n">
         <v>0.4489224569193863</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5006358208247527</v>
+        <v>0.4978144421636235</v>
       </c>
       <c r="L4" t="n">
         <v>42.28521597572163</v>
@@ -775,13 +775,13 @@
         <v>0.929692177466275</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9191877037826821</v>
+        <v>0.9184114196227847</v>
       </c>
       <c r="J5" t="n">
         <v>0.1013657572748851</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09161637184597682</v>
+        <v>0.08750428201791764</v>
       </c>
       <c r="L5" t="n">
         <v>163.8665054210526</v>
@@ -848,13 +848,13 @@
         <v>0.972478099150505</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9537935662538458</v>
+        <v>0.9530177174944041</v>
       </c>
       <c r="J6" t="n">
         <v>0.8123807792000486</v>
       </c>
       <c r="K6" t="n">
-        <v>0.822467890478628</v>
+        <v>0.8180317221940644</v>
       </c>
       <c r="L6" t="n">
         <v>5.668478652861983</v>
@@ -921,13 +921,13 @@
         <v>0.9207403261318348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9519748627859773</v>
+        <v>0.9440011262152957</v>
       </c>
       <c r="J7" t="n">
         <v>0.6899197883377912</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7183996529751426</v>
+        <v>0.7114210013043908</v>
       </c>
       <c r="L7" t="n">
         <v>6.812647729582318</v>
@@ -994,13 +994,13 @@
         <v>0.9474251833827445</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9510641296365299</v>
+        <v>0.9557090450612272</v>
       </c>
       <c r="J8" t="n">
         <v>0.8349972892712356</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8443267531038592</v>
+        <v>0.8479020220897057</v>
       </c>
       <c r="L8" t="n">
         <v>0.7931281673288593</v>
@@ -1073,7 +1073,7 @@
         <v>0.9955351590063858</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9998590287176354</v>
+        <v>0.9998590287176358</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1136,13 +1136,13 @@
         <v>0.9030430298440333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9093437360966836</v>
+        <v>0.911289510479757</v>
       </c>
       <c r="J10" t="n">
         <v>0.7920321457730231</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7629110641513599</v>
+        <v>0.7564910499909325</v>
       </c>
       <c r="L10" t="n">
         <v>2.269020227040517</v>
@@ -1209,13 +1209,13 @@
         <v>0.9652229947878748</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9678180434231227</v>
+        <v>0.9678621478402331</v>
       </c>
       <c r="J11" t="n">
         <v>0.9028121578587365</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8963405675894759</v>
+        <v>0.8963564790783439</v>
       </c>
       <c r="L11" t="n">
         <v>5.904110082353125</v>
@@ -1282,13 +1282,13 @@
         <v>0.9839805203242731</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9543715662249908</v>
+        <v>0.9603015742842809</v>
       </c>
       <c r="J12" t="n">
         <v>0.6822747554989643</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6497797011049407</v>
+        <v>0.6464974667569573</v>
       </c>
       <c r="L12" t="n">
         <v>5.190211222203374</v>
@@ -1355,13 +1355,13 @@
         <v>0.9780114202410796</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9883179098031101</v>
+        <v>0.9889175902627609</v>
       </c>
       <c r="J13" t="n">
         <v>0.7336423377662074</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7493861778079243</v>
+        <v>0.7419603693943674</v>
       </c>
       <c r="L13" t="n">
         <v>10.32890244783706</v>
@@ -1428,13 +1428,13 @@
         <v>0.8727234599054907</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8724002405574519</v>
+        <v>0.8690364524191365</v>
       </c>
       <c r="J14" t="n">
         <v>0.8705184285634944</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7943923596512326</v>
+        <v>0.7862656126481635</v>
       </c>
       <c r="L14" t="n">
         <v>6.540705755360844</v>
@@ -1501,13 +1501,13 @@
         <v>0.9572999427082871</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9309556255000982</v>
+        <v>0.9318061333144438</v>
       </c>
       <c r="J15" t="n">
         <v>0.5829353329793079</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5669579032811601</v>
+        <v>0.5664586343972672</v>
       </c>
       <c r="L15" t="n">
         <v>16.65055314118036</v>
@@ -1574,13 +1574,13 @@
         <v>0.9290963667493711</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9295911053734708</v>
+        <v>0.9295911053734703</v>
       </c>
       <c r="J16" t="n">
         <v>0.9965370912975703</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9955275127701789</v>
+        <v>0.9955275127701788</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1643,13 +1643,13 @@
         <v>0.951626762063243</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9612540179928349</v>
+        <v>0.9620477983526827</v>
       </c>
       <c r="J17" t="n">
         <v>0.5589212807730928</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6383083103717502</v>
+        <v>0.6344410859030679</v>
       </c>
       <c r="L17" t="n">
         <v>15.7304797314563</v>
@@ -1716,13 +1716,13 @@
         <v>0.9796649449918181</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8678362403890658</v>
+        <v>0.8678362403890659</v>
       </c>
       <c r="J18" t="n">
         <v>0.9659464275170122</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7774078101824612</v>
+        <v>0.7774078101824614</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         <v>0.9578191260316599</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9542076589471196</v>
+        <v>0.9582148841164957</v>
       </c>
       <c r="J19" t="n">
         <v>0.8499463737329206</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8034669915087368</v>
+        <v>0.7981866459686259</v>
       </c>
       <c r="L19" t="n">
         <v>3.002562856742959</v>
@@ -1858,13 +1858,13 @@
         <v>0.975434139575947</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9763024936774269</v>
+        <v>0.9741862180691335</v>
       </c>
       <c r="J20" t="n">
         <v>0.7372657332390844</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5220239953661741</v>
+        <v>0.5067517139688824</v>
       </c>
       <c r="L20" t="n">
         <v>11.96830709957616</v>
@@ -1931,13 +1931,13 @@
         <v>0.8956671122333576</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9362987071392876</v>
+        <v>0.9364420269624285</v>
       </c>
       <c r="J21" t="n">
         <v>0.6806677497662093</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5664516080586816</v>
+        <v>0.5603242798676761</v>
       </c>
       <c r="L21" t="n">
         <v>9.549626396730812</v>
@@ -2004,13 +2004,13 @@
         <v>0.9531632821687459</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9766644527137446</v>
+        <v>0.9733576455854616</v>
       </c>
       <c r="J22" t="n">
         <v>0.6235227628305499</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6386430733705381</v>
+        <v>0.6229215418397556</v>
       </c>
       <c r="L22" t="n">
         <v>4.580741592184308</v>
@@ -2077,13 +2077,13 @@
         <v>0.9883291140257277</v>
       </c>
       <c r="I23" t="n">
-        <v>0.976722031293628</v>
+        <v>0.9764788605215103</v>
       </c>
       <c r="J23" t="n">
         <v>0.8383344143204015</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7744174689324486</v>
+        <v>0.7677189383203588</v>
       </c>
       <c r="L23" t="n">
         <v>5.286696521289679</v>
@@ -2150,13 +2150,13 @@
         <v>0.9022344079326899</v>
       </c>
       <c r="I24" t="n">
-        <v>0.895248868519865</v>
+        <v>0.9175311762105741</v>
       </c>
       <c r="J24" t="n">
         <v>0.7803373328992713</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8234945768871653</v>
+        <v>0.8439091183293908</v>
       </c>
       <c r="L24" t="n">
         <v>1.06680996146393</v>
@@ -2223,13 +2223,13 @@
         <v>0.9654994347763881</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9604514402835619</v>
+        <v>0.958041135483536</v>
       </c>
       <c r="J25" t="n">
         <v>0.8378708341747267</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8570248075475875</v>
+        <v>0.8577269340636383</v>
       </c>
       <c r="L25" t="n">
         <v>1.930820456870329</v>
@@ -2296,13 +2296,13 @@
         <v>0.9599137570001955</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9602418130793022</v>
+        <v>0.9596970004623615</v>
       </c>
       <c r="J26" t="n">
         <v>0.401851652011318</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4398563005030176</v>
+        <v>0.435425153916047</v>
       </c>
       <c r="L26" t="n">
         <v>47.20796066291464</v>
@@ -2369,13 +2369,13 @@
         <v>0.9684858514659004</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9733156961631455</v>
+        <v>0.9745944148978668</v>
       </c>
       <c r="J27" t="n">
         <v>0.9597109699779091</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9594868617230063</v>
+        <v>0.9608978585480642</v>
       </c>
       <c r="L27" t="n">
         <v>-0.3973653073210545</v>
@@ -2442,13 +2442,13 @@
         <v>0.9795995889800222</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9904931908448098</v>
+        <v>0.9894957426100602</v>
       </c>
       <c r="J28" t="n">
         <v>0.9811433589819321</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9606212700622762</v>
+        <v>0.959258370009439</v>
       </c>
       <c r="L28" t="n">
         <v>-1.353236489437302</v>
@@ -2515,13 +2515,13 @@
         <v>0.9022485624589032</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9478327709605739</v>
+        <v>0.9285510909684714</v>
       </c>
       <c r="J29" t="n">
         <v>0.8891449008487291</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9248111073270874</v>
+        <v>0.9053502333035361</v>
       </c>
       <c r="L29" t="n">
         <v>5.838767464500953</v>
@@ -2588,13 +2588,13 @@
         <v>0.9816310740309314</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9799613530865678</v>
+        <v>0.9802206178601236</v>
       </c>
       <c r="J30" t="n">
         <v>0.9172249791720093</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9043754404401715</v>
+        <v>0.9049070072377239</v>
       </c>
       <c r="L30" t="n">
         <v>1.412023702974907</v>
@@ -2661,13 +2661,13 @@
         <v>0.9731432497154273</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9803959633627402</v>
+        <v>0.9826903094730325</v>
       </c>
       <c r="J31" t="n">
         <v>0.9802220681656316</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9733299166520434</v>
+        <v>0.9735941299923175</v>
       </c>
       <c r="L31" t="n">
         <v>-0.6157999738070424</v>
@@ -2734,13 +2734,13 @@
         <v>0.9465754317706573</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9673180737593341</v>
+        <v>0.9672279193735077</v>
       </c>
       <c r="J32" t="n">
         <v>0.8794085062473335</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9213873827286474</v>
+        <v>0.9202025250993612</v>
       </c>
       <c r="L32" t="n">
         <v>3.34317902200783</v>
@@ -2807,13 +2807,13 @@
         <v>0.9186335129552035</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9240961497292354</v>
+        <v>0.9284356708505789</v>
       </c>
       <c r="J33" t="n">
         <v>0.7226802181148442</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6691699558470116</v>
+        <v>0.6631689950689539</v>
       </c>
       <c r="L33" t="n">
         <v>9.82683715516575</v>
@@ -2880,13 +2880,13 @@
         <v>0.9847308287724691</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9862532986272947</v>
+        <v>0.9861897621005156</v>
       </c>
       <c r="J34" t="n">
         <v>0.9419396660461248</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9448352377733952</v>
+        <v>0.9448869411265992</v>
       </c>
       <c r="L34" t="n">
         <v>-0.08586160146506275</v>
@@ -2953,13 +2953,13 @@
         <v>0.9854139733963865</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9848214852912753</v>
+        <v>0.9857099336535577</v>
       </c>
       <c r="J35" t="n">
         <v>0.9410711935826805</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9433003010535914</v>
+        <v>0.9428425243038698</v>
       </c>
       <c r="L35" t="n">
         <v>1.08913324359499</v>
@@ -3026,13 +3026,13 @@
         <v>0.9412089093464671</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9456228633803195</v>
+        <v>0.9455040331102524</v>
       </c>
       <c r="J36" t="n">
         <v>0.8688056087814576</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8884211610099567</v>
+        <v>0.8876079866374171</v>
       </c>
       <c r="L36" t="n">
         <v>12.21131677476156</v>
@@ -3099,13 +3099,13 @@
         <v>0.9468811101110821</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9445280525474916</v>
+        <v>0.9417552493518829</v>
       </c>
       <c r="J37" t="n">
         <v>0.8898171532143072</v>
       </c>
       <c r="K37" t="n">
-        <v>0.864462699249297</v>
+        <v>0.8683795528088797</v>
       </c>
       <c r="L37" t="n">
         <v>0.8204360219009512</v>
@@ -3172,13 +3172,13 @@
         <v>0.9706546985838592</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9748794474647776</v>
+        <v>0.9748370575681687</v>
       </c>
       <c r="J38" t="n">
         <v>0.8252870290484627</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8410209673686802</v>
+        <v>0.8409040981188135</v>
       </c>
       <c r="L38" t="n">
         <v>10.87620022088294</v>
@@ -3245,13 +3245,13 @@
         <v>0.9467811380414417</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9180642120630196</v>
+        <v>0.9249435362049317</v>
       </c>
       <c r="J39" t="n">
         <v>0.8950699757770634</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9043980327782193</v>
+        <v>0.9098367774503526</v>
       </c>
       <c r="L39" t="n">
         <v>0.6502411539271484</v>
@@ -3318,13 +3318,13 @@
         <v>0.9362699502971596</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9436469094758352</v>
+        <v>0.9407788142431837</v>
       </c>
       <c r="J40" t="n">
         <v>0.8717929060913877</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7827473234135598</v>
+        <v>0.7774113386726403</v>
       </c>
       <c r="L40" t="n">
         <v>5.712982870909621</v>
@@ -3391,13 +3391,13 @@
         <v>0.980670792735478</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9633020898839904</v>
+        <v>0.9536016963377437</v>
       </c>
       <c r="J41" t="n">
         <v>0.9196367744331216</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8762951649435859</v>
+        <v>0.863536014372004</v>
       </c>
       <c r="L41" t="n">
         <v>4.094525149186255</v>
@@ -3464,13 +3464,13 @@
         <v>0.8813815533659585</v>
       </c>
       <c r="I42" t="n">
-        <v>0.75870676392347</v>
+        <v>0.7587067639234697</v>
       </c>
       <c r="J42" t="n">
         <v>0.8881419827509356</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7721721138764062</v>
+        <v>0.7721721138764063</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         <v>0.9748672079469952</v>
       </c>
       <c r="I43" t="n">
-        <v>0.971485193523098</v>
+        <v>0.96630985951165</v>
       </c>
       <c r="J43" t="n">
         <v>0.2112867046336534</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1686344187607627</v>
+        <v>0.159177693493579</v>
       </c>
       <c r="L43" t="n">
         <v>525.1663376619023</v>
@@ -3606,13 +3606,13 @@
         <v>0.9633142632052857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9611221891369903</v>
+        <v>0.9645133852031788</v>
       </c>
       <c r="J44" t="n">
         <v>0.9676119139575859</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9626791170066653</v>
+        <v>0.966680358069733</v>
       </c>
       <c r="L44" t="n">
         <v>-1.066623475499305</v>
@@ -3679,13 +3679,13 @@
         <v>0.982071153192389</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9834011717462637</v>
+        <v>0.9827587906733408</v>
       </c>
       <c r="J45" t="n">
         <v>0.9656810495914704</v>
       </c>
       <c r="K45" t="n">
-        <v>0.970718581490819</v>
+        <v>0.9710239429878805</v>
       </c>
       <c r="L45" t="n">
         <v>0.1934105440441739</v>
@@ -3752,13 +3752,13 @@
         <v>0.9501898347653676</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9203172267851878</v>
+        <v>0.9299070304301821</v>
       </c>
       <c r="J46" t="n">
         <v>0.930789213775484</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9102495874274408</v>
+        <v>0.9198006311770659</v>
       </c>
       <c r="L46" t="n">
         <v>-0.8259364872851389</v>
@@ -3825,13 +3825,13 @@
         <v>0.9054869344259462</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9239109548009905</v>
+        <v>0.9307014047869741</v>
       </c>
       <c r="J47" t="n">
         <v>0.9497259045844483</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9520711149135589</v>
+        <v>0.9591445608254481</v>
       </c>
       <c r="L47" t="n">
         <v>-0.7175555103435306</v>
@@ -3898,13 +3898,13 @@
         <v>0.9514305868631614</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8839596731286349</v>
+        <v>0.8811535865145093</v>
       </c>
       <c r="J48" t="n">
         <v>0.8321404875263214</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6270007800005779</v>
+        <v>0.6191353025216019</v>
       </c>
       <c r="L48" t="n">
         <v>17.45610091815069</v>
@@ -3971,13 +3971,13 @@
         <v>0.961968651691529</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9355534595019865</v>
+        <v>0.9382383419651381</v>
       </c>
       <c r="J49" t="n">
         <v>0.6533444986987889</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7367704200508431</v>
+        <v>0.7323263155781626</v>
       </c>
       <c r="L49" t="n">
         <v>12.11917777500005</v>
@@ -4044,13 +4044,13 @@
         <v>0.9532135184127367</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9573153188717286</v>
+        <v>0.9528255282056156</v>
       </c>
       <c r="J50" t="n">
         <v>0.8214356871280972</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7554764800270884</v>
+        <v>0.750814084224615</v>
       </c>
       <c r="L50" t="n">
         <v>3.701598110423332</v>
@@ -4117,13 +4117,13 @@
         <v>0.942617875759766</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9285698432291277</v>
+        <v>0.927179826973757</v>
       </c>
       <c r="J51" t="n">
         <v>0.3040643543049877</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3197038470529262</v>
+        <v>0.3160099443114681</v>
       </c>
       <c r="L51" t="n">
         <v>30.85059786755903</v>
@@ -4190,13 +4190,13 @@
         <v>0.9671375358809949</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9697349107314407</v>
+        <v>0.9699044536362832</v>
       </c>
       <c r="J52" t="n">
         <v>0.5355876415060616</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5564444850936798</v>
+        <v>0.5553793733772043</v>
       </c>
       <c r="L52" t="n">
         <v>11.49834456384718</v>
@@ -4263,13 +4263,13 @@
         <v>0.9736282514157977</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9618989801768074</v>
+        <v>0.9531953703848772</v>
       </c>
       <c r="J53" t="n">
         <v>0.8841924993922177</v>
       </c>
       <c r="K53" t="n">
-        <v>0.8422786876312083</v>
+        <v>0.8308422751056909</v>
       </c>
       <c r="L53" t="n">
         <v>0.4152861003419528</v>
@@ -4336,13 +4336,13 @@
         <v>0.8819310189564558</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8849505243937633</v>
+        <v>0.8845006482727006</v>
       </c>
       <c r="J54" t="n">
         <v>0.957828754145963</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9703162055578234</v>
+        <v>0.9710928362997387</v>
       </c>
       <c r="L54" t="n">
         <v>1.043583110562199</v>
@@ -4409,13 +4409,13 @@
         <v>0.9059134069707252</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9480477544728466</v>
+        <v>0.9586864806868646</v>
       </c>
       <c r="J55" t="n">
         <v>0.9698747474161831</v>
       </c>
       <c r="K55" t="n">
-        <v>0.941591994063652</v>
+        <v>0.9542121420021797</v>
       </c>
       <c r="L55" t="n">
         <v>-2.355523716459283</v>
@@ -4482,13 +4482,13 @@
         <v>0.82514045651893</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8632710164081342</v>
+        <v>0.8640016404242711</v>
       </c>
       <c r="J56" t="n">
         <v>0.9525832569828501</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9642406132147385</v>
+        <v>0.9643369688067852</v>
       </c>
       <c r="L56" t="n">
         <v>0.1381867509915326</v>
@@ -4555,13 +4555,13 @@
         <v>0.9818598844200473</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9733193275962856</v>
+        <v>0.9727929961398722</v>
       </c>
       <c r="J57" t="n">
         <v>0.6914038228070565</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6428300351769272</v>
+        <v>0.639559644635877</v>
       </c>
       <c r="L57" t="n">
         <v>16.38871777755219</v>
@@ -4628,13 +4628,13 @@
         <v>0.9518464854848355</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9820108264654308</v>
+        <v>0.9820108264654309</v>
       </c>
       <c r="J58" t="n">
         <v>0.949893963496349</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9810450295997544</v>
+        <v>0.9810450295997541</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -4697,13 +4697,13 @@
         <v>0.9583520154878493</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9426447578313228</v>
+        <v>0.9518279459515709</v>
       </c>
       <c r="J59" t="n">
         <v>0.5740443939582374</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5969111209131408</v>
+        <v>0.5838970155092895</v>
       </c>
       <c r="L59" t="n">
         <v>10.6070709542266</v>
@@ -4770,13 +4770,13 @@
         <v>0.8042775435315257</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8542875930837134</v>
+        <v>0.860521535210255</v>
       </c>
       <c r="J60" t="n">
         <v>0.556352334564728</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6356484294516034</v>
+        <v>0.6174926891147209</v>
       </c>
       <c r="L60" t="n">
         <v>13.59504239802839</v>
@@ -4843,13 +4843,13 @@
         <v>0.9633672546730235</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9633450856730293</v>
+        <v>0.9633842197958534</v>
       </c>
       <c r="J61" t="n">
         <v>0.6238243798519839</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6304307068796957</v>
+        <v>0.6240837856174626</v>
       </c>
       <c r="L61" t="n">
         <v>40.22587551252376</v>
@@ -4916,13 +4916,13 @@
         <v>0.9440637496859311</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9279110452090704</v>
+        <v>0.9272542758582301</v>
       </c>
       <c r="J62" t="n">
         <v>0.8240321768183324</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7576271999845836</v>
+        <v>0.7502973278456877</v>
       </c>
       <c r="L62" t="n">
         <v>8.59685270788783</v>
@@ -4989,13 +4989,13 @@
         <v>0.972454540235953</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9569623874889673</v>
+        <v>0.9606790295030297</v>
       </c>
       <c r="J63" t="n">
         <v>0.7781383125359719</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8036513766302492</v>
+        <v>0.8032142940637226</v>
       </c>
       <c r="L63" t="n">
         <v>0.5015070220605585</v>
@@ -5062,13 +5062,13 @@
         <v>0.8670774729965373</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8527623997462219</v>
+        <v>0.8516775957051272</v>
       </c>
       <c r="J64" t="n">
         <v>0.5649063131443962</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6046637617537263</v>
+        <v>0.5913282496763302</v>
       </c>
       <c r="L64" t="n">
         <v>5.312004768479652</v>
@@ -5135,13 +5135,13 @@
         <v>0.9435590877433198</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9589790051961298</v>
+        <v>0.952245173518852</v>
       </c>
       <c r="J65" t="n">
         <v>0.8411942932386974</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6830020924039805</v>
+        <v>0.6715272529998201</v>
       </c>
       <c r="L65" t="n">
         <v>5.2699782656013</v>
@@ -5208,13 +5208,13 @@
         <v>0.9691571580090885</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9762806236819012</v>
+        <v>0.9763129896924536</v>
       </c>
       <c r="J66" t="n">
         <v>0.6811891617803418</v>
       </c>
       <c r="K66" t="n">
-        <v>0.7203602888414968</v>
+        <v>0.7199936608870245</v>
       </c>
       <c r="L66" t="n">
         <v>18.38499780164793</v>
@@ -5281,13 +5281,13 @@
         <v>0.9751226878495491</v>
       </c>
       <c r="I67" t="n">
-        <v>0.897395668081957</v>
+        <v>0.8917968611009424</v>
       </c>
       <c r="J67" t="n">
         <v>0.8518677721517369</v>
       </c>
       <c r="K67" t="n">
-        <v>0.6525371122782042</v>
+        <v>0.6331597910179844</v>
       </c>
       <c r="L67" t="n">
         <v>-2.220394685081102</v>
@@ -5354,13 +5354,13 @@
         <v>0.8732917745311607</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9509604236799754</v>
+        <v>0.9410733125656034</v>
       </c>
       <c r="J68" t="n">
         <v>0.9085826698003754</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9752253426822088</v>
+        <v>0.9660497361050783</v>
       </c>
       <c r="L68" t="n">
         <v>4.772937894073056</v>
@@ -5427,13 +5427,13 @@
         <v>0.9019765646016595</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8549245506455269</v>
+        <v>0.8754475673706901</v>
       </c>
       <c r="J69" t="n">
         <v>0.9078309723571365</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8770109025523605</v>
+        <v>0.8966277838417209</v>
       </c>
       <c r="L69" t="n">
         <v>-2.445001271247021</v>
@@ -5500,13 +5500,13 @@
         <v>0.9429577987377119</v>
       </c>
       <c r="I70" t="n">
-        <v>0.9496420194823438</v>
+        <v>0.9495696726536563</v>
       </c>
       <c r="J70" t="n">
         <v>0.5733099477776068</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5891387186684434</v>
+        <v>0.5837391670106539</v>
       </c>
       <c r="L70" t="n">
         <v>31.27006391293337</v>
@@ -5573,13 +5573,13 @@
         <v>0.9910023060328255</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9896483556657156</v>
+        <v>0.9891615343512296</v>
       </c>
       <c r="J71" t="n">
         <v>0.7365906903457102</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7216221720870823</v>
+        <v>0.7196268584327049</v>
       </c>
       <c r="L71" t="n">
         <v>26.04710035396777</v>
@@ -5646,13 +5646,13 @@
         <v>0.9638062333650304</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9760458690286841</v>
+        <v>0.9818277296345798</v>
       </c>
       <c r="J72" t="n">
         <v>0.979065881907884</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9594265198691596</v>
+        <v>0.9667346230623551</v>
       </c>
       <c r="L72" t="n">
         <v>-1.180608223118555</v>
@@ -5719,13 +5719,13 @@
         <v>0.8049473530115732</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7592687740448255</v>
+        <v>0.7858857580675497</v>
       </c>
       <c r="J73" t="n">
         <v>0.7357057470331443</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7157729723279735</v>
+        <v>0.7406169039146641</v>
       </c>
       <c r="L73" t="n">
         <v>-2.831062965873204</v>
@@ -5792,13 +5792,13 @@
         <v>0.9607344222142805</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9597051473195952</v>
+        <v>0.9585332049395646</v>
       </c>
       <c r="J74" t="n">
         <v>0.8636545249880749</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9369365116088233</v>
+        <v>0.9326458417713517</v>
       </c>
       <c r="L74" t="n">
         <v>6.418586757296552</v>
@@ -5865,13 +5865,13 @@
         <v>0.9709649683486649</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9460763871725829</v>
+        <v>0.9451940771398796</v>
       </c>
       <c r="J75" t="n">
         <v>0.6906687116354306</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6381903352266356</v>
+        <v>0.6370653038942111</v>
       </c>
       <c r="L75" t="n">
         <v>5.888071755774107</v>
@@ -5938,13 +5938,13 @@
         <v>0.9549130119249012</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9743502442809521</v>
+        <v>0.9733198524388371</v>
       </c>
       <c r="J76" t="n">
         <v>0.971539430709338</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9655384155258485</v>
+        <v>0.9641084148715836</v>
       </c>
       <c r="L76" t="n">
         <v>0.491701708597072</v>
@@ -6011,13 +6011,13 @@
         <v>0.9941641181119407</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9827670469312207</v>
+        <v>0.980332936119686</v>
       </c>
       <c r="J77" t="n">
         <v>0.9683949471962114</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8893485653264389</v>
+        <v>0.885502409863439</v>
       </c>
       <c r="L77" t="n">
         <v>1.242473817405057</v>
@@ -6084,13 +6084,13 @@
         <v>0.8189997399018097</v>
       </c>
       <c r="I78" t="n">
-        <v>0.804588013685579</v>
+        <v>0.8084501702494555</v>
       </c>
       <c r="J78" t="n">
         <v>0.664865278428347</v>
       </c>
       <c r="K78" t="n">
-        <v>0.662859966700212</v>
+        <v>0.6623828205373704</v>
       </c>
       <c r="L78" t="n">
         <v>3.715861765493621</v>
@@ -6157,13 +6157,13 @@
         <v>0.8871627786014125</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9221432656698454</v>
+        <v>0.9291331635779554</v>
       </c>
       <c r="J79" t="n">
         <v>0.918653701935489</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9586818964757403</v>
+        <v>0.97209186221764</v>
       </c>
       <c r="L79" t="n">
         <v>-2.357515921651137</v>
@@ -6230,13 +6230,13 @@
         <v>0.9492397019991253</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9402502757783897</v>
+        <v>0.9367588805273304</v>
       </c>
       <c r="J80" t="n">
         <v>0.9080328322905369</v>
       </c>
       <c r="K80" t="n">
-        <v>0.9015980887993379</v>
+        <v>0.9064873100433711</v>
       </c>
       <c r="L80" t="n">
         <v>-0.6612397412624589</v>
@@ -6303,13 +6303,13 @@
         <v>0.7644668122055117</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8981257801072224</v>
+        <v>0.8965292194046052</v>
       </c>
       <c r="J81" t="n">
         <v>0.4801638195630955</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6750436308567354</v>
+        <v>0.66566430880327</v>
       </c>
       <c r="L81" t="n">
         <v>17.03093091271075</v>
@@ -6376,13 +6376,13 @@
         <v>0.8666386697230382</v>
       </c>
       <c r="I82" t="n">
-        <v>0.869410368239242</v>
+        <v>0.8580021566801009</v>
       </c>
       <c r="J82" t="n">
         <v>0.8643529163081951</v>
       </c>
       <c r="K82" t="n">
-        <v>0.9493417630816191</v>
+        <v>0.9449414651152082</v>
       </c>
       <c r="L82" t="n">
         <v>4.040924625639891</v>
@@ -6449,13 +6449,13 @@
         <v>0.9222809805022177</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9230169916136531</v>
+        <v>0.9265793969273177</v>
       </c>
       <c r="J83" t="n">
         <v>0.6589279632167366</v>
       </c>
       <c r="K83" t="n">
-        <v>0.6961936673662437</v>
+        <v>0.6966262595037365</v>
       </c>
       <c r="L83" t="n">
         <v>3.607664401158456</v>
@@ -6522,13 +6522,13 @@
         <v>0.9498116266504352</v>
       </c>
       <c r="I84" t="n">
-        <v>0.960933685011536</v>
+        <v>0.9636120456832524</v>
       </c>
       <c r="J84" t="n">
         <v>0.9049703933468647</v>
       </c>
       <c r="K84" t="n">
-        <v>0.7460767094876462</v>
+        <v>0.7355695083195254</v>
       </c>
       <c r="L84" t="n">
         <v>0.7280829395190724</v>
@@ -6595,13 +6595,13 @@
         <v>0.9599285800621404</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9720853567966534</v>
+        <v>0.9701110403934403</v>
       </c>
       <c r="J85" t="n">
         <v>0.822266568146786</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7955210846159941</v>
+        <v>0.7910323883767763</v>
       </c>
       <c r="L85" t="n">
         <v>3.136191670406658</v>
@@ -6668,13 +6668,13 @@
         <v>0.8782070203855502</v>
       </c>
       <c r="I86" t="n">
-        <v>0.9107115863194318</v>
+        <v>0.899773458437987</v>
       </c>
       <c r="J86" t="n">
         <v>0.7512810186696256</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8132098059093047</v>
+        <v>0.8117353379120892</v>
       </c>
       <c r="L86" t="n">
         <v>3.245556063192823</v>
@@ -6741,13 +6741,13 @@
         <v>0.7649096687182814</v>
       </c>
       <c r="I87" t="n">
-        <v>0.936883139231212</v>
+        <v>0.9167990364544711</v>
       </c>
       <c r="J87" t="n">
         <v>0.7341427109941541</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9022659119957648</v>
+        <v>0.8825244047854364</v>
       </c>
       <c r="L87" t="n">
         <v>1.779726648425777</v>
@@ -6814,13 +6814,13 @@
         <v>0.8456792844695598</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8858439186529469</v>
+        <v>0.8823019265011078</v>
       </c>
       <c r="J88" t="n">
         <v>0.9510522837616211</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9820656466956146</v>
+        <v>0.9844349107052071</v>
       </c>
       <c r="L88" t="n">
         <v>0.4329255601368591</v>
@@ -6887,13 +6887,13 @@
         <v>0.9074157726089733</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9566613035823043</v>
+        <v>0.9580311469229821</v>
       </c>
       <c r="J89" t="n">
         <v>0.7473191323975155</v>
       </c>
       <c r="K89" t="n">
-        <v>0.8292234295161287</v>
+        <v>0.823994111691712</v>
       </c>
       <c r="L89" t="n">
         <v>9.845323307626238</v>
@@ -6960,13 +6960,13 @@
         <v>0.9640534188773633</v>
       </c>
       <c r="I90" t="n">
-        <v>0.975913112366247</v>
+        <v>0.9752017081213578</v>
       </c>
       <c r="J90" t="n">
         <v>0.5440253280148543</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5156560993004654</v>
+        <v>0.5127725876558968</v>
       </c>
       <c r="L90" t="n">
         <v>14.54732306591537</v>
@@ -7033,13 +7033,13 @@
         <v>0.9309002681236365</v>
       </c>
       <c r="I91" t="n">
-        <v>0.9265091341415583</v>
+        <v>0.9367782791275058</v>
       </c>
       <c r="J91" t="n">
         <v>0.8551581230437142</v>
       </c>
       <c r="K91" t="n">
-        <v>0.939080963356312</v>
+        <v>0.9442475082074633</v>
       </c>
       <c r="L91" t="n">
         <v>1.145358191339976</v>
@@ -7106,13 +7106,13 @@
         <v>0.9338182611462942</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9529889523315745</v>
+        <v>0.9595370042152918</v>
       </c>
       <c r="J92" t="n">
         <v>0.7813206850488175</v>
       </c>
       <c r="K92" t="n">
-        <v>0.7508793217006176</v>
+        <v>0.7486219534887986</v>
       </c>
       <c r="L92" t="n">
         <v>1.808846973688806</v>
@@ -7179,13 +7179,13 @@
         <v>0.9300680884117553</v>
       </c>
       <c r="I93" t="n">
-        <v>0.922348923426846</v>
+        <v>0.9151163940704784</v>
       </c>
       <c r="J93" t="n">
         <v>0.8935854149879883</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7095817101604576</v>
+        <v>0.6957847408064634</v>
       </c>
       <c r="L93" t="n">
         <v>13.76239808991692</v>
@@ -7252,13 +7252,13 @@
         <v>0.9591795941151628</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9692030010918883</v>
+        <v>0.9691209025025631</v>
       </c>
       <c r="J94" t="n">
         <v>0.4576718652063099</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4711389954270896</v>
+        <v>0.4675584024669723</v>
       </c>
       <c r="L94" t="n">
         <v>31.59902578632765</v>
@@ -7325,13 +7325,13 @@
         <v>0.8871676685005473</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8791687543492166</v>
+        <v>0.877284139880063</v>
       </c>
       <c r="J95" t="n">
         <v>0.8615573091733196</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7648029350820403</v>
+        <v>0.7542001333170487</v>
       </c>
       <c r="L95" t="n">
         <v>1.177867813625812</v>
@@ -7398,13 +7398,13 @@
         <v>0.7612901986376266</v>
       </c>
       <c r="I96" t="n">
-        <v>0.7403192118213865</v>
+        <v>0.7460956573143133</v>
       </c>
       <c r="J96" t="n">
         <v>0.9110182257592286</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9050004718726445</v>
+        <v>0.9167228067246915</v>
       </c>
       <c r="L96" t="n">
         <v>-1.362342062572789</v>
@@ -7471,13 +7471,13 @@
         <v>0.9282920417941357</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9559257847486657</v>
+        <v>0.9559032996193716</v>
       </c>
       <c r="J97" t="n">
         <v>0.8594016593062725</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7871854560053695</v>
+        <v>0.786064112358989</v>
       </c>
       <c r="L97" t="n">
         <v>4.46019112712948</v>
@@ -7544,13 +7544,13 @@
         <v>0.8996453009748022</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9689069065859512</v>
+        <v>0.9715676722594047</v>
       </c>
       <c r="J98" t="n">
         <v>0.6459023844646231</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6995724358613418</v>
+        <v>0.6869670475388048</v>
       </c>
       <c r="L98" t="n">
         <v>18.68211258309089</v>
@@ -7617,13 +7617,13 @@
         <v>0.9058623543096419</v>
       </c>
       <c r="I99" t="n">
-        <v>0.947195553437719</v>
+        <v>0.9441785518552663</v>
       </c>
       <c r="J99" t="n">
         <v>0.8473840760520954</v>
       </c>
       <c r="K99" t="n">
-        <v>0.6190449216717577</v>
+        <v>0.6083758802924011</v>
       </c>
       <c r="L99" t="n">
         <v>22.8655829224015</v>
@@ -7690,13 +7690,13 @@
         <v>0.9293062868562693</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9584969216698123</v>
+        <v>0.9585585106523173</v>
       </c>
       <c r="J100" t="n">
         <v>0.8916938255182151</v>
       </c>
       <c r="K100" t="n">
-        <v>0.9296500354873902</v>
+        <v>0.9277877854150426</v>
       </c>
       <c r="L100" t="n">
         <v>2.432626933157633</v>
@@ -7763,13 +7763,13 @@
         <v>0.9239818202435618</v>
       </c>
       <c r="I101" t="n">
-        <v>0.912141377651869</v>
+        <v>0.9132418373642248</v>
       </c>
       <c r="J101" t="n">
         <v>0.5215875085852623</v>
       </c>
       <c r="K101" t="n">
-        <v>0.5105591663139327</v>
+        <v>0.5076411507337909</v>
       </c>
       <c r="L101" t="n">
         <v>28.28160030708699</v>
@@ -7836,13 +7836,13 @@
         <v>0.9470780582933653</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9302077316110111</v>
+        <v>0.9299134235148441</v>
       </c>
       <c r="J102" t="n">
         <v>0.8140167374036025</v>
       </c>
       <c r="K102" t="n">
-        <v>0.7336729667981577</v>
+        <v>0.7329238611971077</v>
       </c>
       <c r="L102" t="n">
         <v>9.302569536348297</v>
@@ -7909,13 +7909,13 @@
         <v>0.9474301938836615</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9607776179559141</v>
+        <v>0.9607672669319586</v>
       </c>
       <c r="J103" t="n">
         <v>0.7127931567166175</v>
       </c>
       <c r="K103" t="n">
-        <v>0.6561514067583674</v>
+        <v>0.6537992328993875</v>
       </c>
       <c r="L103" t="n">
         <v>6.993810882712427</v>
@@ -7982,13 +7982,13 @@
         <v>0.9982226333391805</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9982933090642053</v>
+        <v>0.9982936450982198</v>
       </c>
       <c r="J104" t="n">
         <v>0.9764698273340006</v>
       </c>
       <c r="K104" t="n">
-        <v>0.977555538121432</v>
+        <v>0.9775417020016794</v>
       </c>
       <c r="L104" t="n">
         <v>1.197478685184682</v>
@@ -8055,13 +8055,13 @@
         <v>0.9951600253100358</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9948166207658572</v>
+        <v>0.9948142636587471</v>
       </c>
       <c r="J105" t="n">
         <v>0.9831811815916462</v>
       </c>
       <c r="K105" t="n">
-        <v>0.9832220424239487</v>
+        <v>0.9832010788491115</v>
       </c>
       <c r="L105" t="n">
         <v>1.092873344384106</v>
@@ -8128,13 +8128,13 @@
         <v>0.9904101437830806</v>
       </c>
       <c r="I106" t="n">
-        <v>0.9883631389542754</v>
+        <v>0.9883531352673238</v>
       </c>
       <c r="J106" t="n">
         <v>0.9904478965219439</v>
       </c>
       <c r="K106" t="n">
-        <v>0.9931300444533219</v>
+        <v>0.9930934444985947</v>
       </c>
       <c r="L106" t="n">
         <v>0.2436625027678547</v>
@@ -8201,13 +8201,13 @@
         <v>0.9420908306441922</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9470129275224937</v>
+        <v>0.9470602177097228</v>
       </c>
       <c r="J107" t="n">
         <v>0.9819348304737784</v>
       </c>
       <c r="K107" t="n">
-        <v>0.9812382151575246</v>
+        <v>0.9811897090239802</v>
       </c>
       <c r="L107" t="n">
         <v>1.558347150652827</v>
@@ -8274,13 +8274,13 @@
         <v>0.9892162023489297</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9914994356276202</v>
+        <v>0.9914485725052155</v>
       </c>
       <c r="J108" t="n">
         <v>0.9892317502039953</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9800361481877558</v>
+        <v>0.9798982908304719</v>
       </c>
       <c r="L108" t="n">
         <v>0.4960927669492675</v>
@@ -8347,13 +8347,13 @@
         <v>0.9963088097462847</v>
       </c>
       <c r="I109" t="n">
-        <v>0.99629012307829</v>
+        <v>0.9962489439232705</v>
       </c>
       <c r="J109" t="n">
         <v>0.9114715635752628</v>
       </c>
       <c r="K109" t="n">
-        <v>0.9049552834860752</v>
+        <v>0.9046781479075031</v>
       </c>
       <c r="L109" t="n">
         <v>9.980181674618628</v>
@@ -8420,13 +8420,13 @@
         <v>0.9680636738527292</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9746013036068354</v>
+        <v>0.973226994892649</v>
       </c>
       <c r="J110" t="n">
         <v>0.6875658452951185</v>
       </c>
       <c r="K110" t="n">
-        <v>0.7006694797153243</v>
+        <v>0.6951756113592603</v>
       </c>
       <c r="L110" t="n">
         <v>20.99519948678543</v>
@@ -8493,13 +8493,13 @@
         <v>0.9384346422416922</v>
       </c>
       <c r="I111" t="n">
-        <v>0.9360211490591377</v>
+        <v>0.9361362546829023</v>
       </c>
       <c r="J111" t="n">
         <v>0.5506846500526584</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5447395756348599</v>
+        <v>0.5444577826215516</v>
       </c>
       <c r="L111" t="n">
         <v>12.72678860894951</v>
@@ -8566,13 +8566,13 @@
         <v>0.7591825066523465</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8980326989054888</v>
+        <v>0.8915433109914993</v>
       </c>
       <c r="J112" t="n">
         <v>0.8004099537943093</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9393258346928226</v>
+        <v>0.9322944921273235</v>
       </c>
       <c r="L112" t="n">
         <v>0.04147614781625295</v>
@@ -8639,13 +8639,13 @@
         <v>0.9396276723664576</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9652075554857067</v>
+        <v>0.9662086348327067</v>
       </c>
       <c r="J113" t="n">
         <v>0.923417045201437</v>
       </c>
       <c r="K113" t="n">
-        <v>0.8885601779274186</v>
+        <v>0.8886276215003057</v>
       </c>
       <c r="L113" t="n">
         <v>-0.4677286136268061</v>
@@ -8712,13 +8712,13 @@
         <v>0.8992945415794971</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8999491904844276</v>
+        <v>0.8948838830670247</v>
       </c>
       <c r="J114" t="n">
         <v>0.7577563043655118</v>
       </c>
       <c r="K114" t="n">
-        <v>0.769626178997154</v>
+        <v>0.7694936180781276</v>
       </c>
       <c r="L114" t="n">
         <v>1.214287604857461</v>
@@ -8785,13 +8785,13 @@
         <v>0.978166977457074</v>
       </c>
       <c r="I115" t="n">
-        <v>0.9866280883807539</v>
+        <v>0.9887110291950253</v>
       </c>
       <c r="J115" t="n">
         <v>0.9805437258166971</v>
       </c>
       <c r="K115" t="n">
-        <v>0.9801489765047542</v>
+        <v>0.9819876241925661</v>
       </c>
       <c r="L115" t="n">
         <v>-0.1096169878853978</v>
@@ -8858,13 +8858,13 @@
         <v>0.9880204707981585</v>
       </c>
       <c r="I116" t="n">
-        <v>0.9914188190924526</v>
+        <v>0.9913289303611895</v>
       </c>
       <c r="J116" t="n">
         <v>0.9913602682875844</v>
       </c>
       <c r="K116" t="n">
-        <v>0.9907614423500177</v>
+        <v>0.9907884797386597</v>
       </c>
       <c r="L116" t="n">
         <v>0.5749188139382382</v>
@@ -8931,13 +8931,13 @@
         <v>0.9864034584945446</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9870566165438587</v>
+        <v>0.987361300594233</v>
       </c>
       <c r="J117" t="n">
         <v>0.9779659459498008</v>
       </c>
       <c r="K117" t="n">
-        <v>0.9818476886648675</v>
+        <v>0.9822040130008834</v>
       </c>
       <c r="L117" t="n">
         <v>-0.5370606658832376</v>
@@ -9004,13 +9004,13 @@
         <v>0.9794476579428474</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9820462668309594</v>
+        <v>0.9895823945275486</v>
       </c>
       <c r="J118" t="n">
         <v>0.9641623915742111</v>
       </c>
       <c r="K118" t="n">
-        <v>0.9782483004075341</v>
+        <v>0.9856665716922525</v>
       </c>
       <c r="L118" t="n">
         <v>-3.626855520131396</v>
@@ -9077,13 +9077,13 @@
         <v>0.9831686753283008</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9888880623919533</v>
+        <v>0.9893164097036903</v>
       </c>
       <c r="J119" t="n">
         <v>0.9626808423316935</v>
       </c>
       <c r="K119" t="n">
-        <v>0.9642943223867156</v>
+        <v>0.9645425927083429</v>
       </c>
       <c r="L119" t="n">
         <v>0.2386099610603775</v>
@@ -9150,13 +9150,13 @@
         <v>0.9222284188813621</v>
       </c>
       <c r="I120" t="n">
-        <v>0.942872009456861</v>
+        <v>0.9433847858561852</v>
       </c>
       <c r="J120" t="n">
         <v>0.8378095698334037</v>
       </c>
       <c r="K120" t="n">
-        <v>0.8611448834849338</v>
+        <v>0.8618962691893918</v>
       </c>
       <c r="L120" t="n">
         <v>1.415349233716116</v>
@@ -9223,13 +9223,13 @@
         <v>0.9226673453469799</v>
       </c>
       <c r="I121" t="n">
-        <v>0.9430512033296627</v>
+        <v>0.9395263163236349</v>
       </c>
       <c r="J121" t="n">
         <v>0.8318027219855723</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8438402111619846</v>
+        <v>0.8362290943029386</v>
       </c>
       <c r="L121" t="n">
         <v>-0.2080023265869152</v>
@@ -9296,13 +9296,13 @@
         <v>0.9617146086840636</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9442930210267295</v>
+        <v>0.9593252890926842</v>
       </c>
       <c r="J122" t="n">
         <v>0.9455208862675365</v>
       </c>
       <c r="K122" t="n">
-        <v>0.9477417689983973</v>
+        <v>0.9616281027964303</v>
       </c>
       <c r="L122" t="n">
         <v>-1.224529637038703</v>
@@ -9369,13 +9369,13 @@
         <v>0.9307528474348624</v>
       </c>
       <c r="I123" t="n">
-        <v>0.94268343126057</v>
+        <v>0.933817552141731</v>
       </c>
       <c r="J123" t="n">
         <v>0.646043008293982</v>
       </c>
       <c r="K123" t="n">
-        <v>0.6277805150881279</v>
+        <v>0.6137239419878794</v>
       </c>
       <c r="L123" t="n">
         <v>35.68071805113103</v>
@@ -9442,13 +9442,13 @@
         <v>0.8871166200130614</v>
       </c>
       <c r="I124" t="n">
-        <v>0.912454605945104</v>
+        <v>0.9228536593474741</v>
       </c>
       <c r="J124" t="n">
         <v>0.7765846155466269</v>
       </c>
       <c r="K124" t="n">
-        <v>0.6706855173315315</v>
+        <v>0.6599686787855796</v>
       </c>
       <c r="L124" t="n">
         <v>7.807711274457489</v>
@@ -9515,13 +9515,13 @@
         <v>0.9496686631194888</v>
       </c>
       <c r="I125" t="n">
-        <v>0.9628177563247164</v>
+        <v>0.9618517984288576</v>
       </c>
       <c r="J125" t="n">
         <v>0.9567995493782506</v>
       </c>
       <c r="K125" t="n">
-        <v>0.970432080527098</v>
+        <v>0.9727129014408951</v>
       </c>
       <c r="L125" t="n">
         <v>-0.1785070810978135</v>
@@ -9588,13 +9588,13 @@
         <v>0.8914574667257523</v>
       </c>
       <c r="I126" t="n">
-        <v>0.9069414764011795</v>
+        <v>0.8961807795808713</v>
       </c>
       <c r="J126" t="n">
         <v>0.6053408251649799</v>
       </c>
       <c r="K126" t="n">
-        <v>0.6129075333222098</v>
+        <v>0.5906057343076945</v>
       </c>
       <c r="L126" t="n">
         <v>11.98313305105714</v>
@@ -9661,13 +9661,13 @@
         <v>0.9498891688784538</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9283842137379847</v>
+        <v>0.9248777936616797</v>
       </c>
       <c r="J127" t="n">
         <v>0.9214953156959456</v>
       </c>
       <c r="K127" t="n">
-        <v>0.8455053260876462</v>
+        <v>0.8391944058063695</v>
       </c>
       <c r="L127" t="n">
         <v>0.9743820982059499</v>
@@ -9734,13 +9734,13 @@
         <v>0.8902670687288543</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9293250095388597</v>
+        <v>0.9436109173660033</v>
       </c>
       <c r="J128" t="n">
         <v>0.9018427458553473</v>
       </c>
       <c r="K128" t="n">
-        <v>0.8190954874447443</v>
+        <v>0.8334136120540182</v>
       </c>
       <c r="L128" t="n">
         <v>-1.103819071228612</v>
@@ -9807,13 +9807,13 @@
         <v>0.9209915505378991</v>
       </c>
       <c r="I129" t="n">
-        <v>0.961507346072651</v>
+        <v>0.9488926693878051</v>
       </c>
       <c r="J129" t="n">
         <v>0.916898270823452</v>
       </c>
       <c r="K129" t="n">
-        <v>0.8159698579517914</v>
+        <v>0.799562659104854</v>
       </c>
       <c r="L129" t="n">
         <v>5.078547098091626</v>
@@ -9880,13 +9880,13 @@
         <v>0.8198598691081508</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8792057181561285</v>
+        <v>0.8662676572660597</v>
       </c>
       <c r="J130" t="n">
         <v>0.9348060212576879</v>
       </c>
       <c r="K130" t="n">
-        <v>0.9016795102115777</v>
+        <v>0.8975194774740543</v>
       </c>
       <c r="L130" t="n">
         <v>0.644274067629103</v>
@@ -9953,13 +9953,13 @@
         <v>0.8915580580551598</v>
       </c>
       <c r="I131" t="n">
-        <v>0.8940085624857316</v>
+        <v>0.8969832028968135</v>
       </c>
       <c r="J131" t="n">
         <v>0.6832362286231244</v>
       </c>
       <c r="K131" t="n">
-        <v>0.6767488200663816</v>
+        <v>0.670999632215301</v>
       </c>
       <c r="L131" t="n">
         <v>23.20285075355689</v>
@@ -10026,13 +10026,13 @@
         <v>0.9606060147057622</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9452086398049784</v>
+        <v>0.9385712269160629</v>
       </c>
       <c r="J132" t="n">
         <v>0.5296291252817421</v>
       </c>
       <c r="K132" t="n">
-        <v>0.4942027505529892</v>
+        <v>0.4794716810707141</v>
       </c>
       <c r="L132" t="n">
         <v>23.0586054696122</v>
@@ -10099,13 +10099,13 @@
         <v>0.9682220641444185</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9472277148076841</v>
+        <v>0.9613054723515849</v>
       </c>
       <c r="J133" t="n">
         <v>0.8957644788216702</v>
       </c>
       <c r="K133" t="n">
-        <v>0.8891830643148253</v>
+        <v>0.9001708912893635</v>
       </c>
       <c r="L133" t="n">
         <v>-0.5228737801711257</v>
@@ -10172,13 +10172,13 @@
         <v>0.9576374152704024</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9549088030554224</v>
+        <v>0.9557356326244245</v>
       </c>
       <c r="J134" t="n">
         <v>0.6291891017625849</v>
       </c>
       <c r="K134" t="n">
-        <v>0.681419677490616</v>
+        <v>0.6805796100950823</v>
       </c>
       <c r="L134" t="n">
         <v>6.09647201553334</v>
@@ -10245,13 +10245,13 @@
         <v>0.9208483665563526</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9393172999575172</v>
+        <v>0.9439898147956709</v>
       </c>
       <c r="J135" t="n">
         <v>0.9112207558086641</v>
       </c>
       <c r="K135" t="n">
-        <v>0.9022556790137422</v>
+        <v>0.9058722665286156</v>
       </c>
       <c r="L135" t="n">
         <v>-0.4165425314789139</v>
@@ -10318,13 +10318,13 @@
         <v>0.9720288126065325</v>
       </c>
       <c r="I136" t="n">
-        <v>0.9799075377812185</v>
+        <v>0.9798812251982769</v>
       </c>
       <c r="J136" t="n">
         <v>0.6382700162309799</v>
       </c>
       <c r="K136" t="n">
-        <v>0.6868774911084219</v>
+        <v>0.6770545210433982</v>
       </c>
       <c r="L136" t="n">
         <v>23.00421932769493</v>
@@ -10391,13 +10391,13 @@
         <v>0.9681139100160303</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9662404692278658</v>
+        <v>0.9705698082067098</v>
       </c>
       <c r="J137" t="n">
         <v>0.9269262931830056</v>
       </c>
       <c r="K137" t="n">
-        <v>0.9412145242170876</v>
+        <v>0.948094153253573</v>
       </c>
       <c r="L137" t="n">
         <v>0.2478778917058954</v>
@@ -10464,13 +10464,13 @@
         <v>0.9844274126410508</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9809802278442254</v>
+        <v>0.9814364012966459</v>
       </c>
       <c r="J138" t="n">
         <v>0.4237422910337682</v>
       </c>
       <c r="K138" t="n">
-        <v>0.3345254896314322</v>
+        <v>0.3261284892333517</v>
       </c>
       <c r="L138" t="n">
         <v>58.17265674559997</v>
@@ -10537,13 +10537,13 @@
         <v>0.9881674008309478</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9856935628953374</v>
+        <v>0.9854820649293061</v>
       </c>
       <c r="J139" t="n">
         <v>0.6774120471869016</v>
       </c>
       <c r="K139" t="n">
-        <v>0.6870348852696693</v>
+        <v>0.6838490914023931</v>
       </c>
       <c r="L139" t="n">
         <v>11.51200395612495</v>
@@ -10610,13 +10610,13 @@
         <v>0.8808236646950579</v>
       </c>
       <c r="I140" t="n">
-        <v>0.9252327779453707</v>
+        <v>0.926334301233642</v>
       </c>
       <c r="J140" t="n">
         <v>0.4720476949310664</v>
       </c>
       <c r="K140" t="n">
-        <v>0.4928442127330489</v>
+        <v>0.484820296185451</v>
       </c>
       <c r="L140" t="n">
         <v>9.058462764842714</v>
@@ -10689,7 +10689,7 @@
         <v>0.9771598841771193</v>
       </c>
       <c r="K141" t="n">
-        <v>0.966668504417591</v>
+        <v>0.9666685044175909</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
@@ -10752,13 +10752,13 @@
         <v>0.8976603124129124</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9058813516735246</v>
+        <v>0.9060883283083991</v>
       </c>
       <c r="J142" t="n">
         <v>0.628474710843386</v>
       </c>
       <c r="K142" t="n">
-        <v>0.6544545514974429</v>
+        <v>0.652155312741322</v>
       </c>
       <c r="L142" t="n">
         <v>19.87096425476178</v>
@@ -10825,13 +10825,13 @@
         <v>0.9643001620431965</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9821929129457144</v>
+        <v>0.9828578935698389</v>
       </c>
       <c r="J143" t="n">
         <v>0.8243188167737956</v>
       </c>
       <c r="K143" t="n">
-        <v>0.7204815130384645</v>
+        <v>0.7144007476165176</v>
       </c>
       <c r="L143" t="n">
         <v>5.227208621196781</v>
@@ -10898,13 +10898,13 @@
         <v>0.8624887507882475</v>
       </c>
       <c r="I144" t="n">
-        <v>0.88727920197009</v>
+        <v>0.8877342011445251</v>
       </c>
       <c r="J144" t="n">
         <v>0.8322231756648512</v>
       </c>
       <c r="K144" t="n">
-        <v>0.8345202118701367</v>
+        <v>0.8359044723847456</v>
       </c>
       <c r="L144" t="n">
         <v>2.477569487998396</v>
@@ -10971,13 +10971,13 @@
         <v>0.8897426380015548</v>
       </c>
       <c r="I145" t="n">
-        <v>0.898500164593806</v>
+        <v>0.9019865339143576</v>
       </c>
       <c r="J145" t="n">
         <v>0.898153998545116</v>
       </c>
       <c r="K145" t="n">
-        <v>0.8865250577638243</v>
+        <v>0.8896684165721219</v>
       </c>
       <c r="L145" t="n">
         <v>-0.1945256725278302</v>
@@ -11044,13 +11044,13 @@
         <v>0.8457985588734399</v>
       </c>
       <c r="I146" t="n">
-        <v>0.9330783948343561</v>
+        <v>0.9114634449684178</v>
       </c>
       <c r="J146" t="n">
         <v>0.8875395705508148</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8565311507370187</v>
+        <v>0.8363347776744712</v>
       </c>
       <c r="L146" t="n">
         <v>8.21800057730905</v>
@@ -11117,13 +11117,13 @@
         <v>0.9396581500159067</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7946017684845508</v>
+        <v>0.8054616605726943</v>
       </c>
       <c r="J147" t="n">
         <v>0.9372025573840848</v>
       </c>
       <c r="K147" t="n">
-        <v>0.7794993846516853</v>
+        <v>0.7837754558500371</v>
       </c>
       <c r="L147" t="n">
         <v>-1.178283734991258</v>
@@ -11190,13 +11190,13 @@
         <v>0.8062726345199401</v>
       </c>
       <c r="I148" t="n">
-        <v>0.931095573596477</v>
+        <v>0.9097264260400019</v>
       </c>
       <c r="J148" t="n">
         <v>0.9170056577822541</v>
       </c>
       <c r="K148" t="n">
-        <v>0.8502937991478721</v>
+        <v>0.82891496565842</v>
       </c>
       <c r="L148" t="n">
         <v>3.033899820285974</v>

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W148"/>
+  <dimension ref="A1:Y148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,35 +494,45 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>modality_index_fitted</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>modality_index_fitted_uw</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>modality_index_uw</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>skewness</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>skewness_uw</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>w_v_uw_wasserstein</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>weight_outliers</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>weight_outliers_uw</t>
         </is>
@@ -580,24 +590,30 @@
         <v>1.000620436533473</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.002919141802814</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.040928943346033</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.028084151618127</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>53</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.5055559928364058</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>1.461183341175216</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.1206664306903695</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.002196022764953359</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.01886792452830189</v>
       </c>
     </row>
@@ -656,21 +672,27 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>13</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.7530917292035287</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.7895028742751836</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0803901182218877</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -726,24 +748,30 @@
         <v>1.009324433257974</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.116543596016872</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.074827170779614</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.008822288055942</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>412</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>5.74887852611989</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>5.27016477638714</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.09292574718589587</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.140549183598032</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.145631067961165</v>
       </c>
     </row>
@@ -799,24 +827,30 @@
         <v>1.008711585171832</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.095540906498907</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.106463291044453</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.005654889400433</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>378</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>12.47391859992324</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>15.89024336735051</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.351266000254556</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.1069043690585924</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.126984126984127</v>
       </c>
     </row>
@@ -872,24 +906,30 @@
         <v>1.020427907769703</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.099904119101732</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.034609716389288</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.017329270759607</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>120</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>1.990921907563031</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>2.236995624420989</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.06714912019288702</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.05091374499805163</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -945,24 +985,30 @@
         <v>1.073893286310778</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.13587012755561</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.159210556004727</v>
+      </c>
+      <c r="S7" t="n">
         <v>1.070504973760363</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>36</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>2.511320968056919</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>2.521743750247535</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.08005163988094979</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.06494546106111922</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -1021,21 +1067,27 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
+        <v>1.003307479763752</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
         <v>26</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>1.209131487943906</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>1.074252399930125</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.08218354278050689</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.02872847209371049</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.03846153846153846</v>
       </c>
     </row>
@@ -1090,21 +1142,27 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>-1.607850114171004</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>-0.06168301151315891</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.1978968655652941</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1160,24 +1218,30 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.017274075189011</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.094247496742057</v>
+      </c>
+      <c r="S10" t="n">
         <v>1.020400589490248</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>22</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1.55935795781015</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>1.927573330141693</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.2164893301478635</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.06955559152005275</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.04545454545454546</v>
       </c>
     </row>
@@ -1233,24 +1297,30 @@
         <v>1.006906185453408</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.026990142974648</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.025951272610127</v>
+      </c>
+      <c r="S11" t="n">
         <v>1.009154565156715</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>7232</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>1.539305885574346</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>1.622828497672506</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.004927035618183227</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.04465301340866516</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.04549225663716815</v>
       </c>
     </row>
@@ -1306,24 +1376,30 @@
         <v>1.014305464443179</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.131208644500611</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.137314367612276</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.037033785089428</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>45</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>2.272252795914303</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>2.585468631620784</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1107829961985174</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.1200306044386614</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -1379,24 +1455,30 @@
         <v>1.02777495185325</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.046195620518623</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.049153364533274</v>
+      </c>
+      <c r="S13" t="n">
         <v>1.022207261993878</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>66</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>2.69821941981011</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>2.661886929699789</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.07221369851198846</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.03124815386321646</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>0.06060606060606061</v>
       </c>
     </row>
@@ -1452,24 +1534,30 @@
         <v>1.023729138627498</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.033341357141168</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.095848139130641</v>
+      </c>
+      <c r="S14" t="n">
         <v>1.060576411318667</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>28</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>1.693468329435929</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>1.961356233856485</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.1822990286817721</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.02142453697571388</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.07142857142857142</v>
       </c>
     </row>
@@ -1525,24 +1613,30 @@
         <v>1.033602787502073</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.059514372674616</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.098512757175423</v>
+      </c>
+      <c r="S15" t="n">
         <v>1.053545989607294</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>184</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>3.770015022130187</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>3.295714006834492</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.1079311911602625</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.08115158458739555</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.1032608695652174</v>
       </c>
     </row>
@@ -1597,21 +1691,27 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>-2.408055299343783</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.3454290422676277</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.4473809483591363</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.009585263433586294</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1667,24 +1767,30 @@
         <v>1.015034728294856</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.156544102436062</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.090605257640002</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.012983759217844</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>129</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>3.661356811908116</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>3.034063038417906</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.1000670807739838</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.1103714224572816</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>0.124031007751938</v>
       </c>
     </row>
@@ -1736,24 +1842,30 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>1.013406329542018</v>
       </c>
       <c r="R18" t="n">
+        <v>1.057622670936796</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>1.403204225694987</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>1.723939960012797</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.09293681618496408</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.3622193416706191</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1812,21 +1924,27 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
+        <v>1.012602226728975</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>16</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>1.572077098824211</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>1.752237368192879</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.1009550048599212</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.2928877575166959</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.1875</v>
       </c>
     </row>
@@ -1882,24 +2000,30 @@
         <v>1.014634506552205</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.106419535506455</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.093883842034411</v>
+      </c>
+      <c r="S20" t="n">
         <v>1.028183096469301</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>47</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>2.455646300002948</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>4.642303052486983</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.2390342570685982</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.104032678536985</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>0.06382978723404255</v>
       </c>
     </row>
@@ -1955,24 +2079,30 @@
         <v>1.005537742602281</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.083049042452673</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.102597468904421</v>
+      </c>
+      <c r="S21" t="n">
         <v>1.040669813376224</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>50</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>2.524094470752425</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>3.155293575475566</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.2072051777733712</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.01874995609919143</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -2028,24 +2158,30 @@
         <v>1.066029952148684</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.098449664562807</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.064137881756209</v>
+      </c>
+      <c r="S22" t="n">
         <v>1.052024790847023</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>19</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>2.302727786879513</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>2.877693680470466</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.2391802240072229</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.1569488419598211</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.1578947368421053</v>
       </c>
     </row>
@@ -2101,24 +2237,30 @@
         <v>1.011534246310978</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.02175176566222</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.064295313634011</v>
+      </c>
+      <c r="S23" t="n">
         <v>1.020510203801384</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>77</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>1.871186684698199</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>2.583745260052714</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.1072269630465033</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.04419986790538884</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.06493506493506494</v>
       </c>
     </row>
@@ -2174,24 +2316,30 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.05048745091216</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.088037776533685</v>
+      </c>
+      <c r="S24" t="n">
         <v>1.000210728854058</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>1.488142555963109</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.8120566187453548</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1898109759197049</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.206240334248346</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2247,24 +2395,30 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>1.00996788716746</v>
       </c>
       <c r="R25" t="n">
+        <v>1.00044850973277</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>131</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>1.504831813826573</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>1.314514399256055</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1050724941797343</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.05559657563739673</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.03816793893129771</v>
       </c>
     </row>
@@ -2320,24 +2474,30 @@
         <v>1.015534430173189</v>
       </c>
       <c r="Q26" t="n">
+        <v>1.113653584861552</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.146520993992054</v>
+      </c>
+      <c r="S26" t="n">
         <v>1.020311499581628</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>215</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>6.277880247989138</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>5.45466445904876</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.0875479568364488</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.05631445849468775</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>0.08837209302325581</v>
       </c>
     </row>
@@ -2396,21 +2556,27 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
         <v>137</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.4757050084552138</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.5846912657648252</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.03950705212224796</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.0364963503649635</v>
       </c>
     </row>
@@ -2466,24 +2632,30 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.027238466191349</v>
       </c>
       <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
         <v>18</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>-0.09390159819682313</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.7240351781114304</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>0.1815312296410238</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -2539,24 +2711,30 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>1.000003669999206</v>
       </c>
       <c r="R29" t="n">
+        <v>1.017250456803104</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
         <v>8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.9656589248628967</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.9465448107117128</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.03208152264184194</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.351989492901186</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -2612,24 +2790,30 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
+        <v>1.013718006865077</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.016649198754034</v>
+      </c>
+      <c r="S30" t="n">
         <v>1.004047425114218</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>274</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>1.127859422781441</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>1.226260681961135</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.02902988644830346</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.02361772091223975</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.04014598540145986</v>
       </c>
     </row>
@@ -2688,21 +2872,27 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>-0.4052674887367588</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>0.4420529837320132</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.08047972250136683</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2758,24 +2948,30 @@
         <v>1.027628536119987</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.046373941141127</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.089840870387961</v>
+      </c>
+      <c r="S32" t="n">
         <v>1.02100698543268</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>39</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>1.362560404566828</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.9604788284988173</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.0647332027621435</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.03094931004082265</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.05128205128205128</v>
       </c>
     </row>
@@ -2831,24 +3027,30 @@
         <v>1.019142037573903</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.09532355711025</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.123139887123249</v>
+      </c>
+      <c r="S33" t="n">
         <v>1.035324952445202</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>59</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>2.638774868963251</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>2.903627280708979</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.1060709432827253</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.1009880525259774</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.1016949152542373</v>
       </c>
     </row>
@@ -2904,24 +3106,30 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.011916826192858</v>
+      </c>
+      <c r="S34" t="n">
         <v>1.000632724474762</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1989</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.7670328673943061</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.7715951216898859</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.007908530719415089</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.0057759322541225</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.004022121669180492</v>
       </c>
     </row>
@@ -2977,24 +3185,30 @@
         <v>1.00861433768052</v>
       </c>
       <c r="Q35" t="n">
+        <v>1.011093229986055</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.012689686580874</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.010357082602073</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>255</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.9135146875010787</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.8732279709955294</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.01372963505353348</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.006213803795699154</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.007843137254901961</v>
       </c>
     </row>
@@ -3050,24 +3264,30 @@
         <v>1.012825415429883</v>
       </c>
       <c r="Q36" t="n">
+        <v>1.027221487223966</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.013873069787575</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.007902376243321</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1084</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>2.126514049803474</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>1.923788942613817</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.01479881726374722</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.02438209250151993</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.02214022140221402</v>
       </c>
     </row>
@@ -3126,21 +3346,27 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
+        <v>1.08355843659071</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
         <v>21</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>1.127839796201303</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>1.079351294021625</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.0535503531891449</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.1089635645236065</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -3196,24 +3422,30 @@
         <v>1.009671000409691</v>
       </c>
       <c r="Q38" t="n">
+        <v>1.027542019018279</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.026112799374688</v>
+      </c>
+      <c r="S38" t="n">
         <v>1.006566987101052</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>3764</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>2.410313826200075</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>2.235647251286485</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.005559990021817771</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.04156445286993656</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>0.04330499468650371</v>
       </c>
     </row>
@@ -3269,24 +3501,30 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
+        <v>1.006298309679696</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.058873363791751</v>
+      </c>
+      <c r="S39" t="n">
         <v>1.00087461731477</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>51</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>1.067023445337853</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.7344470257292786</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1230841204921866</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.06234354464083428</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3342,24 +3580,30 @@
         <v>1.014350614475351</v>
       </c>
       <c r="Q40" t="n">
+        <v>1.056382374301643</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.09145096882896</v>
+      </c>
+      <c r="S40" t="n">
         <v>1.016613509646723</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>140</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>1.698254428591839</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>2.727069475997609</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.1200468369461516</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.04307123148709055</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.03571428571428571</v>
       </c>
     </row>
@@ -3415,24 +3659,30 @@
         <v>1.000972158364715</v>
       </c>
       <c r="Q41" t="n">
+        <v>1.017598853304019</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.042367564508245</v>
+      </c>
+      <c r="S41" t="n">
         <v>1.012742172720376</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>16</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>1.302488746895526</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>1.511519705875827</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.1199898516714999</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.03173631284532331</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.0625</v>
       </c>
     </row>
@@ -3484,24 +3734,30 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>1.008765690641969</v>
       </c>
       <c r="R42" t="n">
+        <v>1.057876707721886</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>3</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>-2.204914039740777</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>-1.726782879068862</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.06045842239259847</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3557,24 +3813,30 @@
         <v>1.001727801476282</v>
       </c>
       <c r="Q43" t="n">
+        <v>1.09232396967484</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.047501299852954</v>
+      </c>
+      <c r="S43" t="n">
         <v>1.009314532090233</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>118</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>21.00044240500776</v>
       </c>
-      <c r="T43" t="n">
+      <c r="V43" t="n">
         <v>10.32134715862402</v>
       </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
         <v>0.3128113486015235</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>0.1376199404576909</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>0.06779661016949153</v>
       </c>
     </row>
@@ -3630,24 +3892,30 @@
         <v>1.002885110098406</v>
       </c>
       <c r="Q44" t="n">
+        <v>1.046510918511113</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.108872813947392</v>
+      </c>
+      <c r="S44" t="n">
         <v>1.038158406294417</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>108</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>-0.007461871721663946</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
         <v>0.02556958988775621</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>0.01345279558102345</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3706,21 +3974,27 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
+        <v>1.002564935690344</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>160</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.5560907260138543</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.5162326263362352</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.01033273241913193</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.04714111883164622</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3776,24 +4050,30 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
+        <v>1.002328651104705</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.294511300559417</v>
+      </c>
+      <c r="S46" t="n">
         <v>1.1433136350713</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>42</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.52631220553586</v>
       </c>
-      <c r="T46" t="n">
+      <c r="V46" t="n">
         <v>0.1935692353468302</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>0.08018509400284</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3852,21 +4132,27 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
         <v>32</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>-0.4005626429073495</v>
       </c>
-      <c r="T47" t="n">
+      <c r="V47" t="n">
         <v>-0.09195920820334415</v>
       </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
         <v>0.04587775555374374</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3922,24 +4208,30 @@
         <v>1.005193670477615</v>
       </c>
       <c r="Q48" t="n">
+        <v>1.005749682366869</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.140283965988981</v>
+      </c>
+      <c r="S48" t="n">
         <v>1.07071058825641</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>38</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>2.448691851268712</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>3.019765767365735</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1518645091905205</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.002862189341912476</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>0.05263157894736842</v>
       </c>
     </row>
@@ -3995,24 +4287,30 @@
         <v>1.039897316481201</v>
       </c>
       <c r="Q49" t="n">
+        <v>1.048696211427896</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.056382196913695</v>
+      </c>
+      <c r="S49" t="n">
         <v>1.047719077478554</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>76</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
         <v>3.083408821178731</v>
       </c>
-      <c r="T49" t="n">
+      <c r="V49" t="n">
         <v>2.602967166025265</v>
       </c>
-      <c r="U49" t="n">
+      <c r="W49" t="n">
         <v>0.1791308530415744</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.02735022407140891</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>0.02631578947368421</v>
       </c>
     </row>
@@ -4068,24 +4366,30 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
+        <v>1.012116486556456</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.064229761868608</v>
+      </c>
+      <c r="S50" t="n">
         <v>1.020328607656752</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>54</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>1.724004546722429</v>
       </c>
-      <c r="T50" t="n">
+      <c r="V50" t="n">
         <v>2.241966107715531</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>0.08949046197243843</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.01853070626248618</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -4141,24 +4445,30 @@
         <v>1.017383170594464</v>
       </c>
       <c r="Q51" t="n">
+        <v>1.23076445991246</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.144649805670209</v>
+      </c>
+      <c r="S51" t="n">
         <v>1.023438953331128</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>162</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>5.473583828821956</v>
       </c>
-      <c r="T51" t="n">
+      <c r="V51" t="n">
         <v>4.915243722103843</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>0.1291129016722848</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.1079022522102031</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.08024691358024691</v>
       </c>
     </row>
@@ -4214,24 +4524,30 @@
         <v>1.008843969529432</v>
       </c>
       <c r="Q52" t="n">
+        <v>1.103340147886353</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.055061851730484</v>
+      </c>
+      <c r="S52" t="n">
         <v>1.009498219147334</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>951</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>3.187199359184635</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
         <v>3.489251283955535</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>0.1063572780686947</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.1597487521790868</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>0.1345951629863302</v>
       </c>
     </row>
@@ -4287,24 +4603,30 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>1.004884933958579</v>
       </c>
       <c r="R53" t="n">
+        <v>1.033306594592258</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
         <v>7</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>1.039221365288698</v>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
         <v>1.631002075549539</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>0.2212946589811221</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>0.2068046996074279</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -4360,24 +4682,30 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
+        <v>1.098297177539781</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.097390961791228</v>
+      </c>
+      <c r="S54" t="n">
         <v>1.005950304274737</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>62</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>-0.02184847599909169</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>-0.3913008871117882</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.03957860412623309</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>0.1144382119414316</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>0.01612903225806452</v>
       </c>
     </row>
@@ -4433,24 +4761,30 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>1.038019637887855</v>
       </c>
       <c r="R55" t="n">
+        <v>1.020579265628141</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
         <v>4</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.04531683107253322</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>0.3555428479640818</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>0.1453466336322329</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4506,24 +4840,30 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
+        <v>1.004561603215922</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.016521835670317</v>
+      </c>
+      <c r="S56" t="n">
         <v>1.001153610713452</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>45</v>
       </c>
-      <c r="S56" t="n">
+      <c r="U56" t="n">
         <v>0.115363779849785</v>
       </c>
-      <c r="T56" t="n">
+      <c r="V56" t="n">
         <v>0.3490599321787082</v>
       </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
         <v>0.04658168956995385</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>0</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>0.02222222222222222</v>
       </c>
     </row>
@@ -4579,24 +4919,30 @@
         <v>1.022007001501929</v>
       </c>
       <c r="Q57" t="n">
+        <v>1.027953125986906</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.119521690979794</v>
+      </c>
+      <c r="S57" t="n">
         <v>1.025420395412684</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>61</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
         <v>3.355789137772274</v>
       </c>
-      <c r="T57" t="n">
+      <c r="V57" t="n">
         <v>2.790024305487965</v>
       </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
         <v>0.1735973821850731</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.01892385248884134</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>0.08196721311475411</v>
       </c>
     </row>
@@ -4648,24 +4994,30 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>1.002333852136169</v>
       </c>
       <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
         <v>3</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
         <v>5.516159551846683</v>
       </c>
-      <c r="T58" t="n">
+      <c r="V58" t="n">
         <v>0.6973106571137119</v>
       </c>
-      <c r="U58" t="n">
+      <c r="W58" t="n">
         <v>0.009230255466642488</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>0.2482240629063026</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4721,24 +5073,30 @@
         <v>1.030812974708947</v>
       </c>
       <c r="Q59" t="n">
+        <v>1.037934568265378</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.241365995508224</v>
+      </c>
+      <c r="S59" t="n">
         <v>1.053539405537984</v>
       </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>20</v>
       </c>
-      <c r="S59" t="n">
+      <c r="U59" t="n">
         <v>2.851938276063051</v>
       </c>
-      <c r="T59" t="n">
+      <c r="V59" t="n">
         <v>2.727836334067292</v>
       </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
         <v>0.1949146510083789</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>0.2184653199952523</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Y59" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -4794,24 +5152,30 @@
         <v>1.052378260124975</v>
       </c>
       <c r="Q60" t="n">
+        <v>1.064113369083765</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.083310078616668</v>
+      </c>
+      <c r="S60" t="n">
         <v>1.070921741429366</v>
       </c>
-      <c r="R60" t="n">
+      <c r="T60" t="n">
         <v>17</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>3.450871156035974</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>3.013950285037438</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1809329561066492</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>0.05535073160296863</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Y60" t="n">
         <v>0.05882352941176471</v>
       </c>
     </row>
@@ -4867,24 +5231,30 @@
         <v>1.00876289148698</v>
       </c>
       <c r="Q61" t="n">
+        <v>1.046330399116732</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.041323597038271</v>
+      </c>
+      <c r="S61" t="n">
         <v>1.007126677254597</v>
       </c>
-      <c r="R61" t="n">
+      <c r="T61" t="n">
         <v>259</v>
       </c>
-      <c r="S61" t="n">
+      <c r="U61" t="n">
         <v>4.935740660741186</v>
       </c>
-      <c r="T61" t="n">
+      <c r="V61" t="n">
         <v>5.291879387314282</v>
       </c>
-      <c r="U61" t="n">
+      <c r="W61" t="n">
         <v>0.07834686163228112</v>
       </c>
-      <c r="V61" t="n">
+      <c r="X61" t="n">
         <v>0.05959169416214936</v>
       </c>
-      <c r="W61" t="n">
+      <c r="Y61" t="n">
         <v>0.04633204633204633</v>
       </c>
     </row>
@@ -4940,24 +5310,30 @@
         <v>1.018191714776728</v>
       </c>
       <c r="Q62" t="n">
+        <v>1.023298248971543</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.09524882328101</v>
+      </c>
+      <c r="S62" t="n">
         <v>1.063776019084027</v>
       </c>
-      <c r="R62" t="n">
+      <c r="T62" t="n">
         <v>29</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>2.081827810671911</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>2.229258086043538</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.0948165967610959</v>
       </c>
-      <c r="V62" t="n">
+      <c r="X62" t="n">
         <v>0.01785377709729447</v>
       </c>
-      <c r="W62" t="n">
+      <c r="Y62" t="n">
         <v>0.06896551724137931</v>
       </c>
     </row>
@@ -5013,24 +5389,30 @@
         <v>1.014595909306912</v>
       </c>
       <c r="Q63" t="n">
+        <v>1.067973456109019</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.215258947895359</v>
+      </c>
+      <c r="S63" t="n">
         <v>1.039811505058307</v>
       </c>
-      <c r="R63" t="n">
+      <c r="T63" t="n">
         <v>22</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>1.331159926074473</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>1.711861715935024</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1907914557894293</v>
       </c>
-      <c r="V63" t="n">
+      <c r="X63" t="n">
         <v>0.1580185113163807</v>
       </c>
-      <c r="W63" t="n">
+      <c r="Y63" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -5086,24 +5468,30 @@
         <v>1.06100783406863</v>
       </c>
       <c r="Q64" t="n">
+        <v>1.096232872227099</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.035588750455214</v>
+      </c>
+      <c r="S64" t="n">
         <v>1.013689516213896</v>
       </c>
-      <c r="R64" t="n">
+      <c r="T64" t="n">
         <v>12</v>
       </c>
-      <c r="S64" t="n">
+      <c r="U64" t="n">
         <v>2.458938843451774</v>
       </c>
-      <c r="T64" t="n">
+      <c r="V64" t="n">
         <v>2.428340489880003</v>
       </c>
-      <c r="U64" t="n">
+      <c r="W64" t="n">
         <v>0.1683324397336313</v>
       </c>
-      <c r="V64" t="n">
+      <c r="X64" t="n">
         <v>0.1334486670515767</v>
       </c>
-      <c r="W64" t="n">
+      <c r="Y64" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -5159,24 +5547,30 @@
         <v>1.001843333073003</v>
       </c>
       <c r="Q65" t="n">
+        <v>1.002046130566331</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.070308258708538</v>
+      </c>
+      <c r="S65" t="n">
         <v>1.031453791401421</v>
       </c>
-      <c r="R65" t="n">
+      <c r="T65" t="n">
         <v>47</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>1.578965150762764</v>
       </c>
-      <c r="T65" t="n">
+      <c r="V65" t="n">
         <v>3.178504809515282</v>
       </c>
-      <c r="U65" t="n">
+      <c r="W65" t="n">
         <v>0.1737650922690964</v>
       </c>
-      <c r="V65" t="n">
+      <c r="X65" t="n">
         <v>0.01847555392380641</v>
       </c>
-      <c r="W65" t="n">
+      <c r="Y65" t="n">
         <v>0.0851063829787234</v>
       </c>
     </row>
@@ -5232,24 +5626,30 @@
         <v>1.012901020806906</v>
       </c>
       <c r="Q66" t="n">
+        <v>1.072438028869295</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.044157757569472</v>
+      </c>
+      <c r="S66" t="n">
         <v>1.015013990405764</v>
       </c>
-      <c r="R66" t="n">
+      <c r="T66" t="n">
         <v>2008</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>3.443894096115796</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>3.107484765804786</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.02580578857914404</v>
       </c>
-      <c r="V66" t="n">
+      <c r="X66" t="n">
         <v>0.05566839927327558</v>
       </c>
-      <c r="W66" t="n">
+      <c r="Y66" t="n">
         <v>0.05229083665338644</v>
       </c>
     </row>
@@ -5305,24 +5705,30 @@
         <v>1.001895341750661</v>
       </c>
       <c r="Q67" t="n">
+        <v>1.1187161850272</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.110626358499225</v>
+      </c>
+      <c r="S67" t="n">
         <v>1.062138097491245</v>
       </c>
-      <c r="R67" t="n">
+      <c r="T67" t="n">
         <v>8</v>
       </c>
-      <c r="S67" t="n">
+      <c r="U67" t="n">
         <v>0.5199289352658198</v>
       </c>
-      <c r="T67" t="n">
+      <c r="V67" t="n">
         <v>2.460609840211285</v>
       </c>
-      <c r="U67" t="n">
+      <c r="W67" t="n">
         <v>0.7301746111115792</v>
       </c>
-      <c r="V67" t="n">
+      <c r="X67" t="n">
         <v>0</v>
       </c>
-      <c r="W67" t="n">
+      <c r="Y67" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -5381,21 +5787,27 @@
         <v>1</v>
       </c>
       <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
         <v>5</v>
       </c>
-      <c r="S68" t="n">
+      <c r="U68" t="n">
         <v>-1.050199580675295</v>
       </c>
-      <c r="T68" t="n">
+      <c r="V68" t="n">
         <v>-0.5785605714164811</v>
       </c>
-      <c r="U68" t="n">
+      <c r="W68" t="n">
         <v>0.03240376623317692</v>
       </c>
-      <c r="V68" t="n">
+      <c r="X68" t="n">
         <v>0.2646228087363876</v>
       </c>
-      <c r="W68" t="n">
+      <c r="Y68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5451,24 +5863,30 @@
         <v>1.002469130207169</v>
       </c>
       <c r="Q69" t="n">
+        <v>1.108740666631194</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.153383813200439</v>
+      </c>
+      <c r="S69" t="n">
         <v>1.026295240812482</v>
       </c>
-      <c r="R69" t="n">
+      <c r="T69" t="n">
         <v>7</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>-0.1922223314029115</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>-0.2582741459464289</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.0454286774304016</v>
       </c>
-      <c r="V69" t="n">
+      <c r="X69" t="n">
         <v>0</v>
       </c>
-      <c r="W69" t="n">
+      <c r="Y69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5524,24 +5942,30 @@
         <v>1.018750354018006</v>
       </c>
       <c r="Q70" t="n">
+        <v>1.028187712379764</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.037034672543807</v>
+      </c>
+      <c r="S70" t="n">
         <v>1.023207025568986</v>
       </c>
-      <c r="R70" t="n">
+      <c r="T70" t="n">
         <v>141</v>
       </c>
-      <c r="S70" t="n">
+      <c r="U70" t="n">
         <v>4.825695052249907</v>
       </c>
-      <c r="T70" t="n">
+      <c r="V70" t="n">
         <v>4.208242131636735</v>
       </c>
-      <c r="U70" t="n">
+      <c r="W70" t="n">
         <v>0.08516884928519435</v>
       </c>
-      <c r="V70" t="n">
+      <c r="X70" t="n">
         <v>0.039619556282167</v>
       </c>
-      <c r="W70" t="n">
+      <c r="Y70" t="n">
         <v>0.05673758865248227</v>
       </c>
     </row>
@@ -5597,24 +6021,30 @@
         <v>1.010317259173745</v>
       </c>
       <c r="Q71" t="n">
+        <v>1.033092025542666</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.029419651223312</v>
+      </c>
+      <c r="S71" t="n">
         <v>1.012630819694899</v>
       </c>
-      <c r="R71" t="n">
+      <c r="T71" t="n">
         <v>771</v>
       </c>
-      <c r="S71" t="n">
+      <c r="U71" t="n">
         <v>3.722131837509062</v>
       </c>
-      <c r="T71" t="n">
+      <c r="V71" t="n">
         <v>4.02568946550828</v>
       </c>
-      <c r="U71" t="n">
+      <c r="W71" t="n">
         <v>0.01869222154084405</v>
       </c>
-      <c r="V71" t="n">
+      <c r="X71" t="n">
         <v>0.04095815015005171</v>
       </c>
-      <c r="W71" t="n">
+      <c r="Y71" t="n">
         <v>0.04020752269779509</v>
       </c>
     </row>
@@ -5670,24 +6100,30 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>1.019699398411178</v>
       </c>
       <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>19</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>-0.06987609014801499</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.4202646111685494</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1306888073151825</v>
       </c>
-      <c r="V72" t="n">
+      <c r="X72" t="n">
         <v>0</v>
       </c>
-      <c r="W72" t="n">
+      <c r="Y72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5743,24 +6179,30 @@
         <v>1.000260624720239</v>
       </c>
       <c r="Q73" t="n">
+        <v>1.110793667579346</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.198043022811949</v>
+      </c>
+      <c r="S73" t="n">
         <v>1.042738860871003</v>
       </c>
-      <c r="R73" t="n">
+      <c r="T73" t="n">
         <v>5</v>
       </c>
-      <c r="S73" t="n">
+      <c r="U73" t="n">
         <v>0.7953050367946825</v>
       </c>
-      <c r="T73" t="n">
+      <c r="V73" t="n">
         <v>0.6034631353246369</v>
       </c>
-      <c r="U73" t="n">
+      <c r="W73" t="n">
         <v>0.06916503535285783</v>
       </c>
-      <c r="V73" t="n">
+      <c r="X73" t="n">
         <v>0</v>
       </c>
-      <c r="W73" t="n">
+      <c r="Y73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5816,24 +6258,30 @@
         <v>1.043773657410399</v>
       </c>
       <c r="Q74" t="n">
+        <v>1.054538072993535</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.021528086323941</v>
+      </c>
+      <c r="S74" t="n">
         <v>1.017996896730805</v>
       </c>
-      <c r="R74" t="n">
+      <c r="T74" t="n">
         <v>145</v>
       </c>
-      <c r="S74" t="n">
+      <c r="U74" t="n">
         <v>1.666173787228166</v>
       </c>
-      <c r="T74" t="n">
+      <c r="V74" t="n">
         <v>1.054903540915502</v>
       </c>
-      <c r="U74" t="n">
+      <c r="W74" t="n">
         <v>0.0456876547301234</v>
       </c>
-      <c r="V74" t="n">
+      <c r="X74" t="n">
         <v>0.01945676213047577</v>
       </c>
-      <c r="W74" t="n">
+      <c r="Y74" t="n">
         <v>0.006896551724137931</v>
       </c>
     </row>
@@ -5889,24 +6337,30 @@
         <v>1.027373402013235</v>
       </c>
       <c r="Q75" t="n">
+        <v>1.234070381423914</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.299183612446371</v>
+      </c>
+      <c r="S75" t="n">
         <v>1.035419072932095</v>
       </c>
-      <c r="R75" t="n">
+      <c r="T75" t="n">
         <v>81</v>
       </c>
-      <c r="S75" t="n">
+      <c r="U75" t="n">
         <v>2.402356986868879</v>
       </c>
-      <c r="T75" t="n">
+      <c r="V75" t="n">
         <v>2.508780357651325</v>
       </c>
-      <c r="U75" t="n">
+      <c r="W75" t="n">
         <v>0.08824626218939602</v>
       </c>
-      <c r="V75" t="n">
+      <c r="X75" t="n">
         <v>0.1207698448762107</v>
       </c>
-      <c r="W75" t="n">
+      <c r="Y75" t="n">
         <v>0.1604938271604938</v>
       </c>
     </row>
@@ -5962,24 +6416,30 @@
         <v>1.000399035486704</v>
       </c>
       <c r="Q76" t="n">
+        <v>1.002678270138146</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.01472471618983</v>
+      </c>
+      <c r="S76" t="n">
         <v>1.00935474362358</v>
       </c>
-      <c r="R76" t="n">
+      <c r="T76" t="n">
         <v>271</v>
       </c>
-      <c r="S76" t="n">
+      <c r="U76" t="n">
         <v>0.5098860661524947</v>
       </c>
-      <c r="T76" t="n">
+      <c r="V76" t="n">
         <v>0.7725052913980877</v>
       </c>
-      <c r="U76" t="n">
+      <c r="W76" t="n">
         <v>0.02609509120518377</v>
       </c>
-      <c r="V76" t="n">
+      <c r="X76" t="n">
         <v>0.02436169419646687</v>
       </c>
-      <c r="W76" t="n">
+      <c r="Y76" t="n">
         <v>0.01845018450184502</v>
       </c>
     </row>
@@ -6035,24 +6495,30 @@
         <v>1.000261653562781</v>
       </c>
       <c r="Q77" t="n">
+        <v>1.009355094860997</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.008408193453572</v>
+      </c>
+      <c r="S77" t="n">
         <v>1.006702423634908</v>
       </c>
-      <c r="R77" t="n">
+      <c r="T77" t="n">
         <v>420</v>
       </c>
-      <c r="S77" t="n">
+      <c r="U77" t="n">
         <v>0.706464293965009</v>
       </c>
-      <c r="T77" t="n">
+      <c r="V77" t="n">
         <v>2.110327213800228</v>
       </c>
-      <c r="U77" t="n">
+      <c r="W77" t="n">
         <v>0.01839549968895671</v>
       </c>
-      <c r="V77" t="n">
+      <c r="X77" t="n">
         <v>0.008563272112536574</v>
       </c>
-      <c r="W77" t="n">
+      <c r="Y77" t="n">
         <v>0.01428571428571429</v>
       </c>
     </row>
@@ -6108,24 +6574,30 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
+        <v>1.249367800114113</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.139678607190467</v>
+      </c>
+      <c r="S78" t="n">
         <v>1.006423424039746</v>
       </c>
-      <c r="R78" t="n">
+      <c r="T78" t="n">
         <v>32</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>2.050474914331228</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>1.937953395526726</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.06573107200586986</v>
       </c>
-      <c r="V78" t="n">
+      <c r="X78" t="n">
         <v>0.2213137708039125</v>
       </c>
-      <c r="W78" t="n">
+      <c r="Y78" t="n">
         <v>0.15625</v>
       </c>
     </row>
@@ -6181,24 +6653,30 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>1.040534409130175</v>
       </c>
       <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="S79" t="n">
+      <c r="U79" t="n">
         <v>-0.5722293410977389</v>
       </c>
-      <c r="T79" t="n">
+      <c r="V79" t="n">
         <v>-0.2304468403114039</v>
       </c>
-      <c r="U79" t="n">
+      <c r="W79" t="n">
         <v>0.07420497310756777</v>
       </c>
-      <c r="V79" t="n">
+      <c r="X79" t="n">
         <v>0</v>
       </c>
-      <c r="W79" t="n">
+      <c r="Y79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6257,21 +6735,27 @@
         <v>1</v>
       </c>
       <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
         <v>26</v>
       </c>
-      <c r="S80" t="n">
+      <c r="U80" t="n">
         <v>0.6796374152662644</v>
       </c>
-      <c r="T80" t="n">
+      <c r="V80" t="n">
         <v>0.882568457528503</v>
       </c>
-      <c r="U80" t="n">
+      <c r="W80" t="n">
         <v>0.0761603249518992</v>
       </c>
-      <c r="V80" t="n">
+      <c r="X80" t="n">
         <v>0</v>
       </c>
-      <c r="W80" t="n">
+      <c r="Y80" t="n">
         <v>0.03846153846153846</v>
       </c>
     </row>
@@ -6327,24 +6811,30 @@
         <v>1.030572122238322</v>
       </c>
       <c r="Q81" t="n">
+        <v>1.143239699875436</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1.098696964806258</v>
+      </c>
+      <c r="S81" t="n">
         <v>1.025866133362981</v>
       </c>
-      <c r="R81" t="n">
+      <c r="T81" t="n">
         <v>40</v>
       </c>
-      <c r="S81" t="n">
+      <c r="U81" t="n">
         <v>3.942741928582689</v>
       </c>
-      <c r="T81" t="n">
+      <c r="V81" t="n">
         <v>2.759513275496998</v>
       </c>
-      <c r="U81" t="n">
+      <c r="W81" t="n">
         <v>0.1598801806230219</v>
       </c>
-      <c r="V81" t="n">
+      <c r="X81" t="n">
         <v>0.07336827058058697</v>
       </c>
-      <c r="W81" t="n">
+      <c r="Y81" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -6400,24 +6890,30 @@
         <v>1.024523510585554</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>1.04891641457553</v>
       </c>
       <c r="R82" t="n">
+        <v>1.05127383074672</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
         <v>26</v>
       </c>
-      <c r="S82" t="n">
+      <c r="U82" t="n">
         <v>0.9173160653838927</v>
       </c>
-      <c r="T82" t="n">
+      <c r="V82" t="n">
         <v>0.251521169960115</v>
       </c>
-      <c r="U82" t="n">
+      <c r="W82" t="n">
         <v>0.08452647157386334</v>
       </c>
-      <c r="V82" t="n">
+      <c r="X82" t="n">
         <v>0.09878463735124969</v>
       </c>
-      <c r="W82" t="n">
+      <c r="Y82" t="n">
         <v>0.1153846153846154</v>
       </c>
     </row>
@@ -6473,24 +6969,30 @@
         <v>1.073721446512399</v>
       </c>
       <c r="Q83" t="n">
+        <v>1.114600084769939</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1.190435449306315</v>
+      </c>
+      <c r="S83" t="n">
         <v>1.096834633890862</v>
       </c>
-      <c r="R83" t="n">
+      <c r="T83" t="n">
         <v>66</v>
       </c>
-      <c r="S83" t="n">
+      <c r="U83" t="n">
         <v>2.13363652084701</v>
       </c>
-      <c r="T83" t="n">
+      <c r="V83" t="n">
         <v>1.778200369885677</v>
       </c>
-      <c r="U83" t="n">
+      <c r="W83" t="n">
         <v>0.1375535564575651</v>
       </c>
-      <c r="V83" t="n">
+      <c r="X83" t="n">
         <v>0.1296585331322813</v>
       </c>
-      <c r="W83" t="n">
+      <c r="Y83" t="n">
         <v>0.1666666666666666</v>
       </c>
     </row>
@@ -6546,24 +7048,30 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1.162644459024371</v>
+      </c>
+      <c r="S84" t="n">
         <v>1.016696448388154</v>
       </c>
-      <c r="R84" t="n">
+      <c r="T84" t="n">
         <v>22</v>
       </c>
-      <c r="S84" t="n">
+      <c r="U84" t="n">
         <v>1.082998964935204</v>
       </c>
-      <c r="T84" t="n">
+      <c r="V84" t="n">
         <v>2.332311428310494</v>
       </c>
-      <c r="U84" t="n">
+      <c r="W84" t="n">
         <v>0.5348158179033113</v>
       </c>
-      <c r="V84" t="n">
+      <c r="X84" t="n">
         <v>0.08364119314737734</v>
       </c>
-      <c r="W84" t="n">
+      <c r="Y84" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -6619,24 +7127,30 @@
         <v>1.025691125362011</v>
       </c>
       <c r="Q85" t="n">
+        <v>1.049023521213641</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.063993467385989</v>
+      </c>
+      <c r="S85" t="n">
         <v>1.023267504114854</v>
       </c>
-      <c r="R85" t="n">
+      <c r="T85" t="n">
         <v>42</v>
       </c>
-      <c r="S85" t="n">
+      <c r="U85" t="n">
         <v>1.627804898880422</v>
       </c>
-      <c r="T85" t="n">
+      <c r="V85" t="n">
         <v>1.988841415101766</v>
       </c>
-      <c r="U85" t="n">
+      <c r="W85" t="n">
         <v>0.09402797565305154</v>
       </c>
-      <c r="V85" t="n">
+      <c r="X85" t="n">
         <v>0.0467520872457413</v>
       </c>
-      <c r="W85" t="n">
+      <c r="Y85" t="n">
         <v>0.07142857142857142</v>
       </c>
     </row>
@@ -6692,24 +7206,30 @@
         <v>1.02738807093067</v>
       </c>
       <c r="Q86" t="n">
+        <v>1.077750300314287</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.102158499393509</v>
+      </c>
+      <c r="S86" t="n">
         <v>1.037776500924808</v>
       </c>
-      <c r="R86" t="n">
+      <c r="T86" t="n">
         <v>13</v>
       </c>
-      <c r="S86" t="n">
+      <c r="U86" t="n">
         <v>1.847790614506599</v>
       </c>
-      <c r="T86" t="n">
+      <c r="V86" t="n">
         <v>1.383014613536674</v>
       </c>
-      <c r="U86" t="n">
+      <c r="W86" t="n">
         <v>0.0827384400733604</v>
       </c>
-      <c r="V86" t="n">
+      <c r="X86" t="n">
         <v>0.121783183822627</v>
       </c>
-      <c r="W86" t="n">
+      <c r="Y86" t="n">
         <v>0.1538461538461539</v>
       </c>
     </row>
@@ -6765,24 +7285,30 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>1.052980283921047</v>
       </c>
       <c r="R87" t="n">
+        <v>1.009254179430056</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
         <v>5</v>
       </c>
-      <c r="S87" t="n">
+      <c r="U87" t="n">
         <v>1.607732086193668</v>
       </c>
-      <c r="T87" t="n">
+      <c r="V87" t="n">
         <v>1.030221572208379</v>
       </c>
-      <c r="U87" t="n">
+      <c r="W87" t="n">
         <v>0.06604643444257043</v>
       </c>
-      <c r="V87" t="n">
+      <c r="X87" t="n">
         <v>0.2548570013236684</v>
       </c>
-      <c r="W87" t="n">
+      <c r="Y87" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -6841,21 +7367,27 @@
         <v>1</v>
       </c>
       <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
         <v>19</v>
       </c>
-      <c r="S88" t="n">
+      <c r="U88" t="n">
         <v>0.4102804175537789</v>
       </c>
-      <c r="T88" t="n">
+      <c r="V88" t="n">
         <v>-0.006150723052177727</v>
       </c>
-      <c r="U88" t="n">
+      <c r="W88" t="n">
         <v>0.1001952558717026</v>
       </c>
-      <c r="V88" t="n">
+      <c r="X88" t="n">
         <v>0.3447845839361371</v>
       </c>
-      <c r="W88" t="n">
+      <c r="Y88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6911,24 +7443,30 @@
         <v>1.025724160817855</v>
       </c>
       <c r="Q89" t="n">
+        <v>1.081490740617717</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1.056052410512879</v>
+      </c>
+      <c r="S89" t="n">
         <v>1.022144060724332</v>
       </c>
-      <c r="R89" t="n">
+      <c r="T89" t="n">
         <v>69</v>
       </c>
-      <c r="S89" t="n">
+      <c r="U89" t="n">
         <v>2.494952898910014</v>
       </c>
-      <c r="T89" t="n">
+      <c r="V89" t="n">
         <v>2.00584244311886</v>
       </c>
-      <c r="U89" t="n">
+      <c r="W89" t="n">
         <v>0.0782318229194254</v>
       </c>
-      <c r="V89" t="n">
+      <c r="X89" t="n">
         <v>0.04511360015705466</v>
       </c>
-      <c r="W89" t="n">
+      <c r="Y89" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -6984,24 +7522,30 @@
         <v>1.043853020896188</v>
       </c>
       <c r="Q90" t="n">
+        <v>1.137973750551528</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1.098162439654083</v>
+      </c>
+      <c r="S90" t="n">
         <v>1.022418497241333</v>
       </c>
-      <c r="R90" t="n">
+      <c r="T90" t="n">
         <v>248</v>
       </c>
-      <c r="S90" t="n">
+      <c r="U90" t="n">
         <v>3.577663075138965</v>
       </c>
-      <c r="T90" t="n">
+      <c r="V90" t="n">
         <v>4.350860885955785</v>
       </c>
-      <c r="U90" t="n">
+      <c r="W90" t="n">
         <v>0.1446580034935295</v>
       </c>
-      <c r="V90" t="n">
+      <c r="X90" t="n">
         <v>0.09005993971435373</v>
       </c>
-      <c r="W90" t="n">
+      <c r="Y90" t="n">
         <v>0.07258064516129031</v>
       </c>
     </row>
@@ -7057,24 +7601,30 @@
         <v>1.000401343017475</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>1.038737356941775</v>
       </c>
       <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
         <v>22</v>
       </c>
-      <c r="S91" t="n">
+      <c r="U91" t="n">
         <v>1.176790044253493</v>
       </c>
-      <c r="T91" t="n">
+      <c r="V91" t="n">
         <v>0.603410397063592</v>
       </c>
-      <c r="U91" t="n">
+      <c r="W91" t="n">
         <v>0.1129499796054197</v>
       </c>
-      <c r="V91" t="n">
+      <c r="X91" t="n">
         <v>0.1250655231098887</v>
       </c>
-      <c r="W91" t="n">
+      <c r="Y91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7130,24 +7680,30 @@
         <v>1.003323374829136</v>
       </c>
       <c r="Q92" t="n">
+        <v>1.046936393126166</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.127756234512661</v>
+      </c>
+      <c r="S92" t="n">
         <v>1.000255009972166</v>
       </c>
-      <c r="R92" t="n">
+      <c r="T92" t="n">
         <v>32</v>
       </c>
-      <c r="S92" t="n">
+      <c r="U92" t="n">
         <v>1.549419852347802</v>
       </c>
-      <c r="T92" t="n">
+      <c r="V92" t="n">
         <v>1.857770218499796</v>
       </c>
-      <c r="U92" t="n">
+      <c r="W92" t="n">
         <v>0.1140632903590619</v>
       </c>
-      <c r="V92" t="n">
+      <c r="X92" t="n">
         <v>0.1702102395849686</v>
       </c>
-      <c r="W92" t="n">
+      <c r="Y92" t="n">
         <v>0.15625</v>
       </c>
     </row>
@@ -7203,24 +7759,30 @@
         <v>1.003801241720812</v>
       </c>
       <c r="Q93" t="n">
+        <v>1.004349799147729</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.088386244467616</v>
+      </c>
+      <c r="S93" t="n">
         <v>1.033688772809744</v>
       </c>
-      <c r="R93" t="n">
+      <c r="T93" t="n">
         <v>57</v>
       </c>
-      <c r="S93" t="n">
+      <c r="U93" t="n">
         <v>1.854238919044537</v>
       </c>
-      <c r="T93" t="n">
+      <c r="V93" t="n">
         <v>3.428798116789874</v>
       </c>
-      <c r="U93" t="n">
+      <c r="W93" t="n">
         <v>0.1364108440704677</v>
       </c>
-      <c r="V93" t="n">
+      <c r="X93" t="n">
         <v>0.01803552239027447</v>
       </c>
-      <c r="W93" t="n">
+      <c r="Y93" t="n">
         <v>0.01754385964912281</v>
       </c>
     </row>
@@ -7276,24 +7838,30 @@
         <v>1.023841364128656</v>
       </c>
       <c r="Q94" t="n">
+        <v>1.185793617050255</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.165732751759302</v>
+      </c>
+      <c r="S94" t="n">
         <v>1.039029327919982</v>
       </c>
-      <c r="R94" t="n">
+      <c r="T94" t="n">
         <v>282</v>
       </c>
-      <c r="S94" t="n">
+      <c r="U94" t="n">
         <v>5.222070256643468</v>
       </c>
-      <c r="T94" t="n">
+      <c r="V94" t="n">
         <v>6.023495277186705</v>
       </c>
-      <c r="U94" t="n">
+      <c r="W94" t="n">
         <v>0.1266135075093632</v>
       </c>
-      <c r="V94" t="n">
+      <c r="X94" t="n">
         <v>0.07014167342230265</v>
       </c>
-      <c r="W94" t="n">
+      <c r="Y94" t="n">
         <v>0.05319148936170211</v>
       </c>
     </row>
@@ -7349,24 +7917,30 @@
         <v>1.000347140972972</v>
       </c>
       <c r="Q95" t="n">
+        <v>1.000457347610021</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.065782000815607</v>
+      </c>
+      <c r="S95" t="n">
         <v>1.040438603600053</v>
       </c>
-      <c r="R95" t="n">
+      <c r="T95" t="n">
         <v>17</v>
       </c>
-      <c r="S95" t="n">
+      <c r="U95" t="n">
         <v>1.19124945161719</v>
       </c>
-      <c r="T95" t="n">
+      <c r="V95" t="n">
         <v>2.194861197103704</v>
       </c>
-      <c r="U95" t="n">
+      <c r="W95" t="n">
         <v>0.1339186723634312</v>
       </c>
-      <c r="V95" t="n">
+      <c r="X95" t="n">
         <v>0.01768660701870946</v>
       </c>
-      <c r="W95" t="n">
+      <c r="Y95" t="n">
         <v>0.05882352941176471</v>
       </c>
     </row>
@@ -7422,24 +7996,30 @@
         <v>1.000612132945867</v>
       </c>
       <c r="Q96" t="n">
+        <v>1.105393886455006</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1.12146581512879</v>
+      </c>
+      <c r="S96" t="n">
         <v>1.007236473594104</v>
       </c>
-      <c r="R96" t="n">
+      <c r="T96" t="n">
         <v>12</v>
       </c>
-      <c r="S96" t="n">
+      <c r="U96" t="n">
         <v>-0.07683966955778453</v>
       </c>
-      <c r="T96" t="n">
+      <c r="V96" t="n">
         <v>-0.172585853710321</v>
       </c>
-      <c r="U96" t="n">
+      <c r="W96" t="n">
         <v>0.0675456042499499</v>
       </c>
-      <c r="V96" t="n">
+      <c r="X96" t="n">
         <v>0</v>
       </c>
-      <c r="W96" t="n">
+      <c r="Y96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7495,24 +8075,30 @@
         <v>1.008855777587151</v>
       </c>
       <c r="Q97" t="n">
+        <v>1.028975901892518</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.049673764268197</v>
+      </c>
+      <c r="S97" t="n">
         <v>1.0090969367735</v>
       </c>
-      <c r="R97" t="n">
+      <c r="T97" t="n">
         <v>217</v>
       </c>
-      <c r="S97" t="n">
+      <c r="U97" t="n">
         <v>1.659421993391969</v>
       </c>
-      <c r="T97" t="n">
+      <c r="V97" t="n">
         <v>2.170438466012317</v>
       </c>
-      <c r="U97" t="n">
+      <c r="W97" t="n">
         <v>0.1189580293823029</v>
       </c>
-      <c r="V97" t="n">
+      <c r="X97" t="n">
         <v>0.03808731616476651</v>
       </c>
-      <c r="W97" t="n">
+      <c r="Y97" t="n">
         <v>0.05069124423963134</v>
       </c>
     </row>
@@ -7568,24 +8154,30 @@
         <v>1.027224996138168</v>
       </c>
       <c r="Q98" t="n">
+        <v>1.032120178305842</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.064215588254364</v>
+      </c>
+      <c r="S98" t="n">
         <v>1.047486164796515</v>
       </c>
-      <c r="R98" t="n">
+      <c r="T98" t="n">
         <v>19</v>
       </c>
-      <c r="S98" t="n">
+      <c r="U98" t="n">
         <v>3.645472029070145</v>
       </c>
-      <c r="T98" t="n">
+      <c r="V98" t="n">
         <v>2.562917840510117</v>
       </c>
-      <c r="U98" t="n">
+      <c r="W98" t="n">
         <v>0.3204924200188946</v>
       </c>
-      <c r="V98" t="n">
+      <c r="X98" t="n">
         <v>0.1179090495771241</v>
       </c>
-      <c r="W98" t="n">
+      <c r="Y98" t="n">
         <v>0.05263157894736842</v>
       </c>
     </row>
@@ -7641,24 +8233,30 @@
         <v>1.007071296387913</v>
       </c>
       <c r="Q99" t="n">
+        <v>1.03191186059371</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1.121475256785471</v>
+      </c>
+      <c r="S99" t="n">
         <v>1.036482101907221</v>
       </c>
-      <c r="R99" t="n">
+      <c r="T99" t="n">
         <v>72</v>
       </c>
-      <c r="S99" t="n">
+      <c r="U99" t="n">
         <v>2.274473672245476</v>
       </c>
-      <c r="T99" t="n">
+      <c r="V99" t="n">
         <v>3.908362795964312</v>
       </c>
-      <c r="U99" t="n">
+      <c r="W99" t="n">
         <v>0.1372744059732398</v>
       </c>
-      <c r="V99" t="n">
+      <c r="X99" t="n">
         <v>0.007544722891714243</v>
       </c>
-      <c r="W99" t="n">
+      <c r="Y99" t="n">
         <v>0.04166666666666666</v>
       </c>
     </row>
@@ -7714,24 +8312,30 @@
         <v>1.001061052440342</v>
       </c>
       <c r="Q100" t="n">
+        <v>1.014683299765274</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1.020167778469986</v>
+      </c>
+      <c r="S100" t="n">
         <v>1.000858196647481</v>
       </c>
-      <c r="R100" t="n">
+      <c r="T100" t="n">
         <v>35</v>
       </c>
-      <c r="S100" t="n">
+      <c r="U100" t="n">
         <v>1.331553995645494</v>
       </c>
-      <c r="T100" t="n">
+      <c r="V100" t="n">
         <v>1.023361735976383</v>
       </c>
-      <c r="U100" t="n">
+      <c r="W100" t="n">
         <v>0.01738842179353949</v>
       </c>
-      <c r="V100" t="n">
+      <c r="X100" t="n">
         <v>0.02434334670396598</v>
       </c>
-      <c r="W100" t="n">
+      <c r="Y100" t="n">
         <v>0.02857142857142857</v>
       </c>
     </row>
@@ -7787,24 +8391,30 @@
         <v>1.014016365397673</v>
       </c>
       <c r="Q101" t="n">
+        <v>1.115643195367019</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1.082533642224376</v>
+      </c>
+      <c r="S101" t="n">
         <v>1.013484922788592</v>
       </c>
-      <c r="R101" t="n">
+      <c r="T101" t="n">
         <v>398</v>
       </c>
-      <c r="S101" t="n">
+      <c r="U101" t="n">
         <v>4.343920701537407</v>
       </c>
-      <c r="T101" t="n">
+      <c r="V101" t="n">
         <v>4.609640689229552</v>
       </c>
-      <c r="U101" t="n">
+      <c r="W101" t="n">
         <v>0.06895988746928795</v>
       </c>
-      <c r="V101" t="n">
+      <c r="X101" t="n">
         <v>0.1594215066973216</v>
       </c>
-      <c r="W101" t="n">
+      <c r="Y101" t="n">
         <v>0.1407035175879397</v>
       </c>
     </row>
@@ -7860,24 +8470,30 @@
         <v>1.010954665172787</v>
       </c>
       <c r="Q102" t="n">
+        <v>1.04953648030144</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1.051552741916877</v>
+      </c>
+      <c r="S102" t="n">
         <v>1.015071317116978</v>
       </c>
-      <c r="R102" t="n">
+      <c r="T102" t="n">
         <v>499</v>
       </c>
-      <c r="S102" t="n">
+      <c r="U102" t="n">
         <v>2.303176105176199</v>
       </c>
-      <c r="T102" t="n">
+      <c r="V102" t="n">
         <v>2.906557984936481</v>
       </c>
-      <c r="U102" t="n">
+      <c r="W102" t="n">
         <v>0.02502537181778215</v>
       </c>
-      <c r="V102" t="n">
+      <c r="X102" t="n">
         <v>0.04873973715259736</v>
       </c>
-      <c r="W102" t="n">
+      <c r="Y102" t="n">
         <v>0.0501002004008016</v>
       </c>
     </row>
@@ -7933,24 +8549,30 @@
         <v>1.009893725976472</v>
       </c>
       <c r="Q103" t="n">
+        <v>1.080403588573065</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1.047314072748331</v>
+      </c>
+      <c r="S103" t="n">
         <v>1.020541475120251</v>
       </c>
-      <c r="R103" t="n">
+      <c r="T103" t="n">
         <v>130</v>
       </c>
-      <c r="S103" t="n">
+      <c r="U103" t="n">
         <v>2.417049395166277</v>
       </c>
-      <c r="T103" t="n">
+      <c r="V103" t="n">
         <v>2.869891820976882</v>
       </c>
-      <c r="U103" t="n">
+      <c r="W103" t="n">
         <v>0.1726170480952466</v>
       </c>
-      <c r="V103" t="n">
+      <c r="X103" t="n">
         <v>0.06381066808003505</v>
       </c>
-      <c r="W103" t="n">
+      <c r="Y103" t="n">
         <v>0.06923076923076923</v>
       </c>
     </row>
@@ -8006,24 +8628,30 @@
         <v>1.001230950738564</v>
       </c>
       <c r="Q104" t="n">
+        <v>1.002165316332793</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1.001772487326929</v>
+      </c>
+      <c r="S104" t="n">
         <v>1.000830925627947</v>
       </c>
-      <c r="R104" t="n">
+      <c r="T104" t="n">
         <v>20814</v>
       </c>
-      <c r="S104" t="n">
+      <c r="U104" t="n">
         <v>0.6859790418715828</v>
       </c>
-      <c r="T104" t="n">
+      <c r="V104" t="n">
         <v>0.6669574188385856</v>
       </c>
-      <c r="U104" t="n">
+      <c r="W104" t="n">
         <v>0.001302951011824498</v>
       </c>
-      <c r="V104" t="n">
+      <c r="X104" t="n">
         <v>0.01693864066694719</v>
       </c>
-      <c r="W104" t="n">
+      <c r="Y104" t="n">
         <v>0.01628711444220237</v>
       </c>
     </row>
@@ -8079,24 +8707,30 @@
         <v>1.002465609241256</v>
       </c>
       <c r="Q105" t="n">
+        <v>1.003840727820834</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1.00250265881513</v>
+      </c>
+      <c r="S105" t="n">
         <v>1.001944668362955</v>
       </c>
-      <c r="R105" t="n">
+      <c r="T105" t="n">
         <v>31025</v>
       </c>
-      <c r="S105" t="n">
+      <c r="U105" t="n">
         <v>0.5718333154283729</v>
       </c>
-      <c r="T105" t="n">
+      <c r="V105" t="n">
         <v>0.5707653196191426</v>
       </c>
-      <c r="U105" t="n">
+      <c r="W105" t="n">
         <v>0.001373709037055503</v>
       </c>
-      <c r="V105" t="n">
+      <c r="X105" t="n">
         <v>0.009918913110154847</v>
       </c>
-      <c r="W105" t="n">
+      <c r="Y105" t="n">
         <v>0.009508460918614021</v>
       </c>
     </row>
@@ -8152,24 +8786,30 @@
         <v>1.006305099832498</v>
       </c>
       <c r="Q106" t="n">
+        <v>1.021444007645014</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1.029495840227092</v>
+      </c>
+      <c r="S106" t="n">
         <v>1.014388645385015</v>
       </c>
-      <c r="R106" t="n">
+      <c r="T106" t="n">
         <v>14366</v>
       </c>
-      <c r="S106" t="n">
+      <c r="U106" t="n">
         <v>0.3375076545263215</v>
       </c>
-      <c r="T106" t="n">
+      <c r="V106" t="n">
         <v>0.2592740664657261</v>
       </c>
-      <c r="U106" t="n">
+      <c r="W106" t="n">
         <v>0.002699868133319617</v>
       </c>
-      <c r="V106" t="n">
+      <c r="X106" t="n">
         <v>0.003259895325237743</v>
       </c>
-      <c r="W106" t="n">
+      <c r="Y106" t="n">
         <v>0.002853960740637616</v>
       </c>
     </row>
@@ -8225,24 +8865,30 @@
         <v>1.007535450314046</v>
       </c>
       <c r="Q107" t="n">
+        <v>1.014192510702462</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1.017536230417437</v>
+      </c>
+      <c r="S107" t="n">
         <v>1.00994527209299</v>
       </c>
-      <c r="R107" t="n">
+      <c r="T107" t="n">
         <v>3974</v>
       </c>
-      <c r="S107" t="n">
+      <c r="U107" t="n">
         <v>0.3670557108549273</v>
       </c>
-      <c r="T107" t="n">
+      <c r="V107" t="n">
         <v>0.4125348590414192</v>
       </c>
-      <c r="U107" t="n">
+      <c r="W107" t="n">
         <v>0.00726821087140794</v>
       </c>
-      <c r="V107" t="n">
+      <c r="X107" t="n">
         <v>0.01722501509055378</v>
       </c>
-      <c r="W107" t="n">
+      <c r="Y107" t="n">
         <v>0.0163563160543533</v>
       </c>
     </row>
@@ -8298,24 +8944,30 @@
         <v>1.002019765811897</v>
       </c>
       <c r="Q108" t="n">
+        <v>1.031154218181599</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1.054616859994749</v>
+      </c>
+      <c r="S108" t="n">
         <v>1.019360536910961</v>
       </c>
-      <c r="R108" t="n">
+      <c r="T108" t="n">
         <v>7887</v>
       </c>
-      <c r="S108" t="n">
+      <c r="U108" t="n">
         <v>0.3748103968831243</v>
       </c>
-      <c r="T108" t="n">
+      <c r="V108" t="n">
         <v>0.5709707513364392</v>
       </c>
-      <c r="U108" t="n">
+      <c r="W108" t="n">
         <v>0.004589606704465962</v>
       </c>
-      <c r="V108" t="n">
+      <c r="X108" t="n">
         <v>0.005663937518616677</v>
       </c>
-      <c r="W108" t="n">
+      <c r="Y108" t="n">
         <v>0.006719918853810068</v>
       </c>
     </row>
@@ -8371,24 +9023,30 @@
         <v>1.002587291350518</v>
       </c>
       <c r="Q109" t="n">
+        <v>1.004035411079369</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.007795364176455</v>
+      </c>
+      <c r="S109" t="n">
         <v>1.003893016525779</v>
       </c>
-      <c r="R109" t="n">
+      <c r="T109" t="n">
         <v>8777</v>
       </c>
-      <c r="S109" t="n">
+      <c r="U109" t="n">
         <v>1.654894861563199</v>
       </c>
-      <c r="T109" t="n">
+      <c r="V109" t="n">
         <v>1.776788231725877</v>
       </c>
-      <c r="U109" t="n">
+      <c r="W109" t="n">
         <v>0.003483785486091184</v>
       </c>
-      <c r="V109" t="n">
+      <c r="X109" t="n">
         <v>0.01857134113459018</v>
       </c>
-      <c r="W109" t="n">
+      <c r="Y109" t="n">
         <v>0.02153355360601573</v>
       </c>
     </row>
@@ -8444,24 +9102,30 @@
         <v>1.007455236554274</v>
       </c>
       <c r="Q110" t="n">
+        <v>1.07099861943881</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1.112001908521034</v>
+      </c>
+      <c r="S110" t="n">
         <v>1.025271466101481</v>
       </c>
-      <c r="R110" t="n">
+      <c r="T110" t="n">
         <v>204</v>
       </c>
-      <c r="S110" t="n">
+      <c r="U110" t="n">
         <v>3.414816783051021</v>
       </c>
-      <c r="T110" t="n">
+      <c r="V110" t="n">
         <v>3.36976542456875</v>
       </c>
-      <c r="U110" t="n">
+      <c r="W110" t="n">
         <v>0.03106269780107337</v>
       </c>
-      <c r="V110" t="n">
+      <c r="X110" t="n">
         <v>0.1207410319314589</v>
       </c>
-      <c r="W110" t="n">
+      <c r="Y110" t="n">
         <v>0.08823529411764705</v>
       </c>
     </row>
@@ -8517,24 +9181,30 @@
         <v>1.038976544759671</v>
       </c>
       <c r="Q111" t="n">
+        <v>1.142237717499758</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1.137409975552358</v>
+      </c>
+      <c r="S111" t="n">
         <v>1.037810624895072</v>
       </c>
-      <c r="R111" t="n">
+      <c r="T111" t="n">
         <v>468</v>
       </c>
-      <c r="S111" t="n">
+      <c r="U111" t="n">
         <v>3.488955810413167</v>
       </c>
-      <c r="T111" t="n">
+      <c r="V111" t="n">
         <v>3.512280715203127</v>
       </c>
-      <c r="U111" t="n">
+      <c r="W111" t="n">
         <v>0.02520482083034865</v>
       </c>
-      <c r="V111" t="n">
+      <c r="X111" t="n">
         <v>0.08316791825924923</v>
       </c>
-      <c r="W111" t="n">
+      <c r="Y111" t="n">
         <v>0.09401709401709404</v>
       </c>
     </row>
@@ -8590,24 +9260,30 @@
         <v>1.007015456525137</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>1.061595379301174</v>
       </c>
       <c r="R112" t="n">
+        <v>1.020594937432143</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
         <v>20</v>
       </c>
-      <c r="S112" t="n">
+      <c r="U112" t="n">
         <v>-1.058163125479492</v>
       </c>
-      <c r="T112" t="n">
+      <c r="V112" t="n">
         <v>-0.3681207526856916</v>
       </c>
-      <c r="U112" t="n">
+      <c r="W112" t="n">
         <v>0.0436559872099314</v>
       </c>
-      <c r="V112" t="n">
+      <c r="X112" t="n">
         <v>0</v>
       </c>
-      <c r="W112" t="n">
+      <c r="Y112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8666,21 +9342,27 @@
         <v>1</v>
       </c>
       <c r="R113" t="n">
+        <v>1.001984070467864</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
         <v>61</v>
       </c>
-      <c r="S113" t="n">
+      <c r="U113" t="n">
         <v>0.6888254212557682</v>
       </c>
-      <c r="T113" t="n">
+      <c r="V113" t="n">
         <v>1.22494588083562</v>
       </c>
-      <c r="U113" t="n">
+      <c r="W113" t="n">
         <v>0.1270133769611202</v>
       </c>
-      <c r="V113" t="n">
+      <c r="X113" t="n">
         <v>0.002674418540895177</v>
       </c>
-      <c r="W113" t="n">
+      <c r="Y113" t="n">
         <v>0.01639344262295082</v>
       </c>
     </row>
@@ -8736,24 +9418,30 @@
         <v>1</v>
       </c>
       <c r="Q114" t="n">
+        <v>1.030833818984759</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.052413834280961</v>
+      </c>
+      <c r="S114" t="n">
         <v>1.00123504297487</v>
       </c>
-      <c r="R114" t="n">
+      <c r="T114" t="n">
         <v>71</v>
       </c>
-      <c r="S114" t="n">
+      <c r="U114" t="n">
         <v>1.490840749307944</v>
       </c>
-      <c r="T114" t="n">
+      <c r="V114" t="n">
         <v>1.50472930102468</v>
       </c>
-      <c r="U114" t="n">
+      <c r="W114" t="n">
         <v>0.06592609035373777</v>
       </c>
-      <c r="V114" t="n">
+      <c r="X114" t="n">
         <v>0.130167125795917</v>
       </c>
-      <c r="W114" t="n">
+      <c r="Y114" t="n">
         <v>0.08450704225352113</v>
       </c>
     </row>
@@ -8809,24 +9497,30 @@
         <v>1</v>
       </c>
       <c r="Q115" t="n">
+        <v>1.007322029499063</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1.029799443504566</v>
+      </c>
+      <c r="S115" t="n">
         <v>1.004505860103953</v>
       </c>
-      <c r="R115" t="n">
+      <c r="T115" t="n">
         <v>183</v>
       </c>
-      <c r="S115" t="n">
+      <c r="U115" t="n">
         <v>0.2621574661297971</v>
       </c>
-      <c r="T115" t="n">
+      <c r="V115" t="n">
         <v>0.3788679737389101</v>
       </c>
-      <c r="U115" t="n">
+      <c r="W115" t="n">
         <v>0.01427561207975698</v>
       </c>
-      <c r="V115" t="n">
+      <c r="X115" t="n">
         <v>0.009983350368633759</v>
       </c>
-      <c r="W115" t="n">
+      <c r="Y115" t="n">
         <v>0.01092896174863388</v>
       </c>
     </row>
@@ -8882,24 +9576,30 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>1.000980278674305</v>
       </c>
       <c r="R116" t="n">
+        <v>1.000574668343487</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
         <v>651</v>
       </c>
-      <c r="S116" t="n">
+      <c r="U116" t="n">
         <v>0.2655357194781706</v>
       </c>
-      <c r="T116" t="n">
+      <c r="V116" t="n">
         <v>0.3184181732792312</v>
       </c>
-      <c r="U116" t="n">
+      <c r="W116" t="n">
         <v>0.008019777857085084</v>
       </c>
-      <c r="V116" t="n">
+      <c r="X116" t="n">
         <v>0.017126075011858</v>
       </c>
-      <c r="W116" t="n">
+      <c r="Y116" t="n">
         <v>0.01536098310291859</v>
       </c>
     </row>
@@ -8955,24 +9655,30 @@
         <v>1</v>
       </c>
       <c r="Q117" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.036236767243798</v>
+      </c>
+      <c r="S117" t="n">
         <v>1.001261296845279</v>
       </c>
-      <c r="R117" t="n">
+      <c r="T117" t="n">
         <v>471</v>
       </c>
-      <c r="S117" t="n">
+      <c r="U117" t="n">
         <v>0.3068765856586382</v>
       </c>
-      <c r="T117" t="n">
+      <c r="V117" t="n">
         <v>0.2758034020553505</v>
       </c>
-      <c r="U117" t="n">
+      <c r="W117" t="n">
         <v>0.01057655250555873</v>
       </c>
-      <c r="V117" t="n">
+      <c r="X117" t="n">
         <v>0.003234650199221487</v>
       </c>
-      <c r="W117" t="n">
+      <c r="Y117" t="n">
         <v>0.002123142250530786</v>
       </c>
     </row>
@@ -9028,24 +9734,30 @@
         <v>1.001529129231015</v>
       </c>
       <c r="Q118" t="n">
-        <v>1</v>
+        <v>1.084463602864396</v>
       </c>
       <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="n">
         <v>4</v>
       </c>
-      <c r="S118" t="n">
+      <c r="U118" t="n">
         <v>-0.1339335210408957</v>
       </c>
-      <c r="T118" t="n">
+      <c r="V118" t="n">
         <v>0.2631783249333359</v>
       </c>
-      <c r="U118" t="n">
+      <c r="W118" t="n">
         <v>0.0858053318700126</v>
       </c>
-      <c r="V118" t="n">
+      <c r="X118" t="n">
         <v>0</v>
       </c>
-      <c r="W118" t="n">
+      <c r="Y118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9101,24 +9813,30 @@
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>1</v>
+        <v>1.015284378089266</v>
       </c>
       <c r="R119" t="n">
+        <v>1.000735000895359</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="n">
         <v>264</v>
       </c>
-      <c r="S119" t="n">
+      <c r="U119" t="n">
         <v>0.6299735872045388</v>
       </c>
-      <c r="T119" t="n">
+      <c r="V119" t="n">
         <v>0.6784172290643619</v>
       </c>
-      <c r="U119" t="n">
+      <c r="W119" t="n">
         <v>0.01312818719996932</v>
       </c>
-      <c r="V119" t="n">
+      <c r="X119" t="n">
         <v>0.01401463186829745</v>
       </c>
-      <c r="W119" t="n">
+      <c r="Y119" t="n">
         <v>0.01893939393939394</v>
       </c>
     </row>
@@ -9174,24 +9892,30 @@
         <v>1.066821883470262</v>
       </c>
       <c r="Q120" t="n">
+        <v>1.139239353192504</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.142472689829257</v>
+      </c>
+      <c r="S120" t="n">
         <v>1.062296920709371</v>
       </c>
-      <c r="R120" t="n">
+      <c r="T120" t="n">
         <v>96</v>
       </c>
-      <c r="S120" t="n">
+      <c r="U120" t="n">
         <v>1.384459439528728</v>
       </c>
-      <c r="T120" t="n">
+      <c r="V120" t="n">
         <v>1.45721280365213</v>
       </c>
-      <c r="U120" t="n">
+      <c r="W120" t="n">
         <v>0.03156724995690034</v>
       </c>
-      <c r="V120" t="n">
+      <c r="X120" t="n">
         <v>0.09773434523708385</v>
       </c>
-      <c r="W120" t="n">
+      <c r="Y120" t="n">
         <v>0.07291666666666666</v>
       </c>
     </row>
@@ -9247,24 +9971,30 @@
         <v>1.007777424459459</v>
       </c>
       <c r="Q121" t="n">
+        <v>1.073335843260173</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1.044022486629834</v>
+      </c>
+      <c r="S121" t="n">
         <v>1.022020897969908</v>
       </c>
-      <c r="R121" t="n">
+      <c r="T121" t="n">
         <v>29</v>
       </c>
-      <c r="S121" t="n">
+      <c r="U121" t="n">
         <v>1.02550517992069</v>
       </c>
-      <c r="T121" t="n">
+      <c r="V121" t="n">
         <v>1.685904792682899</v>
       </c>
-      <c r="U121" t="n">
+      <c r="W121" t="n">
         <v>0.2035956850033169</v>
       </c>
-      <c r="V121" t="n">
+      <c r="X121" t="n">
         <v>0.1800080011824223</v>
       </c>
-      <c r="W121" t="n">
+      <c r="Y121" t="n">
         <v>0.03448275862068965</v>
       </c>
     </row>
@@ -9323,21 +10053,27 @@
         <v>1</v>
       </c>
       <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
         <v>11</v>
       </c>
-      <c r="S122" t="n">
+      <c r="U122" t="n">
         <v>0.3461965781098211</v>
       </c>
-      <c r="T122" t="n">
+      <c r="V122" t="n">
         <v>0.1932887635188584</v>
       </c>
-      <c r="U122" t="n">
+      <c r="W122" t="n">
         <v>0.0316613160507849</v>
       </c>
-      <c r="V122" t="n">
+      <c r="X122" t="n">
         <v>0</v>
       </c>
-      <c r="W122" t="n">
+      <c r="Y122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9393,24 +10129,30 @@
         <v>1.013150226475954</v>
       </c>
       <c r="Q123" t="n">
+        <v>1.087625705211359</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.047682093341697</v>
+      </c>
+      <c r="S123" t="n">
         <v>1.021223614675844</v>
       </c>
-      <c r="R123" t="n">
+      <c r="T123" t="n">
         <v>74</v>
       </c>
-      <c r="S123" t="n">
+      <c r="U123" t="n">
         <v>4.700346506375285</v>
       </c>
-      <c r="T123" t="n">
+      <c r="V123" t="n">
         <v>4.52945457277894</v>
       </c>
-      <c r="U123" t="n">
+      <c r="W123" t="n">
         <v>0.04456402920810431</v>
       </c>
-      <c r="V123" t="n">
+      <c r="X123" t="n">
         <v>0.05896447331394603</v>
       </c>
-      <c r="W123" t="n">
+      <c r="Y123" t="n">
         <v>0.04054054054054054</v>
       </c>
     </row>
@@ -9466,24 +10208,30 @@
         <v>1.010963873907253</v>
       </c>
       <c r="Q124" t="n">
+        <v>1.105256704819495</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.056555648933941</v>
+      </c>
+      <c r="S124" t="n">
         <v>1.045290362191896</v>
       </c>
-      <c r="R124" t="n">
+      <c r="T124" t="n">
         <v>27</v>
       </c>
-      <c r="S124" t="n">
+      <c r="U124" t="n">
         <v>1.739460911994443</v>
       </c>
-      <c r="T124" t="n">
+      <c r="V124" t="n">
         <v>2.586558181307767</v>
       </c>
-      <c r="U124" t="n">
+      <c r="W124" t="n">
         <v>0.3059427237263445</v>
       </c>
-      <c r="V124" t="n">
+      <c r="X124" t="n">
         <v>0.004575005067148818</v>
       </c>
-      <c r="W124" t="n">
+      <c r="Y124" t="n">
         <v>0.03703703703703703</v>
       </c>
     </row>
@@ -9539,24 +10287,30 @@
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>1.094588358929022</v>
       </c>
       <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" t="n">
         <v>62</v>
       </c>
-      <c r="S125" t="n">
+      <c r="U125" t="n">
         <v>0.3600575355469509</v>
       </c>
-      <c r="T125" t="n">
+      <c r="V125" t="n">
         <v>0.3458057653557264</v>
       </c>
-      <c r="U125" t="n">
+      <c r="W125" t="n">
         <v>0.03305879380724572</v>
       </c>
-      <c r="V125" t="n">
+      <c r="X125" t="n">
         <v>0.07694031895308452</v>
       </c>
-      <c r="W125" t="n">
+      <c r="Y125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9612,24 +10366,30 @@
         <v>1.043999769996914</v>
       </c>
       <c r="Q126" t="n">
+        <v>1.068887263376771</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1.10164998169456</v>
+      </c>
+      <c r="S126" t="n">
         <v>1.077946271588657</v>
       </c>
-      <c r="R126" t="n">
+      <c r="T126" t="n">
         <v>11</v>
       </c>
-      <c r="S126" t="n">
+      <c r="U126" t="n">
         <v>3.180278128527188</v>
       </c>
-      <c r="T126" t="n">
+      <c r="V126" t="n">
         <v>2.846399436709792</v>
       </c>
-      <c r="U126" t="n">
+      <c r="W126" t="n">
         <v>0.1224618968751506</v>
       </c>
-      <c r="V126" t="n">
+      <c r="X126" t="n">
         <v>0.07152232190490906</v>
       </c>
-      <c r="W126" t="n">
+      <c r="Y126" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -9685,24 +10445,30 @@
         <v>1.000465302497204</v>
       </c>
       <c r="Q127" t="n">
+        <v>1.000542128614338</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.025586231826069</v>
+      </c>
+      <c r="S127" t="n">
         <v>1.020658356003813</v>
       </c>
-      <c r="R127" t="n">
+      <c r="T127" t="n">
         <v>98</v>
       </c>
-      <c r="S127" t="n">
+      <c r="U127" t="n">
         <v>1.009265704486047</v>
       </c>
-      <c r="T127" t="n">
+      <c r="V127" t="n">
         <v>2.176972493956989</v>
       </c>
-      <c r="U127" t="n">
+      <c r="W127" t="n">
         <v>0.01612059176206102</v>
       </c>
-      <c r="V127" t="n">
+      <c r="X127" t="n">
         <v>0.02046487814224904</v>
       </c>
-      <c r="W127" t="n">
+      <c r="Y127" t="n">
         <v>0.03061224489795918</v>
       </c>
     </row>
@@ -9758,24 +10524,30 @@
         <v>1</v>
       </c>
       <c r="Q128" t="n">
+        <v>1.017345946389739</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.125184523970483</v>
+      </c>
+      <c r="S128" t="n">
         <v>1.045878182358265</v>
       </c>
-      <c r="R128" t="n">
+      <c r="T128" t="n">
         <v>19</v>
       </c>
-      <c r="S128" t="n">
+      <c r="U128" t="n">
         <v>0.5513200988965944</v>
       </c>
-      <c r="T128" t="n">
+      <c r="V128" t="n">
         <v>0.9008376289479634</v>
       </c>
-      <c r="U128" t="n">
+      <c r="W128" t="n">
         <v>0.1841703437718766</v>
       </c>
-      <c r="V128" t="n">
+      <c r="X128" t="n">
         <v>0</v>
       </c>
-      <c r="W128" t="n">
+      <c r="Y128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9831,24 +10603,30 @@
         <v>1.003212601165653</v>
       </c>
       <c r="Q129" t="n">
+        <v>1.010081275061546</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1.059601650741658</v>
+      </c>
+      <c r="S129" t="n">
         <v>1.031584810111214</v>
       </c>
-      <c r="R129" t="n">
+      <c r="T129" t="n">
         <v>15</v>
       </c>
-      <c r="S129" t="n">
+      <c r="U129" t="n">
         <v>1.064748612743193</v>
       </c>
-      <c r="T129" t="n">
+      <c r="V129" t="n">
         <v>1.983009311902034</v>
       </c>
-      <c r="U129" t="n">
+      <c r="W129" t="n">
         <v>0.1010731619659722</v>
       </c>
-      <c r="V129" t="n">
+      <c r="X129" t="n">
         <v>0.1002792644248142</v>
       </c>
-      <c r="W129" t="n">
+      <c r="Y129" t="n">
         <v>0.06666666666666667</v>
       </c>
     </row>
@@ -9904,24 +10682,30 @@
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>1</v>
+        <v>1.00160436518928</v>
       </c>
       <c r="R130" t="n">
+        <v>1.011535678494289</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" t="n">
         <v>28</v>
       </c>
-      <c r="S130" t="n">
+      <c r="U130" t="n">
         <v>0.6952762095073944</v>
       </c>
-      <c r="T130" t="n">
+      <c r="V130" t="n">
         <v>1.259071096346934</v>
       </c>
-      <c r="U130" t="n">
+      <c r="W130" t="n">
         <v>0.0974221713568257</v>
       </c>
-      <c r="V130" t="n">
+      <c r="X130" t="n">
         <v>0.005488659894453104</v>
       </c>
-      <c r="W130" t="n">
+      <c r="Y130" t="n">
         <v>0.03571428571428571</v>
       </c>
     </row>
@@ -9977,24 +10761,30 @@
         <v>1.005243726951597</v>
       </c>
       <c r="Q131" t="n">
+        <v>1.042920445842295</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1.069478841464237</v>
+      </c>
+      <c r="S131" t="n">
         <v>1.010052084659834</v>
       </c>
-      <c r="R131" t="n">
+      <c r="T131" t="n">
         <v>161</v>
       </c>
-      <c r="S131" t="n">
+      <c r="U131" t="n">
         <v>3.456624944671316</v>
       </c>
-      <c r="T131" t="n">
+      <c r="V131" t="n">
         <v>3.368519701550973</v>
       </c>
-      <c r="U131" t="n">
+      <c r="W131" t="n">
         <v>0.1907074721795889</v>
       </c>
-      <c r="V131" t="n">
+      <c r="X131" t="n">
         <v>0.04815173800946337</v>
       </c>
-      <c r="W131" t="n">
+      <c r="Y131" t="n">
         <v>0.06211180124223602</v>
       </c>
     </row>
@@ -10050,24 +10840,30 @@
         <v>1.019779094781289</v>
       </c>
       <c r="Q132" t="n">
+        <v>1.1378412941988</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1.188453484583632</v>
+      </c>
+      <c r="S132" t="n">
         <v>1.028004806138072</v>
       </c>
-      <c r="R132" t="n">
+      <c r="T132" t="n">
         <v>43</v>
       </c>
-      <c r="S132" t="n">
+      <c r="U132" t="n">
         <v>4.301494336286658</v>
       </c>
-      <c r="T132" t="n">
+      <c r="V132" t="n">
         <v>4.263071936016621</v>
       </c>
-      <c r="U132" t="n">
+      <c r="W132" t="n">
         <v>0.07539327501076835</v>
       </c>
-      <c r="V132" t="n">
+      <c r="X132" t="n">
         <v>0.1089321650063793</v>
       </c>
-      <c r="W132" t="n">
+      <c r="Y132" t="n">
         <v>0.1395348837209302</v>
       </c>
     </row>
@@ -10123,24 +10919,30 @@
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>1</v>
+        <v>1.021122482344501</v>
       </c>
       <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" t="n">
         <v>17</v>
       </c>
-      <c r="S133" t="n">
+      <c r="U133" t="n">
         <v>0.8728583014274085</v>
       </c>
-      <c r="T133" t="n">
+      <c r="V133" t="n">
         <v>0.7762759986306239</v>
       </c>
-      <c r="U133" t="n">
+      <c r="W133" t="n">
         <v>0.07785094710466912</v>
       </c>
-      <c r="V133" t="n">
+      <c r="X133" t="n">
         <v>0</v>
       </c>
-      <c r="W133" t="n">
+      <c r="Y133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10196,24 +10998,30 @@
         <v>1.021429504033348</v>
       </c>
       <c r="Q134" t="n">
+        <v>1.132079866223419</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1.160367896557249</v>
+      </c>
+      <c r="S134" t="n">
         <v>1.021736585612737</v>
       </c>
-      <c r="R134" t="n">
+      <c r="T134" t="n">
         <v>46</v>
       </c>
-      <c r="S134" t="n">
+      <c r="U134" t="n">
         <v>2.550063488248152</v>
       </c>
-      <c r="T134" t="n">
+      <c r="V134" t="n">
         <v>2.138730143454938</v>
       </c>
-      <c r="U134" t="n">
+      <c r="W134" t="n">
         <v>0.1067213274131488</v>
       </c>
-      <c r="V134" t="n">
+      <c r="X134" t="n">
         <v>0.1282198907768533</v>
       </c>
-      <c r="W134" t="n">
+      <c r="Y134" t="n">
         <v>0.1304347826086956</v>
       </c>
     </row>
@@ -10269,24 +11077,30 @@
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>1.027039392130372</v>
       </c>
       <c r="R135" t="n">
+        <v>1.011295962101767</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1</v>
+      </c>
+      <c r="T135" t="n">
         <v>17</v>
       </c>
-      <c r="S135" t="n">
+      <c r="U135" t="n">
         <v>0.6915859731887382</v>
       </c>
-      <c r="T135" t="n">
+      <c r="V135" t="n">
         <v>0.9785275424222478</v>
       </c>
-      <c r="U135" t="n">
+      <c r="W135" t="n">
         <v>0.09613029841044696</v>
       </c>
-      <c r="V135" t="n">
+      <c r="X135" t="n">
         <v>0.0298471967647992</v>
       </c>
-      <c r="W135" t="n">
+      <c r="Y135" t="n">
         <v>0.1176470588235294</v>
       </c>
     </row>
@@ -10342,24 +11156,30 @@
         <v>1.015155867651729</v>
       </c>
       <c r="Q136" t="n">
+        <v>1.038391508743354</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.025664085417558</v>
+      </c>
+      <c r="S136" t="n">
         <v>1.003816909802737</v>
       </c>
-      <c r="R136" t="n">
+      <c r="T136" t="n">
         <v>11</v>
       </c>
-      <c r="S136" t="n">
+      <c r="U136" t="n">
         <v>3.849436291510053</v>
       </c>
-      <c r="T136" t="n">
+      <c r="V136" t="n">
         <v>2.1481102322363</v>
       </c>
-      <c r="U136" t="n">
+      <c r="W136" t="n">
         <v>0.4552356302167588</v>
       </c>
-      <c r="V136" t="n">
+      <c r="X136" t="n">
         <v>0.05704518364057862</v>
       </c>
-      <c r="W136" t="n">
+      <c r="Y136" t="n">
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -10418,21 +11238,27 @@
         <v>1</v>
       </c>
       <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" t="n">
         <v>14</v>
       </c>
-      <c r="S137" t="n">
+      <c r="U137" t="n">
         <v>0.9567116660103158</v>
       </c>
-      <c r="T137" t="n">
+      <c r="V137" t="n">
         <v>0.5686335102790773</v>
       </c>
-      <c r="U137" t="n">
+      <c r="W137" t="n">
         <v>0.1483606002230113</v>
       </c>
-      <c r="V137" t="n">
+      <c r="X137" t="n">
         <v>0</v>
       </c>
-      <c r="W137" t="n">
+      <c r="Y137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10488,24 +11314,30 @@
         <v>1.020413391949968</v>
       </c>
       <c r="Q138" t="n">
+        <v>1.139061350908823</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.091662236116571</v>
+      </c>
+      <c r="S138" t="n">
         <v>1.010492619786958</v>
       </c>
-      <c r="R138" t="n">
+      <c r="T138" t="n">
         <v>173</v>
       </c>
-      <c r="S138" t="n">
+      <c r="U138" t="n">
         <v>6.223904940906609</v>
       </c>
-      <c r="T138" t="n">
+      <c r="V138" t="n">
         <v>8.363448947307949</v>
       </c>
-      <c r="U138" t="n">
+      <c r="W138" t="n">
         <v>0.2573313695009826</v>
       </c>
-      <c r="V138" t="n">
+      <c r="X138" t="n">
         <v>0.1164493340973879</v>
       </c>
-      <c r="W138" t="n">
+      <c r="Y138" t="n">
         <v>0.08092485549132947</v>
       </c>
     </row>
@@ -10561,24 +11393,30 @@
         <v>1.032575533870016</v>
       </c>
       <c r="Q139" t="n">
+        <v>1.065971095512684</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1.078373366377271</v>
+      </c>
+      <c r="S139" t="n">
         <v>1.033932292630582</v>
       </c>
-      <c r="R139" t="n">
+      <c r="T139" t="n">
         <v>163</v>
       </c>
-      <c r="S139" t="n">
+      <c r="U139" t="n">
         <v>3.021101980483781</v>
       </c>
-      <c r="T139" t="n">
+      <c r="V139" t="n">
         <v>3.223048032724432</v>
       </c>
-      <c r="U139" t="n">
+      <c r="W139" t="n">
         <v>0.1255466710745843</v>
       </c>
-      <c r="V139" t="n">
+      <c r="X139" t="n">
         <v>0.06117989852082235</v>
       </c>
-      <c r="W139" t="n">
+      <c r="Y139" t="n">
         <v>0.0736196319018405</v>
       </c>
     </row>
@@ -10634,24 +11472,30 @@
         <v>1.066958734048004</v>
       </c>
       <c r="Q140" t="n">
+        <v>1.165514017250915</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1.14277074835694</v>
+      </c>
+      <c r="S140" t="n">
         <v>1.037569978740648</v>
       </c>
-      <c r="R140" t="n">
+      <c r="T140" t="n">
         <v>59</v>
       </c>
-      <c r="S140" t="n">
+      <c r="U140" t="n">
         <v>3.156829667099132</v>
       </c>
-      <c r="T140" t="n">
+      <c r="V140" t="n">
         <v>3.922462462830909</v>
       </c>
-      <c r="U140" t="n">
+      <c r="W140" t="n">
         <v>0.1989045080603218</v>
       </c>
-      <c r="V140" t="n">
+      <c r="X140" t="n">
         <v>0.09603208430333636</v>
       </c>
-      <c r="W140" t="n">
+      <c r="Y140" t="n">
         <v>0.0847457627118644</v>
       </c>
     </row>
@@ -10703,24 +11547,30 @@
         <v>1</v>
       </c>
       <c r="Q141" t="n">
-        <v>1</v>
+        <v>1.044308990907629</v>
       </c>
       <c r="R141" t="n">
+        <v>1</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" t="n">
         <v>3</v>
       </c>
-      <c r="S141" t="n">
+      <c r="U141" t="n">
         <v>0.190516492494381</v>
       </c>
-      <c r="T141" t="n">
+      <c r="V141" t="n">
         <v>0.9064969307395134</v>
       </c>
-      <c r="U141" t="n">
+      <c r="W141" t="n">
         <v>0.0699628358613127</v>
       </c>
-      <c r="V141" t="n">
+      <c r="X141" t="n">
         <v>0</v>
       </c>
-      <c r="W141" t="n">
+      <c r="Y141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10776,24 +11626,30 @@
         <v>1.017727904411585</v>
       </c>
       <c r="Q142" t="n">
+        <v>1.102354200089017</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1.097249940681272</v>
+      </c>
+      <c r="S142" t="n">
         <v>1.012312089381855</v>
       </c>
-      <c r="R142" t="n">
+      <c r="T142" t="n">
         <v>358</v>
       </c>
-      <c r="S142" t="n">
+      <c r="U142" t="n">
         <v>3.878523692484617</v>
       </c>
-      <c r="T142" t="n">
+      <c r="V142" t="n">
         <v>3.734577612306516</v>
       </c>
-      <c r="U142" t="n">
+      <c r="W142" t="n">
         <v>0.04622617007454531</v>
       </c>
-      <c r="V142" t="n">
+      <c r="X142" t="n">
         <v>0.05470677793314647</v>
       </c>
-      <c r="W142" t="n">
+      <c r="Y142" t="n">
         <v>0.05586592178770949</v>
       </c>
     </row>
@@ -10849,24 +11705,30 @@
         <v>1.00557437476491</v>
       </c>
       <c r="Q143" t="n">
+        <v>1.122447344887776</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.12562021534747</v>
+      </c>
+      <c r="S143" t="n">
         <v>1.037900570163677</v>
       </c>
-      <c r="R143" t="n">
+      <c r="T143" t="n">
         <v>53</v>
       </c>
-      <c r="S143" t="n">
+      <c r="U143" t="n">
         <v>1.899414364315825</v>
       </c>
-      <c r="T143" t="n">
+      <c r="V143" t="n">
         <v>2.545524398306053</v>
       </c>
-      <c r="U143" t="n">
+      <c r="W143" t="n">
         <v>0.1487209151004562</v>
       </c>
-      <c r="V143" t="n">
+      <c r="X143" t="n">
         <v>0.06662691262845767</v>
       </c>
-      <c r="W143" t="n">
+      <c r="Y143" t="n">
         <v>0.07547169811320754</v>
       </c>
     </row>
@@ -10922,24 +11784,30 @@
         <v>1.012782755456062</v>
       </c>
       <c r="Q144" t="n">
+        <v>1.055117896591402</v>
+      </c>
+      <c r="R144" t="n">
+        <v>1.068863888971745</v>
+      </c>
+      <c r="S144" t="n">
         <v>1.000278931611801</v>
       </c>
-      <c r="R144" t="n">
+      <c r="T144" t="n">
         <v>32</v>
       </c>
-      <c r="S144" t="n">
+      <c r="U144" t="n">
         <v>1.576269932998556</v>
       </c>
-      <c r="T144" t="n">
+      <c r="V144" t="n">
         <v>1.363434763597087</v>
       </c>
-      <c r="U144" t="n">
+      <c r="W144" t="n">
         <v>0.1495797502656855</v>
       </c>
-      <c r="V144" t="n">
+      <c r="X144" t="n">
         <v>0.1283725245153101</v>
       </c>
-      <c r="W144" t="n">
+      <c r="Y144" t="n">
         <v>0.09375</v>
       </c>
     </row>
@@ -10995,24 +11863,30 @@
         <v>1</v>
       </c>
       <c r="Q145" t="n">
+        <v>1.021906599097004</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1.076126932884518</v>
+      </c>
+      <c r="S145" t="n">
         <v>1.000144120413532</v>
       </c>
-      <c r="R145" t="n">
+      <c r="T145" t="n">
         <v>86</v>
       </c>
-      <c r="S145" t="n">
+      <c r="U145" t="n">
         <v>0.8601329234915431</v>
       </c>
-      <c r="T145" t="n">
+      <c r="V145" t="n">
         <v>1.039274492787589</v>
       </c>
-      <c r="U145" t="n">
+      <c r="W145" t="n">
         <v>0.06422663949696464</v>
       </c>
-      <c r="V145" t="n">
+      <c r="X145" t="n">
         <v>0.001505695639488217</v>
       </c>
-      <c r="W145" t="n">
+      <c r="Y145" t="n">
         <v>0.08139534883720931</v>
       </c>
     </row>
@@ -11068,24 +11942,30 @@
         <v>1.002586608618625</v>
       </c>
       <c r="Q146" t="n">
+        <v>1.013766738265798</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1.051338725080092</v>
+      </c>
+      <c r="S146" t="n">
         <v>1.000893303299127</v>
       </c>
-      <c r="R146" t="n">
+      <c r="T146" t="n">
         <v>7</v>
       </c>
-      <c r="S146" t="n">
+      <c r="U146" t="n">
         <v>1.046584952875219</v>
       </c>
-      <c r="T146" t="n">
+      <c r="V146" t="n">
         <v>1.506255263709312</v>
       </c>
-      <c r="U146" t="n">
+      <c r="W146" t="n">
         <v>0.2444793042576891</v>
       </c>
-      <c r="V146" t="n">
+      <c r="X146" t="n">
         <v>0.01969552426254956</v>
       </c>
-      <c r="W146" t="n">
+      <c r="Y146" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -11144,21 +12024,27 @@
         <v>1</v>
       </c>
       <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
         <v>5</v>
       </c>
-      <c r="S147" t="n">
+      <c r="U147" t="n">
         <v>0.5927797837953727</v>
       </c>
-      <c r="T147" t="n">
+      <c r="V147" t="n">
         <v>1.354300096597659</v>
       </c>
-      <c r="U147" t="n">
+      <c r="W147" t="n">
         <v>0.1298758075264771</v>
       </c>
-      <c r="V147" t="n">
+      <c r="X147" t="n">
         <v>0</v>
       </c>
-      <c r="W147" t="n">
+      <c r="Y147" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -11214,24 +12100,30 @@
         <v>1.004835435131385</v>
       </c>
       <c r="Q148" t="n">
+        <v>1.007964247847776</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1.086180435903662</v>
+      </c>
+      <c r="S148" t="n">
         <v>1.04137986588416</v>
       </c>
-      <c r="R148" t="n">
+      <c r="T148" t="n">
         <v>12</v>
       </c>
-      <c r="S148" t="n">
+      <c r="U148" t="n">
         <v>-0.256052564058103</v>
       </c>
-      <c r="T148" t="n">
+      <c r="V148" t="n">
         <v>1.650346730904077</v>
       </c>
-      <c r="U148" t="n">
+      <c r="W148" t="n">
         <v>0.1194784357290234</v>
       </c>
-      <c r="V148" t="n">
+      <c r="X148" t="n">
         <v>0.004962090400331437</v>
       </c>
-      <c r="W148" t="n">
+      <c r="Y148" t="n">
         <v>0.08333333333333333</v>
       </c>
     </row>

--- a/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
+++ b/outputs/tables/TABLE_EmpiricalECCMetrics.xlsx
@@ -593,7 +593,7 @@
         <v>1.001005137361129</v>
       </c>
       <c r="R2" t="n">
-        <v>1.040928943346033</v>
+        <v>1.041371815820066</v>
       </c>
       <c r="S2" t="n">
         <v>1.028084151618127</v>
@@ -748,10 +748,10 @@
         <v>1.016773947613548</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.117779760793197</v>
+        <v>1.118913806324753</v>
       </c>
       <c r="R4" t="n">
-        <v>1.074827170779614</v>
+        <v>1.075796374591005</v>
       </c>
       <c r="S4" t="n">
         <v>1.008822288055942</v>
@@ -827,10 +827,10 @@
         <v>1.005306417188222</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.135991607168941</v>
+        <v>1.136143049127039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.106463291044453</v>
+        <v>1.106519789666069</v>
       </c>
       <c r="S5" t="n">
         <v>1.005654889400433</v>
@@ -909,7 +909,7 @@
         <v>1.017960331410465</v>
       </c>
       <c r="R6" t="n">
-        <v>1.034609716389288</v>
+        <v>1.035644061647895</v>
       </c>
       <c r="S6" t="n">
         <v>1.017329270759607</v>
@@ -988,7 +988,7 @@
         <v>1.014211249708263</v>
       </c>
       <c r="R7" t="n">
-        <v>1.159210556004727</v>
+        <v>1.161841353784153</v>
       </c>
       <c r="S7" t="n">
         <v>1.070504973760363</v>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.003307479763752</v>
+        <v>1.004320645346087</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         <v>1.060612924990478</v>
       </c>
       <c r="R10" t="n">
-        <v>1.094247496742057</v>
+        <v>1.097297761196359</v>
       </c>
       <c r="S10" t="n">
         <v>1.020400589490248</v>
@@ -1297,10 +1297,10 @@
         <v>1.013475204322204</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.028614414198721</v>
+        <v>1.028935613387999</v>
       </c>
       <c r="R11" t="n">
-        <v>1.025951272610127</v>
+        <v>1.026258495497775</v>
       </c>
       <c r="S11" t="n">
         <v>1.009154565156715</v>
@@ -1376,10 +1376,10 @@
         <v>1.080549448342853</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.201758612243786</v>
+        <v>1.204092102131916</v>
       </c>
       <c r="R12" t="n">
-        <v>1.137314367612276</v>
+        <v>1.13972238004452</v>
       </c>
       <c r="S12" t="n">
         <v>1.037033785089428</v>
@@ -1455,10 +1455,10 @@
         <v>1.029396277306996</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.114368293052237</v>
+        <v>1.115693451104787</v>
       </c>
       <c r="R13" t="n">
-        <v>1.049153364533274</v>
+        <v>1.049770517554048</v>
       </c>
       <c r="S13" t="n">
         <v>1.022207261993878</v>
@@ -1537,7 +1537,7 @@
         <v>1.04743179209658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.095848139130641</v>
+        <v>1.096486527360492</v>
       </c>
       <c r="S14" t="n">
         <v>1.060576411318667</v>
@@ -1613,10 +1613,10 @@
         <v>1.048655536058486</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.059818382507851</v>
+        <v>1.06064613716609</v>
       </c>
       <c r="R15" t="n">
-        <v>1.098512757175423</v>
+        <v>1.0998850446617</v>
       </c>
       <c r="S15" t="n">
         <v>1.053545989607294</v>
@@ -1767,10 +1767,10 @@
         <v>1.001928862956075</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.067589308846356</v>
+        <v>1.069352440673402</v>
       </c>
       <c r="R17" t="n">
-        <v>1.090605257640002</v>
+        <v>1.091878950776468</v>
       </c>
       <c r="S17" t="n">
         <v>1.012983759217844</v>
@@ -2000,10 +2000,10 @@
         <v>1.054261395994039</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.183176781354193</v>
+        <v>1.185236522835171</v>
       </c>
       <c r="R20" t="n">
-        <v>1.093883842034411</v>
+        <v>1.09488092595851</v>
       </c>
       <c r="S20" t="n">
         <v>1.028183096469301</v>
@@ -2082,7 +2082,7 @@
         <v>1.013474520786705</v>
       </c>
       <c r="R21" t="n">
-        <v>1.102597468904421</v>
+        <v>1.10342149137605</v>
       </c>
       <c r="S21" t="n">
         <v>1.040669813376224</v>
@@ -2237,10 +2237,10 @@
         <v>1.003368971976756</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.058232584769141</v>
+        <v>1.058955408914242</v>
       </c>
       <c r="R23" t="n">
-        <v>1.064295313634011</v>
+        <v>1.064910610970679</v>
       </c>
       <c r="S23" t="n">
         <v>1.020510203801384</v>
@@ -2395,10 +2395,10 @@
         <v>1.001474574675983</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.024118723169152</v>
+        <v>1.024365295147244</v>
       </c>
       <c r="R25" t="n">
-        <v>1.00044850973277</v>
+        <v>1.000594388582842</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -2474,10 +2474,10 @@
         <v>1.022644424446105</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.111093477678355</v>
+        <v>1.111770225505706</v>
       </c>
       <c r="R26" t="n">
-        <v>1.146520993992054</v>
+        <v>1.147915825999789</v>
       </c>
       <c r="S26" t="n">
         <v>1.020311499581628</v>
@@ -2553,10 +2553,10 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.066517157184333</v>
+        <v>1.070447850305662</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>1.000064240997709</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -2790,10 +2790,10 @@
         <v>1.005232062798919</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.013401556433007</v>
+        <v>1.013570778072815</v>
       </c>
       <c r="R30" t="n">
-        <v>1.016649198754034</v>
+        <v>1.017572587536853</v>
       </c>
       <c r="S30" t="n">
         <v>1.004047425114218</v>
@@ -2951,7 +2951,7 @@
         <v>1.00565550153298</v>
       </c>
       <c r="R32" t="n">
-        <v>1.089840870387961</v>
+        <v>1.094016768518122</v>
       </c>
       <c r="S32" t="n">
         <v>1.02100698543268</v>
@@ -3027,10 +3027,10 @@
         <v>1.008108801711226</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.025978438358032</v>
+        <v>1.026398670056827</v>
       </c>
       <c r="R33" t="n">
-        <v>1.123139887123249</v>
+        <v>1.127000157449258</v>
       </c>
       <c r="S33" t="n">
         <v>1.035324952445202</v>
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.000025206500891</v>
+        <v>1.00002686342504</v>
       </c>
       <c r="R34" t="n">
         <v>1.011916826192858</v>
@@ -3185,7 +3185,7 @@
         <v>1.000279273016993</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.006796332644302</v>
+        <v>1.007290045400148</v>
       </c>
       <c r="R35" t="n">
         <v>1.012689686580874</v>
@@ -3264,10 +3264,10 @@
         <v>1.007528792011665</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.02119732637524</v>
+        <v>1.021835127900505</v>
       </c>
       <c r="R36" t="n">
-        <v>1.013873069787575</v>
+        <v>1.014142832617421</v>
       </c>
       <c r="S36" t="n">
         <v>1.007902376243321</v>
@@ -3346,7 +3346,7 @@
         <v>1.164500580507336</v>
       </c>
       <c r="R37" t="n">
-        <v>1.08355843659071</v>
+        <v>1.087129837971888</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3422,10 +3422,10 @@
         <v>1.006818309509078</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.0150309908208</v>
+        <v>1.015500751504483</v>
       </c>
       <c r="R38" t="n">
-        <v>1.026112799374688</v>
+        <v>1.026685062060117</v>
       </c>
       <c r="S38" t="n">
         <v>1.006566987101052</v>
@@ -3580,10 +3580,10 @@
         <v>1.017003241003839</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.034011606644861</v>
+        <v>1.036009599883016</v>
       </c>
       <c r="R40" t="n">
-        <v>1.09145096882896</v>
+        <v>1.095038354494908</v>
       </c>
       <c r="S40" t="n">
         <v>1.016613509646723</v>
@@ -3813,10 +3813,10 @@
         <v>1.009466591963998</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.084583491593362</v>
+        <v>1.084964957231459</v>
       </c>
       <c r="R43" t="n">
-        <v>1.047501299852954</v>
+        <v>1.048384377869743</v>
       </c>
       <c r="S43" t="n">
         <v>1.009314532090233</v>
@@ -3974,7 +3974,7 @@
         <v>1.112796744487812</v>
       </c>
       <c r="R45" t="n">
-        <v>1.002564935690344</v>
+        <v>1.003500405524472</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         <v>1.193671307438383</v>
       </c>
       <c r="R48" t="n">
-        <v>1.140283965988981</v>
+        <v>1.143732994453072</v>
       </c>
       <c r="S48" t="n">
         <v>1.07071058825641</v>
@@ -4290,7 +4290,7 @@
         <v>1.047403668878102</v>
       </c>
       <c r="R49" t="n">
-        <v>1.056382196913695</v>
+        <v>1.056585979120672</v>
       </c>
       <c r="S49" t="n">
         <v>1.047719077478554</v>
@@ -4366,10 +4366,10 @@
         <v>1.044027435087589</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.060968474854467</v>
+        <v>1.061375837601876</v>
       </c>
       <c r="R50" t="n">
-        <v>1.064229761868608</v>
+        <v>1.065551599416964</v>
       </c>
       <c r="S50" t="n">
         <v>1.020328607656752</v>
@@ -4445,10 +4445,10 @@
         <v>1.03071495916729</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.108714477349759</v>
+        <v>1.109515923361111</v>
       </c>
       <c r="R51" t="n">
-        <v>1.144649805670209</v>
+        <v>1.146002786956885</v>
       </c>
       <c r="S51" t="n">
         <v>1.023438953331128</v>
@@ -4524,10 +4524,10 @@
         <v>1.009637718721611</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.023846426141057</v>
+        <v>1.023987241206366</v>
       </c>
       <c r="R52" t="n">
-        <v>1.055061851730484</v>
+        <v>1.055754558196295</v>
       </c>
       <c r="S52" t="n">
         <v>1.009498219147334</v>
@@ -4682,10 +4682,10 @@
         <v>1.000928172842933</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.100211466831979</v>
+        <v>1.101927690068251</v>
       </c>
       <c r="R54" t="n">
-        <v>1.097390961791228</v>
+        <v>1.100179195723765</v>
       </c>
       <c r="S54" t="n">
         <v>1.005950304274737</v>
@@ -4919,10 +4919,10 @@
         <v>1.010334977323024</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.032153325114691</v>
+        <v>1.03240040044616</v>
       </c>
       <c r="R57" t="n">
-        <v>1.119521690979794</v>
+        <v>1.121337249992476</v>
       </c>
       <c r="S57" t="n">
         <v>1.025420395412684</v>
@@ -5076,7 +5076,7 @@
         <v>1.083716170495417</v>
       </c>
       <c r="R59" t="n">
-        <v>1.241365995508224</v>
+        <v>1.242313264637713</v>
       </c>
       <c r="S59" t="n">
         <v>1.053539405537984</v>
@@ -5231,10 +5231,10 @@
         <v>1.003257632254175</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.015930975536776</v>
+        <v>1.016565413489855</v>
       </c>
       <c r="R61" t="n">
-        <v>1.041323597038271</v>
+        <v>1.042621615051056</v>
       </c>
       <c r="S61" t="n">
         <v>1.007126677254597</v>
@@ -5313,7 +5313,7 @@
         <v>1.038206103802567</v>
       </c>
       <c r="R62" t="n">
-        <v>1.09524882328101</v>
+        <v>1.095233475569031</v>
       </c>
       <c r="S62" t="n">
         <v>1.063776019084027</v>
@@ -5392,7 +5392,7 @@
         <v>1.096863075106416</v>
       </c>
       <c r="R63" t="n">
-        <v>1.215258947895359</v>
+        <v>1.219112277842685</v>
       </c>
       <c r="S63" t="n">
         <v>1.039811505058307</v>
@@ -5550,7 +5550,7 @@
         <v>1.008501710306724</v>
       </c>
       <c r="R65" t="n">
-        <v>1.070308258708538</v>
+        <v>1.071213945610821</v>
       </c>
       <c r="S65" t="n">
         <v>1.031453791401421</v>
@@ -5626,10 +5626,10 @@
         <v>1.010849983984087</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.021642759681015</v>
+        <v>1.021912895320703</v>
       </c>
       <c r="R66" t="n">
-        <v>1.044157757569472</v>
+        <v>1.044708832486122</v>
       </c>
       <c r="S66" t="n">
         <v>1.015013990405764</v>
@@ -5942,10 +5942,10 @@
         <v>1.052465911252749</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.08102935277936</v>
+        <v>1.08156199152313</v>
       </c>
       <c r="R70" t="n">
-        <v>1.037034672543807</v>
+        <v>1.037384215505138</v>
       </c>
       <c r="S70" t="n">
         <v>1.023207025568986</v>
@@ -6021,10 +6021,10 @@
         <v>1.01250487802955</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.026156448743483</v>
+        <v>1.026353246044601</v>
       </c>
       <c r="R71" t="n">
-        <v>1.029419651223312</v>
+        <v>1.029702678114278</v>
       </c>
       <c r="S71" t="n">
         <v>1.012630819694899</v>
@@ -6337,10 +6337,10 @@
         <v>1.01915392111379</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.183325607898676</v>
+        <v>1.184003819840244</v>
       </c>
       <c r="R75" t="n">
-        <v>1.299183612446371</v>
+        <v>1.30103486506603</v>
       </c>
       <c r="S75" t="n">
         <v>1.035419072932095</v>
@@ -6416,10 +6416,10 @@
         <v>1.033475854842358</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.083085134862351</v>
+        <v>1.084752210383922</v>
       </c>
       <c r="R76" t="n">
-        <v>1.01472471618983</v>
+        <v>1.015188617681806</v>
       </c>
       <c r="S76" t="n">
         <v>1.00935474362358</v>
@@ -6495,10 +6495,10 @@
         <v>1.010086023593949</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.013758140317791</v>
+        <v>1.013841681361958</v>
       </c>
       <c r="R77" t="n">
-        <v>1.008408193453572</v>
+        <v>1.008466247582792</v>
       </c>
       <c r="S77" t="n">
         <v>1.006702423634908</v>
@@ -6577,7 +6577,7 @@
         <v>1.000105927208099</v>
       </c>
       <c r="R78" t="n">
-        <v>1.139678607190467</v>
+        <v>1.140490649595412</v>
       </c>
       <c r="S78" t="n">
         <v>1.006423424039746</v>
@@ -6814,7 +6814,7 @@
         <v>1.085063658874821</v>
       </c>
       <c r="R81" t="n">
-        <v>1.098696964806258</v>
+        <v>1.099623643501167</v>
       </c>
       <c r="S81" t="n">
         <v>1.025866133362981</v>
@@ -6893,7 +6893,7 @@
         <v>1.008399520679616</v>
       </c>
       <c r="R82" t="n">
-        <v>1.05127383074672</v>
+        <v>1.052841477046448</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -6969,10 +6969,10 @@
         <v>1.10023898526898</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.227149875949632</v>
+        <v>1.227728040334726</v>
       </c>
       <c r="R83" t="n">
-        <v>1.190435449306315</v>
+        <v>1.19126269922003</v>
       </c>
       <c r="S83" t="n">
         <v>1.096834633890862</v>
@@ -7051,7 +7051,7 @@
         <v>1.001577046792815</v>
       </c>
       <c r="R84" t="n">
-        <v>1.162644459024371</v>
+        <v>1.164813175855732</v>
       </c>
       <c r="S84" t="n">
         <v>1.016696448388154</v>
@@ -7130,7 +7130,7 @@
         <v>1.018685932803797</v>
       </c>
       <c r="R85" t="n">
-        <v>1.063993467385989</v>
+        <v>1.065899030805943</v>
       </c>
       <c r="S85" t="n">
         <v>1.023267504114854</v>
@@ -7443,10 +7443,10 @@
         <v>1.036823526797908</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.130853435263917</v>
+        <v>1.13381697196313</v>
       </c>
       <c r="R89" t="n">
-        <v>1.056052410512879</v>
+        <v>1.059491866107141</v>
       </c>
       <c r="S89" t="n">
         <v>1.022144060724332</v>
@@ -7522,10 +7522,10 @@
         <v>1.016675447209708</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.066650411213881</v>
+        <v>1.067414600117276</v>
       </c>
       <c r="R90" t="n">
-        <v>1.098162439654083</v>
+        <v>1.0988971811051</v>
       </c>
       <c r="S90" t="n">
         <v>1.022418497241333</v>
@@ -7683,7 +7683,7 @@
         <v>1.015491839119834</v>
       </c>
       <c r="R92" t="n">
-        <v>1.127756234512661</v>
+        <v>1.129756875595182</v>
       </c>
       <c r="S92" t="n">
         <v>1.000255009972166</v>
@@ -7762,7 +7762,7 @@
         <v>1.009574733636376</v>
       </c>
       <c r="R93" t="n">
-        <v>1.088386244467616</v>
+        <v>1.091325654718282</v>
       </c>
       <c r="S93" t="n">
         <v>1.033688772809744</v>
@@ -7838,10 +7838,10 @@
         <v>1.017525371528395</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.132920330374832</v>
+        <v>1.134441569559192</v>
       </c>
       <c r="R94" t="n">
-        <v>1.165732751759302</v>
+        <v>1.169218555655489</v>
       </c>
       <c r="S94" t="n">
         <v>1.039029327919982</v>
@@ -8075,10 +8075,10 @@
         <v>1.014104428106125</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.034277594365932</v>
+        <v>1.034829752274044</v>
       </c>
       <c r="R97" t="n">
-        <v>1.049673764268197</v>
+        <v>1.050741589488603</v>
       </c>
       <c r="S97" t="n">
         <v>1.0090969367735</v>
@@ -8233,10 +8233,10 @@
         <v>1.016251206873568</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.040146902911874</v>
+        <v>1.040664163486428</v>
       </c>
       <c r="R99" t="n">
-        <v>1.121475256785471</v>
+        <v>1.125190571316243</v>
       </c>
       <c r="S99" t="n">
         <v>1.036482101907221</v>
@@ -8315,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>1.020167778469986</v>
+        <v>1.021258290171881</v>
       </c>
       <c r="S100" t="n">
         <v>1.000858196647481</v>
@@ -8391,10 +8391,10 @@
         <v>1.017535480649453</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.095040746556481</v>
+        <v>1.0960638649596</v>
       </c>
       <c r="R101" t="n">
-        <v>1.082533642224376</v>
+        <v>1.083347527794401</v>
       </c>
       <c r="S101" t="n">
         <v>1.013484922788592</v>
@@ -8470,10 +8470,10 @@
         <v>1.009097458874169</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.040510312661889</v>
+        <v>1.041459514564951</v>
       </c>
       <c r="R102" t="n">
-        <v>1.051552741916877</v>
+        <v>1.053115674218995</v>
       </c>
       <c r="S102" t="n">
         <v>1.015071317116978</v>
@@ -8549,10 +8549,10 @@
         <v>1.010879044614635</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.044967177118566</v>
+        <v>1.045614230738552</v>
       </c>
       <c r="R103" t="n">
-        <v>1.047314072748331</v>
+        <v>1.047660121784866</v>
       </c>
       <c r="S103" t="n">
         <v>1.020541475120251</v>
@@ -8628,10 +8628,10 @@
         <v>1.000745040550296</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.001455952920771</v>
+        <v>1.001512663626723</v>
       </c>
       <c r="R104" t="n">
-        <v>1.001772487326929</v>
+        <v>1.00182708648815</v>
       </c>
       <c r="S104" t="n">
         <v>1.000830925627947</v>
@@ -8707,10 +8707,10 @@
         <v>1.001446298869981</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.002652126390932</v>
+        <v>1.002668142936662</v>
       </c>
       <c r="R105" t="n">
-        <v>1.00250265881513</v>
+        <v>1.002522392830705</v>
       </c>
       <c r="S105" t="n">
         <v>1.001944668362955</v>
@@ -8865,10 +8865,10 @@
         <v>1.007528808882736</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.011366143999975</v>
+        <v>1.011830704961316</v>
       </c>
       <c r="R107" t="n">
-        <v>1.017536230417437</v>
+        <v>1.017791839749926</v>
       </c>
       <c r="S107" t="n">
         <v>1.00994527209299</v>
@@ -9023,10 +9023,10 @@
         <v>1.002013807548805</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.003714004434963</v>
+        <v>1.003796442919276</v>
       </c>
       <c r="R109" t="n">
-        <v>1.007795364176455</v>
+        <v>1.008279082668069</v>
       </c>
       <c r="S109" t="n">
         <v>1.003893016525779</v>
@@ -9102,10 +9102,10 @@
         <v>1.014687776985438</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.142899371814483</v>
+        <v>1.144445338953628</v>
       </c>
       <c r="R110" t="n">
-        <v>1.112001908521034</v>
+        <v>1.112791113416083</v>
       </c>
       <c r="S110" t="n">
         <v>1.025271466101481</v>
@@ -9181,10 +9181,10 @@
         <v>1.044217537281513</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.233892375040221</v>
+        <v>1.2374806507151</v>
       </c>
       <c r="R111" t="n">
-        <v>1.137409975552358</v>
+        <v>1.13955957646049</v>
       </c>
       <c r="S111" t="n">
         <v>1.037810624895072</v>
@@ -9263,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>1.020594937432143</v>
+        <v>1.02283463239648</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -9342,7 +9342,7 @@
         <v>1.102693387741539</v>
       </c>
       <c r="R113" t="n">
-        <v>1.001984070467864</v>
+        <v>1.002290808304046</v>
       </c>
       <c r="S113" t="n">
         <v>1</v>
@@ -9418,10 +9418,10 @@
         <v>1.006012606692849</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.329854565967702</v>
+        <v>1.332158884173532</v>
       </c>
       <c r="R114" t="n">
-        <v>1.052413834280961</v>
+        <v>1.053861813538904</v>
       </c>
       <c r="S114" t="n">
         <v>1.00123504297487</v>
@@ -9500,7 +9500,7 @@
         <v>1.002098553553409</v>
       </c>
       <c r="R115" t="n">
-        <v>1.029799443504566</v>
+        <v>1.03112065460028</v>
       </c>
       <c r="S115" t="n">
         <v>1.004505860103953</v>
@@ -9576,10 +9576,10 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.028423280103563</v>
+        <v>1.031202497954827</v>
       </c>
       <c r="R116" t="n">
-        <v>1.000574668343487</v>
+        <v>1.000640374866406</v>
       </c>
       <c r="S116" t="n">
         <v>1</v>
@@ -9813,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.00101675698499</v>
+        <v>1.001120070844107</v>
       </c>
       <c r="R119" t="n">
         <v>1.000735000895359</v>
@@ -9892,10 +9892,10 @@
         <v>1.013094761109131</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.132042831740214</v>
+        <v>1.135627244828141</v>
       </c>
       <c r="R120" t="n">
-        <v>1.142472689829257</v>
+        <v>1.143816588786133</v>
       </c>
       <c r="S120" t="n">
         <v>1.062296920709371</v>
@@ -9974,7 +9974,7 @@
         <v>1.014103998890121</v>
       </c>
       <c r="R121" t="n">
-        <v>1.044022486629834</v>
+        <v>1.044722607564978</v>
       </c>
       <c r="S121" t="n">
         <v>1.022020897969908</v>
@@ -10129,10 +10129,10 @@
         <v>1.013149961933713</v>
       </c>
       <c r="Q123" t="n">
-        <v>1.020380669778818</v>
+        <v>1.020622232544045</v>
       </c>
       <c r="R123" t="n">
-        <v>1.047682093341697</v>
+        <v>1.048224754289153</v>
       </c>
       <c r="S123" t="n">
         <v>1.021223614675844</v>
@@ -10211,7 +10211,7 @@
         <v>1.05572362784677</v>
       </c>
       <c r="R124" t="n">
-        <v>1.056555648933941</v>
+        <v>1.057523612713476</v>
       </c>
       <c r="S124" t="n">
         <v>1.045290362191896</v>
@@ -10445,10 +10445,10 @@
         <v>1.013106436406949</v>
       </c>
       <c r="Q127" t="n">
-        <v>1.026421068886595</v>
+        <v>1.026916691563903</v>
       </c>
       <c r="R127" t="n">
-        <v>1.025586231826069</v>
+        <v>1.025750472503384</v>
       </c>
       <c r="S127" t="n">
         <v>1.020658356003813</v>
@@ -10761,10 +10761,10 @@
         <v>1.015075583618936</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.017079013921605</v>
+        <v>1.017163306640877</v>
       </c>
       <c r="R131" t="n">
-        <v>1.069478841464237</v>
+        <v>1.070797261622067</v>
       </c>
       <c r="S131" t="n">
         <v>1.010052084659834</v>
@@ -10840,10 +10840,10 @@
         <v>1.020294196131324</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.126608841608396</v>
+        <v>1.128598743867653</v>
       </c>
       <c r="R132" t="n">
-        <v>1.188453484583632</v>
+        <v>1.190225530849396</v>
       </c>
       <c r="S132" t="n">
         <v>1.028004806138072</v>
@@ -10998,10 +10998,10 @@
         <v>1.046665800453953</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.141421819711912</v>
+        <v>1.14243025552887</v>
       </c>
       <c r="R134" t="n">
-        <v>1.160367896557249</v>
+        <v>1.162515577537538</v>
       </c>
       <c r="S134" t="n">
         <v>1.021736585612737</v>
@@ -11314,10 +11314,10 @@
         <v>1.028656088161708</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.08662541417153</v>
+        <v>1.086909725542303</v>
       </c>
       <c r="R138" t="n">
-        <v>1.091662236116571</v>
+        <v>1.092163920389355</v>
       </c>
       <c r="S138" t="n">
         <v>1.010492619786958</v>
@@ -11393,10 +11393,10 @@
         <v>1.038624047913878</v>
       </c>
       <c r="Q139" t="n">
-        <v>1.124498478724844</v>
+        <v>1.126226182813179</v>
       </c>
       <c r="R139" t="n">
-        <v>1.078373366377271</v>
+        <v>1.07924387306207</v>
       </c>
       <c r="S139" t="n">
         <v>1.033932292630582</v>
@@ -11472,10 +11472,10 @@
         <v>1.020158683026965</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.203888712261839</v>
+        <v>1.204627240844355</v>
       </c>
       <c r="R140" t="n">
-        <v>1.14277074835694</v>
+        <v>1.144111519999631</v>
       </c>
       <c r="S140" t="n">
         <v>1.037569978740648</v>
@@ -11626,10 +11626,10 @@
         <v>1.012582012179135</v>
       </c>
       <c r="Q142" t="n">
-        <v>1.177493547102611</v>
+        <v>1.180410714042639</v>
       </c>
       <c r="R142" t="n">
-        <v>1.097249940681272</v>
+        <v>1.098593285139021</v>
       </c>
       <c r="S142" t="n">
         <v>1.012312089381855</v>
@@ -11705,10 +11705,10 @@
         <v>1.002986794977022</v>
       </c>
       <c r="Q143" t="n">
-        <v>1.049754673128539</v>
+        <v>1.05075406396519</v>
       </c>
       <c r="R143" t="n">
-        <v>1.12562021534747</v>
+        <v>1.126286570838365</v>
       </c>
       <c r="S143" t="n">
         <v>1.037900570163677</v>
@@ -11787,7 +11787,7 @@
         <v>1.012769096579075</v>
       </c>
       <c r="R144" t="n">
-        <v>1.068863888971745</v>
+        <v>1.069762181548098</v>
       </c>
       <c r="S144" t="n">
         <v>1.000278931611801</v>
@@ -11863,10 +11863,10 @@
         <v>1.017775406722974</v>
       </c>
       <c r="Q145" t="n">
-        <v>1.173608048918247</v>
+        <v>1.175835024156027</v>
       </c>
       <c r="R145" t="n">
-        <v>1.076126932884518</v>
+        <v>1.077475759745978</v>
       </c>
       <c r="S145" t="n">
         <v>1.000144120413532</v>
